--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +48,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D3CE"/>
+        <fgColor rgb="00D9F2DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -58,7 +58,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9F2DC"/>
+        <fgColor rgb="00F8D3CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력에 '견적서 작성 #영업 !높음 ~내일' 입력·Enter 2) 캘린더 업무 패널에서 그 업무를 오늘 14:00 칸으로 끌어 놓기</t>
+          <t>1) 빠른 입력에 '견적서 작성 @영업 !높음 ~내일' 입력·Enter 2) 캘린더 업무 패널에서 그 업무를 오늘 14:00 칸으로 끌어 놓기</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -774,8 +774,16 @@
           <t>항목별 자동 저장(저장 버튼 없음), 새로고침 후 값 유지, 사이드바 프로필에 이름·소속 반영</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] /settings → /settings/profile(데스크톱은 첫 탭). 이름·소속·직책 입력 후 Tab·Enter로 칸을 벗어나면 저장(저장 버튼 없음, version 1→3 순서대로). 새로고침 후 값 유지, 사이드바 프로필에 이름·소속 반영</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
     </row>
@@ -820,8 +828,16 @@
           <t>이메일은 읽기 전용, 미리보기가 입력값으로 즉시 갱신</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 이메일 칸 readOnly(입력해도 안 바뀜), 일지 머리 미리보기가 입력 중 즉시 갱신(작성자·소속·직책·일자 2026. 10. 6.(화)), 빈 칸은 [이름]·[소속]·[직책]</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
     </row>
@@ -866,10 +882,22 @@
           <t>시간대 Asia/Seoul, 주 시작 월요일, 업무 요일 월~금, 키보드 단축키 켜짐</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 기본값: 서울(Asia/Seoul), 월요일, 월~금, 키보드 단축키 켜짐</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>화면정의서 SCR-SET-02 ④업무 시간대·⑤하루 마감 시각은 P2·P3라 화면에 없음(정상). 시간대 목록이 418개를 그대로 나열하고 Asia/Calcutta·Asia/Saigon 같은 옛 이름이 섞여 있음 — 사용성 관찰</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -912,10 +940,22 @@
           <t>자동 저장, 캘린더 주가 일요일부터 시작, 되돌리면 월요일부터</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 주 시작 요일 일요일로 바꾸면 즉시 저장(version 증가). 캘린더 반영은 확인 불가</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>캘린더(P1-07) 구현 전</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -958,10 +998,22 @@
           <t>"기존 기록의 날짜는 그대로예요. 시각 표시만 새 시간대로 바뀌어요" 안내, 시각만 새 시간대로 표시</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 시간대 도쿄로 바꾸면 즉시 저장. 안내 '시간대를 바꿔도 기존 기록의 날짜는 그대로예요. 시각 표시만 새 시간대로 바뀌어요.'는 화면에 늘 표시. 일정 시각 표시는 확인 불가</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>일정 화면(P1-05·07) 구현 전. 안내를 변경 시에만이 아니라 늘 보여 줌 — 화면정의서 '시간대 변경 시 안내'와 표현 차이, 판단은 erp-design</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1004,8 +1056,16 @@
           <t>변경 유지(identity 프로필, work_days 비트마스크). 마지막 요일은 끌 수 없거나 칸 오류(서버는 1~127만 받음, D-59)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 요일 버튼 클릭마다 즉시 저장(aria-pressed 반영, 새로고침 유지). 마지막 남은 요일을 끄면 저장하지 않고 '업무 요일을 하루 이상 골라 주세요'(role=alert)</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
     </row>
@@ -1050,10 +1110,22 @@
           <t>실패한 항목에만 오류 표시, 다른 항목 값은 영향 없음</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 소속 칸에 101자를 넣고 벗어나면(maxlength를 지워 서버 검증까지 보냄) 그 칸만 aria-invalid + '100자 이하로 적어 주세요', 다른 칸(직책)은 그대로 저장됨</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>평소에는 maxlength=100이라 101자를 입력할 수 없음</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1096,8 +1168,16 @@
           <t>B에 409 VERSION_CONFLICT → 충돌 띠 "다른 곳에서 먼저 수정됐어요. 이 변경은 저장되지 않았어요" + [새로 불러오기]</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 같은 계정 두 탭: B에서 이름 저장 후 A에서 직책 변경 → '다른 곳에서 먼저 수정됐어요. 이 변경은 저장되지 않았어요' + [새로 불러오기], A의 변경은 저장 안 됨. 새로 불러오기 → 띠 사라지고 칸이 서버 값(B의 이름)으로 채워짐, 이후 저장 정상. 일반 탭(시간대·단축키)도 같음</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
     </row>
@@ -1142,10 +1222,22 @@
           <t>worklog 프로필 재조회로 바뀐 이름이 반영, 늦게 온 옛 값이 새 값을 덮어쓰지 않음(version 큰 값만 반영)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>worklog 화면에서 이름을 보여 주는 곳이 아직 없고, dev:mock은 worklog 재조회를 흉내만 냄. 운영 배포 후 확인</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1188,25 +1280,37 @@
           <t>목록 → 상세 구조, 가로 스크롤 없음</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 390px: /settings는 목록(프로필 ›, 일반 ›)만, 항목을 누르면 상세에서 목록 숨김 + '‹ 설정'(44px)으로 돌아옴. 가로 스크롤 없음, 요일 버튼 44x44, select 높이 44</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>키보드 단축키 스위치는 56x32로 높이가 44px 미만(화면정의서 2.5 터치 영역) — 관찰, 목업 기준은 erp-design</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>P1-02-01</t>
+          <t>P1-01-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08</t>
+          <t>SCR-SET-02</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04</t>
+          <t>P1-01, UX-09, D-60</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1226,38 +1330,50 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1) /settings/projects에서 이름 입력·팔레트 색 선택해 프로젝트 추가</t>
+          <t>1) 설정 › 일반에서 키보드 단축키 끄기 2) 홈·다른 화면에서 N 3) Ctrl+K 4) 빠른 입력창·팔레트의 단축키 표시 확인 5) 다시 켜기</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>목록에 색·이름·업무 수 0 표시, 사이드바 프로젝트 목록에 색 점과 함께 추가</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>끄면 즉시 저장, N 등 한 글자 단축키 미동작, 수식키 단축키(Ctrl+K)는 동작, 화면의 단축키 안내(N)도 숨김, 켜면 다시 동작</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 끄면 즉시 저장(version 증가), N은 홈·설정 어디서도 미동작, Ctrl+K 팔레트는 열리고 팔레트의 '업무 추가' 옆 N 표시는 사라짐. 그러나 빠른 입력창 오른쪽의 'N' 안내(kbd)는 그대로 보여, 눌러도 동작하지 않는 단축키를 안내함. 다시 켜면 N 동작</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-01-11.png</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>P1-02-02</t>
+          <t>P1-01-12</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08</t>
+          <t>SCR-SET-01, 02</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04, 2.2</t>
+          <t>P1-01, D-58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1272,33 +1388,41 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1) 프로젝트 색 팔레트 확인 2) 테마 키 컬러와 비교</t>
+          <t>1) 여러 칸을 빠르게 연달아 바꾸기(Tab으로 이동하며 저장, 요일 버튼 연속 클릭)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>전용 8색, 테마와 무관하게 고정</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+          <t>저장이 순서대로 나가 409가 생기지 않고 모든 변경이 반영</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] Tab으로 칸을 옮기며 연달아 저장, 요일 버튼 3개를 빠르게 연속 클릭 → 409 없음, 모든 변경 반영(14 → 111), version이 저장 수만큼 증가</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>P1-02-03</t>
+          <t>P1-01-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08</t>
+          <t>SCR-SET-01</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>P1-02</t>
+          <t>P1-01, AUTH-04</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1313,38 +1437,46 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 이름·소속·직책 입력됨</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1) 이미 있는 이름으로 프로젝트 추가 2) 빈 이름으로 추가</t>
+          <t>1) 칸을 비우거나 공백만 남기고 벗어나기 2) 바꾸지 않고 벗어나기</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>칸 아래 오류(서버 errors[] 포함)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t>빈 칸은 null로 저장(미리보기 [이름] 등 빈칸 표시), 값이 그대로면 저장 요청 없음</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 소속을 지우고, 직책을 공백만 남기고 벗어나면 각각 null로 저장되고 미리보기가 [소속]·[직책]으로 바뀜. 값을 바꾸지 않고 벗어나면 저장 요청 없음(version 그대로)</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>P1-02-04</t>
+          <t>P1-02-01</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08, SCR-TASK-01</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04, D-59</t>
+          <t>P1-02, TASK-04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1359,17 +1491,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무가 있는 프로젝트</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1) 프로젝트 보관 2) 업무 목록·캘린더 확인</t>
+          <t>1) /settings/projects에서 이름 입력·팔레트 색 선택해 프로젝트 추가</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>삭제 버튼 없이 보관만 가능(D-59), 보관 프로젝트의 업무가 목록·캘린더에서 숨겨짐, 되돌리기 토스트</t>
+          <t>목록에 색·이름·업무 수 0 표시, 사이드바 프로젝트 목록에 색 점과 함께 추가</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1380,7 +1512,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P1-02-05</t>
+          <t>P1-02-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1390,12 +1522,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04, D-59</t>
+          <t>P1-02, TASK-04, 2.2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1405,17 +1537,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 태그 2개를 업무 3개에 붙임</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1) 태그 목록의 사용 수 확인 2) 태그 이름 변경 3) 태그 삭제</t>
+          <t>1) 프로젝트 색 팔레트 확인 2) 테마 키 컬러와 비교</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>사용 수 정확, 이름 변경이 업무에 반영, 삭제 시 업무에서 태그 제거(하드 삭제, D-59) + 되돌리기 토스트(되돌리기 방식은 구현 확인)</t>
+          <t>전용 8색, 테마와 무관하게 고정</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1426,17 +1558,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P1-02-06</t>
+          <t>P1-02-03</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>P1-02, SCR-COM-01 ①</t>
+          <t>P1-02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1451,17 +1583,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트 2개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1) 사이드바 프로젝트 클릭</t>
+          <t>1) 이미 있는 이름으로 프로젝트 추가 2) 빈 이름으로 추가</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>/tasks?project=&lt;id&gt;로 이동해 그 프로젝트로 필터, 남은 업무 수 표시</t>
+          <t>칸 아래 오류(서버 errors[] 포함)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1472,17 +1604,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P1-03-01</t>
+          <t>P1-02-04</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01, 02</t>
+          <t>SCR-SET-08, SCR-TASK-01</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-02, TASK-04, D-59</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1497,17 +1629,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무가 있는 프로젝트</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 목록 빠른 입력으로 업무 생성 2) 행 클릭해 상세 패널 열기</t>
+          <t>1) 프로젝트 보관 2) 업무 목록·캘린더 확인</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>목록에 행 추가, 상세 패널(/tasks/:id) 열림, URL 직접 접근·새로고침도 같은 패널</t>
+          <t>삭제 버튼 없이 보관만 가능(D-59), 보관 프로젝트의 업무가 목록·캘린더에서 숨겨짐, 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1518,17 +1650,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P1-03-02</t>
+          <t>P1-02-05</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-02, TASK-04, D-59, UX-03, 태그 삭제 방식(사용자 결정, pm 전달 2026-10-06)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1543,17 +1675,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 태그 2개를 업무 3개에 붙임</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1) 상세에서 제목 바로 편집, 메모 입력 2) 패널 닫고 다시 열기</t>
+          <t>1) 태그 목록의 사용 수 확인 2) 태그 이름 변경 3) 태그 삭제 → 토스트의 되돌리기 4) 다시 삭제 후 토스트가 닫힐 때까지 대기 5) 새로고침</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>저장 버튼 없이 자동 저장, 값 유지</t>
+          <t>사용 수 정확, 이름 변경이 업무에 반영. 삭제는 확인창 없이 목록에서 바로 빠지고 되돌리기 토스트, 되돌리기 시 태그·업무 연결 복원. 토스트가 닫힌 뒤에야 실제 삭제(하드 삭제, D-59) → 새로고침해도 없음, 업무에서도 제거</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1564,17 +1696,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P1-03-03</t>
+          <t>P1-02-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-02</t>
+          <t>P1-02, UX-03, 태그 삭제 방식</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1589,17 +1721,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 태그 1개</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1) 상태 할 일 → 진행 중 → 보류 → 완료로 변경</t>
+          <t>1) 태그 삭제 직후(토스트가 떠 있는 동안) 새로고침 또는 다른 화면으로 이동 2) 다시 확인</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>각 변경 저장, 완료 시 완료 일시 기록·표시, 상태 변경마다 되돌리기 토스트</t>
+          <t>토스트가 닫히기 전 이탈 시 처리(삭제 확정 또는 유지)가 일관됨 — 구현 방침 확인 필요</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1610,17 +1742,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>P1-03-04</t>
+          <t>P1-02-06</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-02, SCR-TASK-01</t>
+          <t>P1-02, SCR-COM-01 ①</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1635,17 +1767,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 프로젝트 2개</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 행의 완료 체크</t>
+          <t>1) 사이드바 프로젝트 클릭</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>완료 처리. 결과 팝오버(SCR-TASK-03)는 P2라 이번에는 없음을 확인</t>
+          <t>/tasks?project=&lt;id&gt;로 이동해 그 프로젝트로 필터, 남은 업무 수 표시</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1656,17 +1788,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P1-03-05</t>
+          <t>P1-03-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-TASK-01, 02</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-03</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1686,12 +1818,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1) 우선순위 높음/보통/낮음 변경 2) 마감일 어제·오늘·다음 주 지정</t>
+          <t>1) 업무 목록 빠른 입력으로 업무 생성 2) 행 클릭해 상세 패널 열기</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>목록 행에 우선순위 표시, 마감 초과는 빨강, 임박 표시</t>
+          <t>목록에 행 추가, 상세 패널(/tasks/:id) 열림, URL 직접 접근·새로고침도 같은 패널</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1702,7 +1834,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>P1-03-06</t>
+          <t>P1-03-02</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1712,7 +1844,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-05</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1732,12 +1864,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1) 진행률 슬라이더를 끌고 키보드 ←→로 조정</t>
+          <t>1) 상세에서 제목 바로 편집, 메모 입력 2) 패널 닫고 다시 열기</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0~100% 10 단위로만 움직임, 목록 행에 진행률 반영</t>
+          <t>저장 버튼 없이 자동 저장, 값 유지</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1748,7 +1880,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>P1-03-07</t>
+          <t>P1-03-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1758,7 +1890,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-04</t>
+          <t>P1-03, TASK-02</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1773,17 +1905,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트·태그 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1) 상세에서 프로젝트 지정, 태그 2개 붙이고 하나 떼기</t>
+          <t>1) 상태 할 일 → 진행 중 → 보류 → 완료로 변경</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>목록 행에 프로젝트 칩·태그 반영</t>
+          <t>각 변경 저장, 완료 시 완료 일시 기록·표시, 상태 변경마다 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1794,17 +1926,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>P1-03-08</t>
+          <t>P1-03-04</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01, 02</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01, UX-03</t>
+          <t>P1-03, TASK-02, SCR-TASK-01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1824,12 +1956,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1) 목록에서 행 선택 후 Delete 키 2) 토스트의 되돌리기 3) 다시 Delete 후 5초 대기</t>
+          <t>1) 목록 행의 완료 체크</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>보관(소프트 삭제) + 되돌리기 토스트, 되돌리기로 복원, 5초 뒤 토스트 사라지고 목록에서 빠짐</t>
+          <t>완료 처리. 결과 팝오버(SCR-TASK-03)는 P2라 이번에는 없음을 확인</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1840,7 +1972,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>P1-03-09</t>
+          <t>P1-03-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1850,7 +1982,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-03, TASK-03</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1865,17 +1997,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 보관된 업무 id</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1) /tasks/&lt;보관된 id&gt; 직접 접속</t>
+          <t>1) 우선순위 높음/보통/낮음 변경 2) 마감일 어제·오늘·다음 주 지정</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>읽기 전용 + 복원 버튼, 복원하면 목록에 다시 나타남</t>
+          <t>목록 행에 우선순위 표시, 마감 초과는 빨강, 임박 표시</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1886,7 +2018,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>P1-03-10</t>
+          <t>P1-03-06</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1896,7 +2028,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>P1-03, D-30, D-58 (409)</t>
+          <t>P1-03, TASK-05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1911,17 +2043,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 업무를 두 탭에서</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1) 탭 A에서 제목 변경 2) 탭 B에서 진행률 변경</t>
+          <t>1) 진행률 슬라이더를 끌고 키보드 ←→로 조정</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>B 패널 상단에 충돌 띠 + [새로 불러오기], 새로 불러오면 A의 변경이 보임</t>
+          <t>0~100% 10 단위로만 움직임, 목록 행에 진행률 반영</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1932,22 +2064,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>P1-03-11</t>
+          <t>P1-03-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>P1-03, D-30</t>
+          <t>P1-03, TASK-04</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1957,17 +2089,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>로그인 상태(qa- 계정), 프로젝트·태그 있음</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1) A의 업무 id로 B가 GET·PATCH·DELETE /api/worklog/tasks/{id}</t>
+          <t>1) 상세에서 프로젝트 지정, 태그 2개 붙이고 하나 떼기</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>404(또는 403). 다른 사용자 업무 조회·수정 불가</t>
+          <t>목록 행에 프로젝트 칩·태그 반영</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1978,22 +2110,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>P1-03-12</t>
+          <t>P1-03-08</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-01, 02</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>P1-03, 화면정의서 2.5</t>
+          <t>P1-03, TASK-01, UX-03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2003,17 +2135,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 0개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1) /tasks 확인</t>
+          <t>1) 목록에서 행 선택 후 Delete 키 2) 토스트의 되돌리기 3) 다시 Delete 후 5초 대기</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>빈 상태: 빠른 입력 문법 안내</t>
+          <t>보관(소프트 삭제) + 되돌리기 토스트, 되돌리기로 복원, 5초 뒤 토스트 사라지고 목록에서 빠짐</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2024,7 +2156,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>P1-03-13</t>
+          <t>P1-03-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2034,12 +2166,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NFR-06</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2049,17 +2181,17 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>로그인 상태(qa- 계정), 보관된 업무 id</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 업무 상세 열기</t>
+          <t>1) /tasks/&lt;보관된 id&gt; 직접 접속</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>전체 화면 패널, 가로 스크롤 없음, 닫기 가능</t>
+          <t>읽기 전용 + 복원 버튼, 복원하면 목록에 다시 나타남</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2070,17 +2202,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>P1-04-01</t>
+          <t>P1-03-10</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>P1-04, TASK-06</t>
+          <t>P1-03, D-30, D-58 (409)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2095,17 +2227,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 10개 이상</t>
+          <t>로그인 상태(qa- 계정), 같은 업무를 두 탭에서</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1) 제목 검색어 입력</t>
+          <t>1) 탭 A에서 제목 변경 2) 탭 B에서 진행률 변경</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>제목에 검색어가 포함된 업무만 표시</t>
+          <t>B 패널 상단에 충돌 띠 + [새로 불러오기], 새로 불러오면 A의 변경이 보임</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2116,22 +2248,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>P1-04-02</t>
+          <t>P1-03-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>P1-04, TASK-06</t>
+          <t>P1-03, D-30</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2141,17 +2273,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1) 상태·프로젝트·태그·마감 기간 필터 칩을 각각, 그리고 함께 적용</t>
+          <t>1) A의 업무 id로 B가 GET·PATCH·DELETE /api/worklog/tasks/{id}</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>조건 교집합만 표시, 칩에 적용 수 표시</t>
+          <t>404(또는 403). 다른 사용자 업무 조회·수정 불가</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2162,7 +2294,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>P1-04-03</t>
+          <t>P1-03-12</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2172,12 +2304,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>P1-04, SCR-TASK-01</t>
+          <t>P1-03, 화면정의서 2.5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2187,17 +2319,17 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무 0개</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1) 필터 적용 후 새로고침 2) 다른 화면 갔다가 뒤로 가기</t>
+          <t>1) /tasks 확인</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>필터가 URL에 남아 그대로 복원</t>
+          <t>빈 상태: 빠른 입력 문법 안내</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2208,22 +2340,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>P1-04-04</t>
+          <t>P1-03-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>P1-04</t>
+          <t>NFR-06</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2233,17 +2365,17 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1) 결과가 없는 조건 적용 2) 필터 지우기</t>
+          <t>1) 모바일에서 업무 상세 열기</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>"조건에 맞는 업무가 없어요" + 필터 지우기, 누르면 전체 목록</t>
+          <t>전체 화면 패널, 가로 스크롤 없음, 닫기 가능</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2254,7 +2386,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>P1-04-05</t>
+          <t>P1-04-01</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2264,7 +2396,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>P1-04, SCR-TASK-01 ④⑥</t>
+          <t>P1-04, TASK-06</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2279,17 +2411,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무 10개 이상</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1) 그룹 기준 마감순/프로젝트/상태 전환 2) 완료 업무 접기 영역 확인</t>
+          <t>1) 제목 검색어 입력</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>그룹이 기준대로 묶임, 완료 업무는 최근 7일만 접힌 영역에</t>
+          <t>제목에 검색어가 포함된 업무만 표시</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2300,17 +2432,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>P1-05-01</t>
+          <t>P1-04-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02</t>
+          <t>P1-04, TASK-06</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2330,12 +2462,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1) 일정 만들기 → 자세히에서 제목·날짜·시작·종료·메모 입력 후 저장 2) 다시 열어 수정 3) 삭제</t>
+          <t>1) 상태·프로젝트·태그·마감 기간 필터 칩을 각각, 그리고 함께 적용</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>생성·수정 반영, 삭제는 확인창 없이 + 되돌리기 토스트</t>
+          <t>조건 교집합만 표시, 칩에 적용 수 표시</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2346,17 +2478,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>P1-05-02</t>
+          <t>P1-04-03</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02</t>
+          <t>P1-04, SCR-TASK-01</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2376,12 +2508,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1) 종일 일정 생성</t>
+          <t>1) 필터 적용 후 새로고침 2) 다른 화면 갔다가 뒤로 가기</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>주·일 보기 종일 행, 월 보기 칩으로 표시</t>
+          <t>필터가 URL에 남아 그대로 복원</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2392,17 +2524,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>P1-05-03</t>
+          <t>P1-04-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02, 2.5</t>
+          <t>P1-04</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2422,12 +2554,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1) 종료를 시작보다 앞으로 지정해 저장</t>
+          <t>1) 결과가 없는 조건 적용 2) 필터 지우기</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>해당 칸 아래 오류(서버 errors[] 포함), 저장 안 됨</t>
+          <t>"조건에 맞는 업무가 없어요" + 필터 지우기, 누르면 전체 목록</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2438,17 +2570,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>P1-05-04</t>
+          <t>P1-04-05</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>P1-05, TIME-06</t>
+          <t>P1-04, SCR-TASK-01 ④⑥</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2468,12 +2600,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 시간에 일정 2개 생성</t>
+          <t>1) 그룹 기준 마감순/프로젝트/상태 전환 2) 완료 업무 접기 영역 확인</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>겹침 경고 없이 생성, 주 보기에서 나란히 배치</t>
+          <t>그룹이 기준대로 묶임, 완료 업무는 최근 7일만 접힌 영역에</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2484,7 +2616,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>P1-05-05</t>
+          <t>P1-05-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2494,7 +2626,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>P1-05, D-30, D-58 (409)</t>
+          <t>P1-05, SCH-02</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2509,17 +2641,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 일정을 두 탭에서</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1) A에서 제목 수정 2) B에서 시간 수정</t>
+          <t>1) 일정 만들기 → 자세히에서 제목·날짜·시작·종료·메모 입력 후 저장 2) 다시 열어 수정 3) 삭제</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>B 모달 상단 충돌 띠 + [새로 불러오기]</t>
+          <t>생성·수정 반영, 삭제는 확인창 없이 + 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2530,7 +2662,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>P1-05-06</t>
+          <t>P1-05-02</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2540,7 +2672,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>P1-05</t>
+          <t>P1-05, SCH-02</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2555,17 +2687,17 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 1개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1) 일정에 업무 연결(검색) 2) 해제 3) 새 업무로 연결</t>
+          <t>1) 종일 일정 생성</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>연결·해제 반영, 일정 프로젝트는 업무를 따름, 업무 상세 연결 일정 목록에도 반영</t>
+          <t>주·일 보기 종일 행, 월 보기 칩으로 표시</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2576,22 +2708,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>P1-05-07</t>
+          <t>P1-05-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>P1-05</t>
+          <t>P1-05, SCH-02, 2.5</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2601,17 +2733,17 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1) A의 일정 id로 B가 조회·수정·삭제</t>
+          <t>1) 종료를 시작보다 앞으로 지정해 저장</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>404(또는 403)</t>
+          <t>해당 칸 아래 오류(서버 errors[] 포함), 저장 안 됨</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2622,7 +2754,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>P1-06-01</t>
+          <t>P1-05-04</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2632,7 +2764,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05, TIME-06</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2652,12 +2784,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1) 매일 반복, 종료 날짜 지정 2) 매월 반복, 종료 없음</t>
+          <t>1) 같은 시간에 일정 2개 생성</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>지정 범위 회차만 표시, 종료 없음은 먼 미래 달에도 표시</t>
+          <t>겹침 경고 없이 생성, 주 보기에서 나란히 배치</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2668,7 +2800,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>P1-06-02</t>
+          <t>P1-05-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2678,7 +2810,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05, D-30, D-58 (409)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2693,17 +2825,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 같은 일정을 두 탭에서</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1) 매주 화·목 반복 생성</t>
+          <t>1) A에서 제목 수정 2) B에서 시간 수정</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>선택한 요일에만 회차 표시</t>
+          <t>B 모달 상단 충돌 띠 + [새로 불러오기]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2714,17 +2846,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>P1-06-03</t>
+          <t>P1-05-06</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03, D-24</t>
+          <t>P1-05</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2739,17 +2871,17 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>로그인 상태(qa- 계정), 업무 1개</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1) 한 회차 제목 수정 → 범위 다이얼로그 확인 2) '이 일정만' 3) 다른 회차 수정 → '모든 일정'</t>
+          <t>1) 일정에 업무 연결(검색) 2) 해제 3) 새 업무로 연결</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>선택지는 '이 일정만 / 모든 일정' 두 개('이후 일정' 없음), 이 일정만은 그 회차만, 모든 일정은 전 회차 변경</t>
+          <t>연결·해제 반영, 일정 프로젝트는 업무를 따름, 업무 상세 연결 일정 목록에도 반영</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2760,22 +2892,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>P1-06-04</t>
+          <t>P1-05-07</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2785,17 +2917,17 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1) 한 회차 삭제 → '이 일정만' 2) 다른 회차 삭제 → '모든 일정'</t>
+          <t>1) A의 일정 id로 B가 조회·수정·삭제</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>해당 회차만 사라짐 / 반복 전체 사라짐, 되돌리기 토스트</t>
+          <t>404(또는 403)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2806,12 +2938,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>P1-06-05</t>
+          <t>P1-06-01</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2831,17 +2963,17 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1) 주 보기에서 한 회차를 끌어 이동</t>
+          <t>1) 매일 반복, 종료 날짜 지정 2) 매월 반복, 종료 없음</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>범위 선택 다이얼로그가 뜨고, 취소하면 원래 자리로 돌아감</t>
+          <t>지정 범위 회차만 표시, 종료 없음은 먼 미래 달에도 표시</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2852,22 +2984,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>P1-06-06</t>
+          <t>P1-06-02</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>P1-06</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2882,12 +3014,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1) 범위 다이얼로그에서 Esc·키보드로 선택</t>
+          <t>1) 매주 화·목 반복 생성</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Esc로 닫힘(변경 없음), 키보드만으로 선택·확인 가능</t>
+          <t>선택한 요일에만 회차 표시</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2898,17 +3030,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>P1-07-01</t>
+          <t>P1-06-03</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-06, SCH-03, D-24</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2923,17 +3055,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1) 사이드바 캘린더 진입 2) 주 보기 구성 확인</t>
+          <t>1) 한 회차 제목 수정 → 범위 다이얼로그 확인 2) '이 일정만' 3) 다른 회차 수정 → '모든 일정'</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>기본 주 보기(/calendar/week/:date), 오늘 열 강조, 기본 08~19시·스크롤로 0~24시, 현재 시각선, 종일 행</t>
+          <t>선택지는 '이 일정만 / 모든 일정' 두 개('이후 일정' 없음), 이 일정만은 그 회차만, 모든 일정은 전 회차 변경</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2944,17 +3076,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>P1-07-02</t>
+          <t>P1-06-04</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01~05</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2969,17 +3101,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1) 보기 전환 버튼으로 일·주·월·연·목록 이동 2) 각 URL로 직접 접속·새로고침</t>
+          <t>1) 한 회차 삭제 → '이 일정만' 2) 다른 회차 삭제 → '모든 일정'</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>각 보기가 정의된 경로로 열리고 새로고침해도 유지</t>
+          <t>해당 회차만 사라짐 / 반복 전체 사라짐, 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2990,17 +3122,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>P1-07-03</t>
+          <t>P1-06-05</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-01, 08</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, UX-09</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3015,17 +3147,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 한글 입력 상태 포함</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1) 그리드에 포커스를 두고 D·W·M·Y·A, T, J/K, C, P 누르기 2) 한글 입력 상태(ㅇ·ㅈ 등)로 같은 키</t>
+          <t>1) 주 보기에서 한 회차를 끌어 이동</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>보기 전환·오늘·이전/다음·만들기·업무 패널이 동작, 한글 상태에서도 동작(event.code)</t>
+          <t>범위 선택 다이얼로그가 뜨고, 취소하면 원래 자리로 돌아감</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3036,22 +3168,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>P1-07-04</t>
+          <t>P1-06-06</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, SCR-SET-02</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>P1-07, UX-09, WCAG 2.1.4, D-60</t>
+          <t>P1-06</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3066,12 +3198,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창에 포커스를 두고 D·W 입력 2) 설정에서 단축키 끄기 후 캘린더에서 D·W</t>
+          <t>1) 범위 다이얼로그에서 Esc·키보드로 선택</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>입력창·모달에서는 글자만 입력되고 보기 안 바뀜, 끄면 단일 문자 단축키 모두 무시. 설정은 다른 브라우저에서 로그인해도 유지(identity 저장, D-60)</t>
+          <t>Esc로 닫힘(변경 없음), 키보드만으로 선택·확인 가능</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3082,17 +3214,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>P1-07-05</t>
+          <t>P1-07-01</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 03</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, D-25</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3112,12 +3244,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1) 공휴일이 있는 주·월로 이동(예: 2026-10-09 한글날)</t>
+          <t>1) 사이드바 캘린더 진입 2) 주 보기 구성 확인</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>요일 머리·날짜가 빨강 + 공휴일 명칭, 주말·공휴일 음영</t>
+          <t>기본 주 보기(/calendar/week/:date), 오늘 열 강조, 기본 08~19시·스크롤로 0~24시, 현재 시각선, 종일 행</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3128,12 +3260,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>P1-07-06</t>
+          <t>P1-07-02</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-01~05</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3153,17 +3285,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트 2개 일정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1) 좌측 프로젝트 필터 토글</t>
+          <t>1) 보기 전환 버튼으로 일·주·월·연·목록 이동 2) 각 URL로 직접 접속·새로고침</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>끈 프로젝트의 일정이 숨겨짐, 다시 켜면 표시</t>
+          <t>각 보기가 정의된 경로로 열리고 새로고침해도 유지</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3174,7 +3306,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>P1-07-07</t>
+          <t>P1-07-03</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3184,7 +3316,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, SCH-01, UX-09</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3199,17 +3331,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 한글 입력 상태 포함</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1) 미니 달력에서 다른 주 날짜 클릭</t>
+          <t>1) 그리드에 포커스를 두고 D·W·M·Y·A, T, J/K, C, P 누르기 2) 한글 입력 상태(ㅇ·ㅈ 등)로 같은 키</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>해당 주로 이동, 미니 달력에 이번 주 강조</t>
+          <t>보기 전환·오늘·이전/다음·만들기·업무 패널이 동작, 한글 상태에서도 동작(event.code)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3220,17 +3352,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>P1-07-08</t>
+          <t>P1-07-04</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 06</t>
+          <t>SCR-CAL-01, SCR-SET-02</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, SCH-04</t>
+          <t>P1-07, UX-09, WCAG 2.1.4, D-60</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3250,12 +3382,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1) 빈 칸 클릭 2) 빈 칸 드래그(10:00~11:45)</t>
+          <t>1) 입력창에 포커스를 두고 D·W 입력 2) 설정에서 단축키 끄기 후 캘린더에서 D·W</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>클릭은 1시간, 드래그는 15분 단위로 맞춘 범위의 빠른 생성 팝오버</t>
+          <t>입력창·모달에서는 글자만 입력되고 보기 안 바뀜, 끄면 단일 문자 단축키 모두 무시. 설정은 다른 브라우저에서 로그인해도 유지(identity 저장, D-60)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3266,17 +3398,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>P1-07-09</t>
+          <t>P1-07-05</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-01, 03</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-04, UX-03</t>
+          <t>P1-07, SCH-01, D-25</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3291,17 +3423,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 일정 1개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1) 블록을 다른 시간·요일로 끌기 2) 아래 끝을 끌어 길이 조절 3) 되돌리기</t>
+          <t>1) 공휴일이 있는 주·월로 이동(예: 2026-10-09 한글날)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15분 단위로 이동·조절, 되돌리기 토스트로 원복</t>
+          <t>요일 머리·날짜가 빨강 + 공휴일 명칭, 주말·공휴일 음영</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3312,12 +3444,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>P1-07-10</t>
+          <t>P1-07-06</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-02</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3337,17 +3469,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 시간 없는 기록이 있는 날(P2 전이면 생략)</t>
+          <t>로그인 상태(qa- 계정), 프로젝트 2개 일정</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1) 일 보기 구성 확인</t>
+          <t>1) 좌측 프로젝트 필터 토글</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>하루 그리드, 우측 '이날의 기록' 패널</t>
+          <t>끈 프로젝트의 일정이 숨겨짐, 다시 켜면 표시</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3358,12 +3490,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>P1-07-11</t>
+          <t>P1-07-07</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-03</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3383,17 +3515,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 하루에 일정 5개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1) 월 보기 확인 2) +n개 더보기 3) 날짜 숫자 클릭 4) 빈 칸 클릭 5) 칩을 다른 날로 끌기</t>
+          <t>1) 미니 달력에서 다른 주 날짜 클릭</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>6주×7일, 칩 최대 3개 + '+2개 더보기' 팝오버, 숫자 → 일 보기, 빈 칸 → 종일 빠른 생성, 칩 이동</t>
+          <t>해당 주로 이동, 미니 달력에 이번 주 강조</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3404,17 +3536,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>P1-07-12</t>
+          <t>P1-07-08</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-04</t>
+          <t>SCR-CAL-01, 06</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, SCH-01, SCH-04</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3434,12 +3566,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1) 연 보기 확인 2) 날짜 클릭 3) 월 이름 클릭 4) 390px</t>
+          <t>1) 빈 칸 클릭 2) 빈 칸 드래그(10:00~11:45)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>12개월(데스크톱 4×3, 모바일 1열), 일정 밀도 점 3단계, 날짜 → 일 보기, 월 이름 → 월 보기</t>
+          <t>클릭은 1시간, 드래그는 15분 단위로 맞춘 범위의 빠른 생성 팝오버</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3450,17 +3582,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>P1-07-13</t>
+          <t>P1-07-09</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-05</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, SCH-04, UX-03</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3475,17 +3607,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 반복 일정 포함</t>
+          <t>로그인 상태(qa- 계정), 일정 1개</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 보기 확인 2) 아래로 스크롤 3) 지난 일정 보기</t>
+          <t>1) 블록을 다른 시간·요일로 끌기 2) 아래 끝을 끌어 길이 조절 3) 되돌리기</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>오늘부터 날짜별 그룹, 반복 아이콘, 무한 스크롤로 다음 일정 로드, 지난 일정 표시</t>
+          <t>15분 단위로 이동·조절, 되돌리기 토스트로 원복</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3496,22 +3628,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>P1-07-14</t>
+          <t>P1-07-10</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-05</t>
+          <t>SCR-CAL-02</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>P1-07</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3521,17 +3653,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>일정 없는 새 계정</t>
+          <t>로그인 상태(qa- 계정), 시간 없는 기록이 있는 날(P2 전이면 생략)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 보기</t>
+          <t>1) 일 보기 구성 확인</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>"다가오는 일정이 없어요"</t>
+          <t>하루 그리드, 우측 '이날의 기록' 패널</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3542,22 +3674,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>P1-07-15</t>
+          <t>P1-07-11</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01~05</t>
+          <t>SCR-CAL-03</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, 2.4</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3567,17 +3699,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px·800px</t>
+          <t>로그인 상태(qa- 계정), 하루에 일정 5개</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 캘린더 진입 2) 태블릿 폭</t>
+          <t>1) 월 보기 확인 2) +n개 더보기 3) 날짜 숫자 클릭 4) 빈 칸 클릭 5) 칩을 다른 날로 끌기</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>모바일 기본 보기는 일 보기, 가로 스크롤 없음. 태블릿은 업무 패널 접힘</t>
+          <t>6주×7일, 칩 최대 3개 + '+2개 더보기' 팝오버, 숫자 → 일 보기, 빈 칸 → 종일 빠른 생성, 칩 이동</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3588,17 +3720,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>P1-07-16</t>
+          <t>P1-07-12</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-04</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>P1-07, D-37</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3618,12 +3750,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1) 연말·연초(12월 마지막 주) 주 보기</t>
+          <t>1) 연 보기 확인 2) 날짜 클릭 3) 월 이름 클릭 4) 390px</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>연도가 바뀌는 주가 끊기지 않고 표시, 1/1 공휴일 표시</t>
+          <t>12개월(데스크톱 4×3, 모바일 1열), 일정 밀도 점 3단계, 날짜 → 일 보기, 월 이름 → 월 보기</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3634,17 +3766,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>P1-08-01</t>
+          <t>P1-07-13</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-05</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCH-07</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3659,17 +3791,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 일정 없는 업무(마감 초과·날짜 없음 포함)</t>
+          <t>로그인 상태(qa- 계정), 반복 일정 포함</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1) 캘린더 업무 패널 확인</t>
+          <t>1) 목록 보기 확인 2) 아래로 스크롤 3) 지난 일정 보기</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>기본 열림, 마감순, 마감 초과 강조, 프로젝트 칩·마감 표시, 날짜 없는 업무 접힘</t>
+          <t>오늘부터 날짜별 그룹, 반복 아이콘, 무한 스크롤로 다음 일정 로드, 지난 일정 표시</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3680,22 +3812,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>P1-08-02</t>
+          <t>P1-07-14</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09, 01</t>
+          <t>SCR-CAL-05</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCH-04, SCH-07</t>
+          <t>P1-07</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3705,17 +3837,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>일정 없는 새 계정</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1) 패널 카드를 그리드 10:15 칸으로 끌기</t>
+          <t>1) 목록 보기</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>10:15~11:15 일정 생성(15분 단위), 업무와 연결, 패널에서 빠짐</t>
+          <t>"다가오는 일정이 없어요"</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3726,22 +3858,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>P1-08-03</t>
+          <t>P1-07-15</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-01~05</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>P1-08</t>
+          <t>NFR-06, 2.4</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3751,17 +3883,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 모든 업무가 배치됨</t>
+          <t>로그인 상태(qa- 계정), 390px·800px</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1) 패널 확인</t>
+          <t>1) 모바일에서 캘린더 진입 2) 태블릿 폭</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>"배치할 업무가 없어요"</t>
+          <t>모바일 기본 보기는 일 보기, 가로 스크롤 없음. 태블릿은 업무 패널 접힘</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3772,17 +3904,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>P1-08-04</t>
+          <t>P1-07-16</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>P1-08, UX-09</t>
+          <t>P1-07, D-37</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3802,12 +3934,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1) P 키로 패널 닫기·열기 2) 패널 안 빠른 입력으로 업무 추가</t>
+          <t>1) 연말·연초(12월 마지막 주) 주 보기</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>토글 동작, 추가한 업무가 패널에 나타남</t>
+          <t>연도가 바뀌는 주가 끊기지 않고 표시, 1/1 공휴일 표시</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3818,17 +3950,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>P1-08-05</t>
+          <t>P1-08-01</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCR-HOME-01 ④</t>
+          <t>P1-08, SCH-07</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3843,17 +3975,17 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 일정 없는 업무(마감 초과·날짜 없음 포함)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1) 홈 남은 업무를 일정 영역으로 끌기</t>
+          <t>1) 캘린더 업무 패널 확인</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>P1 범위 확인: 오늘 일정 영역(③)은 P2라 이번에는 대상 없음 → N/A 예상</t>
+          <t>기본 열림, 마감순, 마감 초과 강조, 프로젝트 칩·마감 표시, 날짜 없는 업무 접힘</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3864,17 +3996,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>P1-09-01</t>
+          <t>P1-08-02</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09, 01</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-08, SCH-04, SCH-07</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3894,49 +4026,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1) '14-16 견적서 작성 #영업 !높음 ~금' 입력</t>
+          <t>1) 패널 카드를 그리드 10:15 칸으로 끌기</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>칩: 시간 14:00~16:00 · 날짜(오늘) · #영업 · !높음 · ~이번 주 금요일 실제 날짜, 종류별 색, 제목 '견적서 작성'</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 해석은 맞음: 칩 '오늘 14:00–16:00' · '#영업' · '우선순위 높음' · '마감 10/9(금)', 제목 '견적서 작성', 안내 '일정과 업무가 함께 만들어져요'. 그러나 마감 칩 class에 'undefined'가 들어가고 전용 색이 없어 '우선순위 낮음·보통' 칩과 같은 회색(#EEF0F6)으로 보임 → 종류별 색 구분이 안 됨</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-09-01.png</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>원인 추정: QuickInput.module.css에 .due 규칙이 없고 .priority는 strong일 때만 색이 있음. 목업 색 기준은 erp-design 확인 필요</t>
-        </is>
-      </c>
+          <t>10:15~11:15 일정 생성(15분 단위), 업무와 연결, 패널에서 빠짐</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>P1-09-02</t>
+          <t>P1-08-03</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04</t>
+          <t>P1-08</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3951,50 +4067,38 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 모든 업무가 배치됨</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
+          <t>1) 패널 확인</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>"배치할 업무가 없어요"</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>Enter 저장: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>P1-09-03</t>
+          <t>P1-08-04</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-08, UX-09</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4014,45 +4118,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
+          <t>1) P 키로 패널 닫기·열기 2) 패널 안 빠른 입력으로 업무 추가</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>토글 동작, 추가한 업무가 패널에 나타남</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
-        </is>
-      </c>
+      <c r="L76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>P1-09-04</t>
+          <t>P1-08-05</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>P1-09</t>
+          <t>P1-08, SCR-HOME-01 ④</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4072,35 +4164,23 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 프로젝트 '#신규' 입력</t>
+          <t>1) 홈 남은 업무를 일정 영역으로 끌기</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>P1 범위 확인: 오늘 일정 영역(③)은 P2라 이번에는 대상 없음 → N/A 예상</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>새 프로젝트 칩: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>P1-09-05</t>
+          <t>P1-09-01</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4110,7 +4190,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>P1-09</t>
+          <t>P1-09, REC-04, D-62, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4130,20 +4210,20 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '#영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
+          <t>1) '14-16 견적서 작성 @영업 #긴급 !높음 ~금' 입력</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
+          <t>칩: 시간(오늘 14:00–16:00) · 프로젝트 @영업 · 태그 #긴급 · 우선순위 높음 · 마감 이번 주 금요일 실제 날짜, 종류별 색 구분, 제목 '견적서 작성'</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] Esc → 입력 비움·미리보기 사라짐. 빈 입력·공백만 Enter → 아무 반응 없음(토스트·오류 없음). '#영업 !높음'·'~금' → 칩은 보이고 '할 일 이름을 적어 주세요' 안내</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] [재검증, a82f5d8 수정] 칩 class에 undefined 없음. 시간=accent(#E9E8FA/#3C32AB), 프로젝트=노랑(#FFF0C7), 우선순위 높음=빨강 계열(#FDE2DD/#A02613), 우선순위 보통·낮음과 마감=의도된 회색(#EEF0F6)</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4151,14 +4231,14 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>pm 전달 기준(완전히 빈 입력은 조용히 무시, 제목만 비면 안내)으로 기대 결과를 고치고 칩 수정 드롭다운은 P1-09-12로 분리</t>
+          <t>[최초 2026-10-06 FAIL: 마감 칩 class 'undefined', 증거 evidence/P1/P1-09-01.png] 회색 칩은 pm 전달 기준(의도된 회색)으로 판정. 기호 변경 전 코드(#=프로젝트)로 확인. #태그·@프로젝트 기대 결과는 frontend 다음 커밋 후 재실행</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>P1-09-12</t>
+          <t>P1-09-02</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4168,7 +4248,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCR-COM-02 주요 동작</t>
+          <t>P1-09, REC-04</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4188,12 +4268,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1) 해석 칩 클릭</t>
+          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>그 값만 바꾸는 드롭다운</t>
+          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4209,14 +4289,14 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
+          <t>Enter 저장: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>P1-09-06</t>
+          <t>P1-09-03</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4246,20 +4326,20 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
+          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
+          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4267,14 +4347,14 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
+          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>P1-09-07</t>
+          <t>P1-09-04</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4284,7 +4364,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>UX-09</t>
+          <t>P1-09, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4304,31 +4384,35 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
+          <t>1) 없는 프로젝트 '@신규' 입력</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
+          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>새 프로젝트 칩: API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>P1-09-11</t>
+          <t>P1-09-13</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4338,7 +4422,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>P1-09, UX-09</t>
+          <t>P1-09, TASK-04, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4348,7 +4432,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4358,45 +4442,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
+          <t>1) '보고서 #긴급 #검토' 입력 2) 없는 태그 '#새태그' 입력 3) Enter 저장 후 업무 상세 확인</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>태그 칩 2개(#긴급·#검토), 프로젝트 칩과 다른 색. 저장하면 업무에 태그 2개 연결(여러 개 허용 — 구현 범위 확인), 없는 태그 처리 방식은 구현 확인</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
-        </is>
-      </c>
+      <c r="L82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>P1-09-08</t>
+          <t>P1-09-05</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SCR-ONB-02</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04</t>
+          <t>P1-09</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4416,49 +4488,45 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
+          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '@영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>문법 표(시간·#·!·~·상대 날짜)와 예시 3개, 예시 클릭 시 입력창에 채워짐</t>
+          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] ? 버튼 → 문법 도움말 팝오버(aria-expanded=true, 팝오버로 포커스 이동), 문법 표 5줄과 예시 3개, 예시 클릭 시 입력창 채움·포커스, 바깥 클릭·Esc로 닫힘. 그러나 Esc로 닫으면 포커스가 ? 버튼으로 돌아가지 않고 사라짐(document.activeElement=BODY). 이어서 Tab을 누르면 홈 예시 버튼으로 가 키보드 사용자가 위치를 잃음</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] Esc → 입력 비움·미리보기 사라짐. 빈 입력·공백만 Enter → 아무 반응 없음(토스트·오류 없음). '#영업 !높음'·'~금' → 칩은 보이고 '할 일 이름을 적어 주세요' 안내</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-09-08.png</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>화면정의서 2.5 '키보드만으로 모든 동작 가능'. 문법 표의 '오늘 · 내일 · 다음주 수요일 → 날짜'는 개정대기에 '날짜(시간 없이 쓰면 마감일)'로 바꾸기로 되어 있음(frontend 변경 대기)</t>
+          <t>[기호 변경(# 태그·@ 프로젝트) 전 실행 결과 — frontend 수정 후 재실행 예정] pm 전달 기준(완전히 빈 입력은 조용히 무시, 제목만 비면 안내)으로 기대 결과를 고치고 칩 수정 드롭다운은 P1-09-12로 분리</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>P1-09-09</t>
+          <t>P1-09-12</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-06</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCH-02</t>
+          <t>P1-09, SCR-COM-02 주요 동작</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4473,17 +4541,17 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 #영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
+          <t>1) 해석 칩 클릭</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 토글 기본 켜짐(끄면 일정만), Esc는 임시 블록 제거</t>
+          <t>그 값만 바꾸는 드롭다운</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4499,14 +4567,14 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
+          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>P1-09-10</t>
+          <t>P1-09-06</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4516,7 +4584,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>P1-09, REC-04, D-62</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4531,50 +4599,50 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 포커스</t>
+          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 상위 3개 제안</t>
+          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
+          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>P1-10-01</t>
+          <t>P1-09-07</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>UX-09</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4594,45 +4662,41 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
+          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
+          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎)</t>
-        </is>
-      </c>
+      <c r="L86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>P1-10-02</t>
+          <t>P1-09-11</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-09, UX-09</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4642,7 +4706,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4652,45 +4716,45 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
+          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
+          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
+          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>P1-10-08</t>
+          <t>P1-09-08</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-ONB-02</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01, SCR-COM-03 ②</t>
+          <t>P1-09, REC-04, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4705,50 +4769,50 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 제목 일부·일지 내용 입력</t>
+          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>업무 검색·일지 검색 결과 그룹</t>
+          <t>문법 표(시간·@프로젝트·#태그·!우선순위·~마감·날짜(시간 없이 쓰면 마감일))와 예시 3개(새 기호), 예시 클릭 시 입력창에 채워짐, Esc로 닫으면 ? 버튼으로 포커스 복귀</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] [재검증, a82f5d8 수정] 도움말을 Esc로 닫으면 포커스가 ? 버튼(문법 도움말)으로 돌아옴, 다음 Tab도 정상. 문법 표에 '날짜 (시간 없이 쓰면 마감일)' 반영</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
+          <t>[최초 2026-10-06 FAIL: Esc 후 포커스 BODY, 증거 evidence/P1/P1-09-08.png] 문법 표·예시는 아직 #=프로젝트. 기호 변경 전 코드(#=프로젝트)로 확인. #태그·@프로젝트 기대 결과는 frontend 다음 커밋 후 재실행</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>P1-10-03</t>
+          <t>P1-09-09</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-CAL-06</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-09, SCH-02</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4763,50 +4827,50 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
+          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 @영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
+          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 토글 기본 켜짐(끄면 일정만), Esc는 임시 블록 제거</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
+          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>P1-10-04</t>
+          <t>P1-09-10</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4821,17 +4885,17 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
+          <t>1) 빠른 입력 포커스</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
+          <t>자주 하는 업무 상위 3개 제안</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4847,24 +4911,24 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>P1-10-09</t>
+          <t>P1-10-01</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03, UX-09</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4884,46 +4948,50 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
+          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
+          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎) / [재검증 a5bb168] vite dev에서도 입력창 Ctrl+K → 팔레트 검색 입력에 포커스, Esc로 닫히고 빠른 입력창 값 유지(관찰 ① 해소)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>P1-10-05</t>
+          <t>P1-10-02</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4933,50 +5001,50 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 업무 보관</t>
+          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>토스트가 하단 탭 위에 표시</t>
+          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
+          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>P1-10-06</t>
+          <t>P1-10-08</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-04</t>
+          <t>P1-10, UX-01, SCR-COM-03 ②</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4991,40 +5059,40 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 계정</t>
+          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 직후 첫 화면</t>
+          <t>1) 업무 제목 일부·일지 내용 입력</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
+          <t>업무 검색·일지 검색 결과 그룹</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 데모 계정 첫 화면: 날짜·인사·빠른 기록 입력창, '오늘 할 일을 한 줄로 적어 보세요' + 안내 + 예시 3개(클릭 시 입력창 채움·포커스). 390px에서 가로 스크롤 없음, 예시 버튼 높이 44px</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>'데이터 없음' 판정은 업무 API 이후. 지금은 항상 빈 상태를 보여 줌(P1-11에서 확인)</t>
+          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>P1-10-07</t>
+          <t>P1-10-03</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5034,12 +5102,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>UX-09, 2.5</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5054,20 +5122,20 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
+          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5075,24 +5143,24 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고)</t>
+          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>P1-11-01</t>
+          <t>P1-10-04</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5107,38 +5175,50 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 직후 홈 확인</t>
+          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
+          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>P1-11-02</t>
+          <t>P1-10-09</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-03, UX-09</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5158,38 +5238,46 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
+          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
+          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>P1-11-03</t>
+          <t>P1-10-05</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5199,28 +5287,40 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
+          <t>1) 모바일에서 업무 보관</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
+          <t>토스트가 하단 탭 위에 표시</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>P1-11-04</t>
+          <t>P1-10-06</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5230,7 +5330,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05, D-25</t>
+          <t>P1-10, UX-04</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5245,43 +5345,55 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
+          <t>막 가입한 계정</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1) 다가오는 일정 영역</t>
+          <t>1) 가입 직후 첫 화면</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 데모 계정 첫 화면: 날짜·인사·빠른 기록 입력창, '오늘 할 일을 한 줄로 적어 보세요' + 안내 + 예시 3개(클릭 시 입력창 채움·포커스). 390px에서 가로 스크롤 없음, 예시 버튼 높이 44px</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>'데이터 없음' 판정은 업무 API 이후. 지금은 항상 빈 상태를 보여 줌(P1-11에서 확인)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>P1-11-05</t>
+          <t>P1-10-07</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>UX-09, 2.5</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5296,23 +5408,35 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1) 홈 빠른 입력으로 업무 추가</t>
+          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
+          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고) / [재검증 a5bb168] dev 모드에서도 같은 결과</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>P1-11-06</t>
+          <t>P1-11-01</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5322,12 +5446,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, 2.4</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5337,17 +5461,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
+          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1) 폭별 카드 배치</t>
+          <t>1) 로그인 직후 홈 확인</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
+          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -5358,7 +5482,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>P1-11-07</t>
+          <t>P1-11-02</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5368,12 +5492,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2.5 (로딩)</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5388,12 +5512,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1) 느린 네트워크로 홈 진입</t>
+          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
+          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5404,17 +5528,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>P1-12-01</t>
+          <t>P1-11-03</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5429,17 +5553,17 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 미인증 계정</t>
+          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
+          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
+          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5450,17 +5574,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02</t>
+          <t>P1-11-04</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-01</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08, D-41, D-53</t>
+          <t>P1-11, SCH-05, D-25</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -5470,22 +5594,22 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 qa- 주소(사용자 승인)</t>
+          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
+          <t>1) 다가오는 일정 영역</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
+          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -5496,42 +5620,42 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>P1-12-03</t>
+          <t>P1-11-05</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-01</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>P1-12, D-57</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02 메일</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
+          <t>1) 홈 빠른 입력으로 업무 추가</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
+          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5542,42 +5666,42 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>P1-12-04</t>
+          <t>P1-11-06</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>NFR-06, 2.4</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
+          <t>1) 폭별 카드 배치</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
+          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -5588,42 +5712,42 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>P1-12-05</t>
+          <t>P1-11-07</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>2.5 (로딩)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번 입력</t>
+          <t>1) 느린 네트워크로 홈 진입</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
+          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5634,12 +5758,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>P1-12-06</t>
+          <t>P1-12-01</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5654,22 +5778,22 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
+          <t>막 가입한 미인증 계정</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 발급 후 10분 경과</t>
+          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
+          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5680,17 +5804,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>P1-12-07</t>
+          <t>P1-12-02</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-MAIL-01</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-12, AUTH-08, D-41, D-53</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5705,17 +5829,17 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>수신 가능한 qa- 주소(사용자 승인)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 다시 받기 직후 다시 누르기</t>
+          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
+          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5726,42 +5850,42 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>P1-12-08</t>
+          <t>P1-12-03</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-MAIL-01</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-12, D-57</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>로컬(실제 메일 10통 발송 회피)</t>
+          <t>P1-12-02 메일</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1) 하루 11번째 발송 요청</t>
+          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>"내일 다시 시도" 안내, 서버 거부</t>
+          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5772,7 +5896,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>P1-12-09</t>
+          <t>P1-12-04</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5782,7 +5906,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>P1-12</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5797,17 +5921,17 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>코드 2번 발급</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1) 먼저 받은 코드로 인증</t>
+          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>이전 코드 무효(새 코드만 유효) — 구현 방침 확인 필요</t>
+          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5818,12 +5942,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>P1-12-10</t>
+          <t>P1-12-05</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5833,27 +5957,27 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
+          <t>1) 틀린 코드 5번 입력</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>거부(코드는 계정별), 비로그인 401</t>
+          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5864,17 +5988,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>P1-12-11</t>
+          <t>P1-12-06</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>P1-12</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5884,22 +6008,22 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>인증 완료 계정</t>
+          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입</t>
+          <t>1) 코드 발급 후 10분 경과</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>배너 표시 안 됨</t>
+          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -5910,17 +6034,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>P1-13-01</t>
+          <t>P1-12-07</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>P1-13, SCR-AUTH-02 ④</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5930,22 +6054,22 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
+          <t>1) 코드 다시 받기 직후 다시 누르기</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>/password/forgot 이동</t>
+          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -5956,42 +6080,42 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>P1-13-02</t>
+          <t>P1-12-08</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>로컬(실제 메일 10통 발송 회피)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
+          <t>1) 가입 직후 자동 발송 1통 포함, 24시간 안에 11번째 발송 요청 2) 첫 발송 24시간 뒤 다시 요청</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동, 응답 코드·본문 동일(계정 존재 비노출)</t>
+          <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -6002,17 +6126,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>P1-13-03</t>
+          <t>P1-12-09</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, D-64</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6022,22 +6146,22 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>코드 2번 발급</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1) 빈 값·형식 오류 이메일 제출</t>
+          <t>1) 먼저 받은 코드로 인증</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
+          <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -6048,42 +6172,42 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>P1-13-04</t>
+          <t>P1-12-10</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-02</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-41</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 계정</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1) 재설정 메일 확인</t>
+          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
+          <t>거부(코드는 계정별), 비로그인 401</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6094,42 +6218,42 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>P1-13-05</t>
+          <t>P1-12-12</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, P1-13, D-65</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>로컬(운영 IP 제한 회피), 계정 여러 개</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
+          <t>1) 같은 IP에서 인증 코드·재설정 코드 메일을 합쳐 1시간에 11번 요청 2) X-Client-Ip 헤더 없이 요청</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
+          <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6140,17 +6264,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>P1-13-06</t>
+          <t>P1-12-11</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-38</t>
+          <t>P1-12</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6160,22 +6284,22 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>코드 확인됨</t>
+          <t>인증 완료 계정</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
+          <t>1) 앱 화면 진입</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
+          <t>배너 표시 안 됨</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -6186,17 +6310,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>P1-13-07</t>
+          <t>P1-13-01</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, AUTH-08</t>
+          <t>P1-13, SCR-AUTH-02 ④</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6206,22 +6330,22 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
+          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음)</t>
+          <t>/password/forgot 이동</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -6232,42 +6356,42 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>P1-13-08</t>
+          <t>P1-13-02</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-13, AUTH-03, D-65</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번</t>
+          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
+          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -6278,7 +6402,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>P1-13-09</t>
+          <t>P1-13-03</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6298,22 +6422,22 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
+          <t>1) 빈 값·형식 오류 이메일 제출</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
+          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -6324,17 +6448,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>P1-13-10</t>
+          <t>P1-13-04</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02, 04</t>
+          <t>SCR-MAIL-02</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>P1-13, P1-14</t>
+          <t>P1-13, AUTH-03, D-41</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -6344,22 +6468,22 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>잠긴 계정</t>
+          <t>수신 가능한 계정</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 안내의 재설정 링크</t>
+          <t>1) 재설정 메일 확인</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>/password/forgot 이동</t>
+          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -6370,42 +6494,42 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>P1-13-11</t>
+          <t>P1-13-05</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04, 05</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, NFR-13</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>비로그인, 390px, 오프라인 전환</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
+          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
+          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6416,17 +6540,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>P1-14-01</t>
+          <t>P1-13-06</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, AUTH-03, D-38</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6436,22 +6560,22 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>qa- 계정</t>
+          <t>코드 확인됨</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
+          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
+          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -6462,17 +6586,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>P1-14-02</t>
+          <t>P1-13-07</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, AUTH-03, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -6482,22 +6606,22 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>qa- 계정</t>
+          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
+          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
+          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -6508,17 +6632,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>P1-14-03</t>
+          <t>P1-13-12</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-02, 05</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, P1-14, D-64</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -6533,17 +6657,17 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
+          <t>로컬, 10회 실패로 잠긴 계정</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 해제 시점 이후 로그인</t>
+          <t>1) 잠긴 상태에서 비밀번호 재설정 완료 2) 곧바로 새 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
+          <t>잠금이 풀려 바로 로그인 성공</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -6554,42 +6678,42 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>P1-14-04</t>
+          <t>P1-13-08</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>P1-14, D-61</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>없는 이메일</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 이메일로 10회 이상 실패</t>
+          <t>1) 틀린 코드 5번</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
+          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -6600,22 +6724,22 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>P1-14-05</t>
+          <t>P1-13-09</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09, D-61</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6625,17 +6749,17 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>로컬(운영 IP 차단 위험 회피)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
+          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
+          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -6646,22 +6770,22 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>P1-14-06</t>
+          <t>P1-13-10</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-02, 04</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>P1-14, p1-14-springdoc-429</t>
+          <t>P1-13, P1-14</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6669,15 +6793,19 @@
           <t>운영</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>잠긴 계정</t>
+        </is>
+      </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
+          <t>1) 잠금 안내의 재설정 링크</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
+          <t>/password/forgot 이동</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6688,22 +6816,22 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>P1-X-01</t>
+          <t>P1-13-11</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-AUTH-04, 05</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01 (P1 완성)</t>
+          <t>NFR-06, NFR-13</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6713,17 +6841,17 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>비로그인, 390px, 오프라인 전환</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
+          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
+          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -6734,22 +6862,22 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>P1-X-02</t>
+          <t>P1-14-01</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6759,17 +6887,17 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>qa- 계정</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>1) 화면 전환 중 표시</t>
+          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
+          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -6780,17 +6908,17 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>P1-X-03</t>
+          <t>P1-14-02</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ④</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>NFR-13 (P0 TC-81 재확인)</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -6805,17 +6933,17 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>qa- 계정</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
+          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
+          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6826,17 +6954,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>P1-X-04</t>
+          <t>P1-14-03</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ③</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>NFR-13</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -6846,22 +6974,22 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
+          <t>1) 잠금 해제 시점 이후 로그인</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
+          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6872,17 +7000,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>P1-X-05</t>
+          <t>P1-14-04</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>NFR-02, NFR-14</t>
+          <t>P1-14, D-61</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -6897,17 +7025,17 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>없는 이메일</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
+          <t>1) 없는 이메일로 10회 이상 실패</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>모두 403 ORIGIN_REJECTED</t>
+          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -6918,7 +7046,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>P1-X-06</t>
+          <t>P1-14-05</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6928,32 +7056,32 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>D-30</t>
+          <t>P1-14, AUTH-09, D-61</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>로컬(운영 IP 차단 위험 회피)</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
+          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
+          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
@@ -6964,17 +7092,17 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>P1-X-07</t>
+          <t>P1-14-06</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>—(배포)</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>D-56</t>
+          <t>P1-14, p1-14-springdoc-429</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6987,19 +7115,15 @@
           <t>운영</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>배포 브랜치 main 전환 후</t>
-        </is>
-      </c>
+      <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
+          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
+          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -7010,22 +7134,22 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>P1-X-08</t>
+          <t>P1-X-01</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>—(배포)</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>P0-09</t>
+          <t>SCR-COM-01 (P1 완성)</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7035,17 +7159,17 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
+          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
+          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -7056,17 +7180,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>P1-X-09</t>
+          <t>P1-X-02</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>2.6 문구 말투, D-36</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -7086,12 +7210,12 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면 문구 말투 확인</t>
+          <t>1) 화면 전환 중 표시</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
+          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -7102,22 +7226,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>P1-X-10</t>
+          <t>P1-X-03</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SCR-SYS-02 ④</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>화면정의서 2.5 (키보드·터치)</t>
+          <t>NFR-13 (P0 TC-81 재확인)</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7132,12 +7256,12 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -7145,10 +7269,332 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-04</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SCR-SYS-02 ③</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>NFR-13</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-05</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>—(API)</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>NFR-02, NFR-14</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>모두 403 ORIGIN_REJECTED</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-06</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>—(API)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-07</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>—(배포)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>D-56</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>배포 브랜치 main 전환 후</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-08</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>—(배포)</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>P0-09</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>브라우저</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-09</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>2.6 문구 말투, D-36</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 새 화면 문구 말투 확인</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-10</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>화면정의서 2.5 (키보드·터치)</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L139"/>
+  <autoFilter ref="A1:L146"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7587,7 +8033,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1-09·10)</t>
+          <t>2026-10-06 (P1-09·10, P1-01, 재검증)</t>
         </is>
       </c>
     </row>
@@ -7611,7 +8057,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -7623,7 +8069,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>기능 111, 사용성 15, 보안 8, 배포 4</t>
+          <t>기능 117, 사용성 15, 보안 9, 배포 4</t>
         </is>
       </c>
     </row>
@@ -7635,7 +8081,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>미실행 117, FAIL 2, BLOCKED 9, PASS 10</t>
+          <t>미실행 111, PASS 21, BLOCKED 12, FAIL 1</t>
         </is>
       </c>
     </row>
@@ -7647,7 +8093,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>P1-09-01 마감 칩 색 구분 없음(class undefined), P1-09-08 도움말 Esc 후 포커스 유실</t>
+          <t>P1-01-11 단축키를 꺼도 빠른 입력창 N 안내 표시 (P1-09-01·08은 재검증 PASS)</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1340,20 +1340,20 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 끄면 즉시 저장(version 증가), N은 홈·설정 어디서도 미동작, Ctrl+K 팔레트는 열리고 팔레트의 '업무 추가' 옆 N 표시는 사라짐. 그러나 빠른 입력창 오른쪽의 'N' 안내(kbd)는 그대로 보여, 눌러도 동작하지 않는 단축키를 안내함. 다시 켜면 N 동작</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-01-11.png</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [재검증, 4e8e0d2] 단축키를 끄면 빠른 입력창의 N 안내가 사라짐(kbd 없음), N 미동작. 다시 켜면 N 안내·동작 복귀</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>[이전 FAIL 증거 evidence/P1/P1-01-11.png]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1466,22 +1466,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>P1-02-01</t>
+          <t>P1-01-14</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08</t>
+          <t>SCR-SET-02</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04</t>
+          <t>P1-01, 화면정의서 2.5(터치 44px), 개정대기 SET-02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1496,38 +1496,50 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1) /settings/projects에서 이름 입력·팔레트 색 선택해 프로젝트 추가</t>
+          <t>1) 키보드 단축키 스위치·업무 요일 버튼 크기 측정 2) 행 제목 '키보드 단축키' 클릭</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>목록에 색·이름·업무 수 0 표시, 사이드바 프로젝트 목록에 색 점과 함께 추가</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>스위치 누르는 영역 높이 44px 이상, 요일 버튼 44x44, 행 제목을 눌러도 켜짐/꺼짐</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] [재검증 e39aa14] 단축키 스위치 56x44, 업무 요일 버튼 44x44, 행 제목 '키보드 단축키' 클릭으로 켜짐/꺼짐(저장 version 증가)</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>[관찰 2026-10-06: 스위치 56x32]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P1-02-02</t>
+          <t>P1-01-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08</t>
+          <t>SCR-SET-02</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04, 2.2</t>
+          <t>P1-01, D-40, 개정대기 SET-02</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1542,38 +1554,50 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1) 프로젝트 색 팔레트 확인 2) 테마 키 컬러와 비교</t>
+          <t>1) 일반 탭 처음 열기 2) 시간대 변경 3) 다른 설정 탭 갔다 오기</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>전용 8색, 테마와 무관하게 고정</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+          <t>안내 '시간대를 바꿔도 기존 기록의 날짜는 그대로예요…'는 바꾼 뒤에만 시간대 행 아래 표시, 화면을 떠나면 사라짐</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] [재검증 e39aa14] 처음 열면 안내 없음, 시간대를 바꾸면 시간대 행 아래 안내 표시, 프로필 탭에 갔다 오면 사라짐</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>[관찰 2026-10-06: 안내가 늘 보임]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P1-02-03</t>
+          <t>P1-01-16</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08</t>
+          <t>SCR-SET-02</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>P1-02</t>
+          <t>P1-01, 개정대기 SET-02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1588,33 +1612,45 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1) 이미 있는 이름으로 프로젝트 추가 2) 빈 이름으로 추가</t>
+          <t>1) 시간대 칸 열기 2) '서울'·'도쿄'·'kolkata'·'+9'·'+5:30'·'zzz' 입력 3) ↑↓·Enter로 고르기 4) 입력 후 Esc·Tab으로 벗어나기</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>칸 아래 오류(서버 errors[] 포함)</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>'추천'(현재 값) 다음 '전체'(UTC 오프셋 순), 'Asia/Seoul (UTC+09:00)' 표기, 한국어 도시·영문·오프셋으로 거름, 결과 없으면 안내, ↑↓·Enter 선택 시 저장, Esc·벗어나면 원래 값, 옛 이름(Asia/Calcutta 등) 없음</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] [재검증 e39aa14] 콤보박스: 열면 '추천'(Asia/Seoul) + '전체' 418개(UTC-11:00부터 오프셋 순), 'Asia/Seoul (UTC+09:00)' 표기. '서울'·'도쿄'·'뉴욕'·'kolkata'·'seoul' → 1건, '+9' → 10건, '+5:30' → Colombo·Kolkata, '-3' → 36건, 'zzz' → '찾는 시간대가 없어요'. ↓↑로 이동(aria-activedescendant), Enter로 선택·저장, 클릭 선택도 저장, Esc·Tab으로 벗어나면 원래 값. Asia/Calcutta·Saigon·Katmandu·Rangoon·Kiev 등 옛 이름 없음(Kolkata·Ho_Chi_Minh·Kyiv 있음)</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>목록 폭이 좁아(약 210px) 긴 이름이 두 줄로 꺾임 — 보기 관찰. [관찰 2026-10-06: select 418개 나열·옛 이름 섞임]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P1-02-04</t>
+          <t>P1-02-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SCR-SET-08, SCR-TASK-01</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04, D-59</t>
+          <t>P1-02, TASK-04</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1629,28 +1665,40 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무가 있는 프로젝트</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1) 프로젝트 보관 2) 업무 목록·캘린더 확인</t>
+          <t>1) /settings/projects에서 이름 입력·팔레트 색 선택해 프로젝트 추가</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>삭제 버튼 없이 보관만 가능(D-59), 보관 프로젝트의 업무가 목록·캘린더에서 숨겨짐, 되돌리기 토스트</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+          <t>목록에 색·이름·업무 수 0 표시, 사이드바 프로젝트 목록에 색 점과 함께 추가</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] /settings/projects: 프로젝트 목록(색 점·이름·'업무 n'·보관 버튼). 이름 입력(placeholder '프로젝트 이름', maxlength 50)+색 선택 후 추가 → 목록 끝에 추가, 입력칸 비움, 색은 다음 미사용 색으로 기본 선택</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>사이드바 프로젝트 목록(SCR-COM-01 ①)은 아직 없음 → P1-02-06</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P1-02-05</t>
+          <t>P1-02-02</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1660,12 +1708,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>P1-02, TASK-04, D-59, UX-03, 태그 삭제 방식(사용자 결정, pm 전달 2026-10-06)</t>
+          <t>P1-02, TASK-04, 2.2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1675,28 +1723,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 태그 2개를 업무 3개에 붙임</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1) 태그 목록의 사용 수 확인 2) 태그 이름 변경 3) 태그 삭제 → 토스트의 되돌리기 4) 다시 삭제 후 토스트가 닫힐 때까지 대기 5) 새로고침</t>
+          <t>1) 프로젝트 색 팔레트 확인 2) 테마 키 컬러와 비교</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>사용 수 정확, 이름 변경이 업무에 반영. 삭제는 확인창 없이 목록에서 바로 빠지고 되돌리기 토스트, 되돌리기 시 태그·업무 연결 복원. 토스트가 닫힌 뒤에야 실제 삭제(하드 삭제, D-59) → 새로고침해도 없음, 업무에서도 제거</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>전용 8색, 테마와 무관하게 고정</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] 색 선택은 라디오 8개(파랑·주황·청록·보라·빨강·올리브·분홍·회색), 안내 '프로젝트 색은 테마를 바꿔도 그대로예요'</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P1-02-07</t>
+          <t>P1-02-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1706,7 +1762,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>P1-02, UX-03, 태그 삭제 방식</t>
+          <t>P1-02</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1721,38 +1777,46 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 태그 1개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1) 태그 삭제 직후(토스트가 떠 있는 동안) 새로고침 또는 다른 화면으로 이동 2) 다시 확인</t>
+          <t>1) 이미 있는 이름으로 프로젝트 추가 2) 빈 이름으로 추가</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>토스트가 닫히기 전 이탈 시 처리(삭제 확정 또는 유지)가 일관됨 — 구현 방침 확인 필요</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t>칸 아래 오류(서버 errors[] 포함)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] 빈 이름 추가 → '프로젝트 이름을 적어 주세요', '영업'·'  공통  '(앞뒤 공백) → 409 '같은 이름의 프로젝트가 있어요'</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>P1-02-06</t>
+          <t>P1-02-04</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-SET-08, SCR-TASK-01</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>P1-02, SCR-COM-01 ①</t>
+          <t>P1-02, TASK-04, D-59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,38 +1831,50 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트 2개</t>
+          <t>로그인 상태(qa- 계정), 업무가 있는 프로젝트</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1) 사이드바 프로젝트 클릭</t>
+          <t>1) 프로젝트 보관 2) 업무 목록·캘린더 확인</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>/tasks?project=&lt;id&gt;로 이동해 그 프로젝트로 필터, 남은 업무 수 표시</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t>삭제 버튼 없이 보관만 가능(D-59), 보관 프로젝트의 업무가 목록·캘린더에서 숨겨짐, 되돌리기 토스트</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] 보관 버튼 → 목록에서 빠지고 '프로젝트 1개를 보관했어요 [되돌리기]' 토스트(약 5초), 제목 옆 '보관한 프로젝트 n'(글자만). 되돌리기 → 복원. 두 개 연달아 보관 → '프로젝트 2개를 보관했어요'로 누적, 입력창 밖 Ctrl+Z → 둘 다 복원. 삭제 버튼은 없음(D-59)</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>업무 목록·캘린더에서 숨김은 업무·캘린더 화면(P1-03·07) 이후 확인</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P1-03-01</t>
+          <t>P1-02-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01, 02</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-02, TASK-04, D-59, UX-03, D-68</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1813,38 +1889,50 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 태그 2개를 업무 3개에 붙임</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 목록 빠른 입력으로 업무 생성 2) 행 클릭해 상세 패널 열기</t>
+          <t>1) 태그 목록의 사용 수 확인 2) 태그 이름 변경 3) 태그 삭제 → 토스트의 되돌리기 4) 다시 삭제 후 토스트가 닫힐 때까지 대기 5) 새로고침</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>목록에 행 추가, 상세 패널(/tasks/:id) 열림, URL 직접 접근·새로고침도 같은 패널</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t>사용 수 정확, 이름 변경이 업무에 반영. 삭제는 확인창 없이 목록에서 바로 빠지고 되돌리기 토스트, 되돌리기 시 태그·업무 연결 복원. 토스트가 닫힌 뒤에야 실제 삭제(하드 삭제, D-59) → 새로고침해도 없음, 업무에서도 제거</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 태그 ✎ → 이름 칸(maxlength 30)+삭제. 빈 값·공백만·'견 적'·'#견적' → '공백과 #은 쓸 수 없고 30자까지예요', '결제'·'결제 ' → 409 '같은 이름의 태그가 있어요'(칸 aria-invalid), '견적서' Enter → 저장(사용 수 3 유지), Esc → 취소. 삭제는 확인창 없이 목록에서 바로 빠지고 '태그 1개를 지웠어요 [되돌리기]', 그동안 저장소에는 남아 있음 → 되돌리기로 복원. 토스트가 닫히면(약 5초) 실제 삭제, 새로고침해도 없음</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>빈 값에도 같은 문구(1자 이상 조건은 문구에 없음) — 문구 관찰. 업무의 태그 이름 반영·제거는 업무 화면(P1-03) 이후</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>P1-03-02</t>
+          <t>P1-02-07</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-02, UX-03, D-68, 사용자 결정(pm 전달 2026-10-06: 새로고침·탭 닫기에도 삭제 확정)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1859,38 +1947,50 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 태그 1개</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1) 상세에서 제목 바로 편집, 메모 입력 2) 패널 닫고 다시 열기</t>
+          <t>1) 태그 삭제 직후(토스트가 떠 있는 동안) 새로고침 2) 다른 태그 삭제 직후 탭 닫기 후 다시 열기 3) 다른 태그 삭제 직후 앱 안 다른 화면으로 이동</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>저장 버튼 없이 자동 저장, 값 유지</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+          <t>세 경우 모두 삭제가 확정되어 다시 열어도 태그가 없음</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 토스트가 떠 있는 동안 새로고침 → 삭제 요청이 나가지 않아 태그가 다시 나타남(화면에서는 지웠는데 남음). 같은 상황에서 앱 안 다른 탭(설정 › 일반)으로 이동 → 토스트가 닫힐 때 삭제됨. 이탈 방식에 따라 결과가 다름</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>기대 결과는 사용자 결정(새로고침·탭 닫기에도 삭제 확정, pm 전달 2026-10-06)으로 고침. 실행 시점 코드는 새로고침하면 삭제가 취소돼 FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>P1-03-03</t>
+          <t>P1-02-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-02</t>
+          <t>P1-02, D-58, 화면정의서 2.5</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1905,43 +2005,51 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 같은 계정 두 탭</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1) 상태 할 일 → 진행 중 → 보류 → 완료로 변경</t>
+          <t>1) 탭 A·B에서 프로젝트·태그 화면 열기 2) A에서 프로젝트 보관·태그 이름 변경 3) B에서 같은 항목 보관·이름 변경</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>각 변경 저장, 완료 시 완료 일시 기록·표시, 상태 변경마다 되돌리기 토스트</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+          <t>B는 409 → 목록을 다시 불러오고 토스트로 알림(목록 동작은 충돌 띠 대신 다시 불러오기+토스트)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 두 탭: B에서 '기획' 보관 후 A에서 같은 프로젝트 보관 → 409 → 목록을 다시 불러오고 토스트 '다른 곳에서 먼저 수정돼서 새로 불러왔어요. 다시 해 주세요'(보관한 프로젝트 1 반영). 태그도 B가 '결제B'로 바꾼 뒤 A가 '결제A'로 바꾸면 같은 토스트 + 목록에 결제B</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>P1-03-04</t>
+          <t>P1-02-09</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-02, SCR-TASK-01</t>
+          <t>P1-02, NFR-06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1951,43 +2059,59 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 행의 완료 체크</t>
+          <t>1) 모바일 폭에서 프로젝트·태그 화면</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>완료 처리. 결과 팝오버(SCR-TASK-03)는 P2라 이번에는 없음을 확인</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>가로 스크롤 없음, 색 선택·보관·태그 편집 버튼 터치 영역 44px 이상</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 390px: 가로 스크롤 없음. 그러나 터치 영역이 44px 미만 — 프로젝트 보관 버튼 54x36, 색 선택 34x34, 태그 ✎ 32x32</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-02-09.png</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>설정 일반은 e39aa14에서 44px로 고쳤으나 프로젝트·태그 화면은 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>P1-03-05</t>
+          <t>P1-02-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-03</t>
+          <t>P1-02, 화면정의서 2.5(키보드)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2002,33 +2126,45 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1) 우선순위 높음/보통/낮음 변경 2) 마감일 어제·오늘·다음 주 지정</t>
+          <t>1) 태그 ✎로 편집 시작 2) Enter로 저장 / Esc로 취소 3) 포커스 위치 확인</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>목록 행에 우선순위 표시, 마감 초과는 빨강, 임박 표시</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+          <t>편집을 마치면 포커스가 그 태그의 ✎ 버튼(또는 바뀐 태그)으로 돌아옴</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 태그 이름을 Enter로 저장하거나 Esc로 취소하면 포커스가 BODY로 사라짐(편집 칸이 없어지며 포커스 복귀 없음). 삭제 후에도 BODY</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>P1-09-08과 같은 유형(키보드 사용자가 위치를 잃음)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>P1-03-06</t>
+          <t>P1-02-06</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-05</t>
+          <t>P1-02, SCR-COM-01 ①</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2043,38 +2179,50 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 프로젝트 2개</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1) 진행률 슬라이더를 끌고 키보드 ←→로 조정</t>
+          <t>1) 사이드바 프로젝트 클릭</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0~100% 10 단위로만 움직임, 목록 행에 진행률 반영</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+          <t>/tasks?project=&lt;id&gt;로 이동해 그 프로젝트로 필터, 남은 업무 수 표시</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] 사이드바에 프로젝트 목록이 없음</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>P1-04 구현 전(pm 결정 2026-10-06: 사이드바 프로젝트 목록·/tasks?project= 이동은 업무 목록 화면과 함께 P1-04 frontend 범위)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>P1-03-07</t>
+          <t>P1-03-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-TASK-01, 02</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-04</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2089,17 +2237,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트·태그 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1) 상세에서 프로젝트 지정, 태그 2개 붙이고 하나 떼기</t>
+          <t>1) 업무 목록 빠른 입력으로 업무 생성 2) 행 클릭해 상세 패널 열기</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>목록 행에 프로젝트 칩·태그 반영</t>
+          <t>목록에 행 추가, 상세 패널(/tasks/:id) 열림, URL 직접 접근·새로고침도 같은 패널</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2110,17 +2258,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>P1-03-08</t>
+          <t>P1-03-02</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01, 02</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01, UX-03</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2140,12 +2288,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1) 목록에서 행 선택 후 Delete 키 2) 토스트의 되돌리기 3) 다시 Delete 후 5초 대기</t>
+          <t>1) 상세에서 제목 바로 편집, 메모 입력 2) 패널 닫고 다시 열기</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>보관(소프트 삭제) + 되돌리기 토스트, 되돌리기로 복원, 5초 뒤 토스트 사라지고 목록에서 빠짐</t>
+          <t>저장 버튼 없이 자동 저장, 값 유지</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2156,7 +2304,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>P1-03-09</t>
+          <t>P1-03-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2166,7 +2314,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-03, TASK-02</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2181,17 +2329,17 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 보관된 업무 id</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1) /tasks/&lt;보관된 id&gt; 직접 접속</t>
+          <t>1) 상태 할 일 → 진행 중 → 보류 → 완료로 변경</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>읽기 전용 + 복원 버튼, 복원하면 목록에 다시 나타남</t>
+          <t>각 변경 저장, 완료 시 완료 일시 기록·표시, 상태 변경마다 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2202,17 +2350,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>P1-03-10</t>
+          <t>P1-03-04</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>P1-03, D-30, D-58 (409)</t>
+          <t>P1-03, TASK-02, SCR-TASK-01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2227,17 +2375,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 업무를 두 탭에서</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1) 탭 A에서 제목 변경 2) 탭 B에서 진행률 변경</t>
+          <t>1) 목록 행의 완료 체크</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>B 패널 상단에 충돌 띠 + [새로 불러오기], 새로 불러오면 A의 변경이 보임</t>
+          <t>완료 처리. 결과 팝오버(SCR-TASK-03)는 P2라 이번에는 없음을 확인</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2248,22 +2396,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>P1-03-11</t>
+          <t>P1-03-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>P1-03, D-30</t>
+          <t>P1-03, TASK-03</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2273,17 +2421,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1) A의 업무 id로 B가 GET·PATCH·DELETE /api/worklog/tasks/{id}</t>
+          <t>1) 우선순위 높음/보통/낮음 변경 2) 마감일 어제·오늘·다음 주 지정</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>404(또는 403). 다른 사용자 업무 조회·수정 불가</t>
+          <t>목록 행에 우선순위 표시, 마감 초과는 빨강, 임박 표시</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2294,22 +2442,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>P1-03-12</t>
+          <t>P1-03-06</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>P1-03, 화면정의서 2.5</t>
+          <t>P1-03, TASK-05</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2319,17 +2467,17 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 0개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1) /tasks 확인</t>
+          <t>1) 진행률 슬라이더를 끌고 키보드 ←→로 조정</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>빈 상태: 빠른 입력 문법 안내</t>
+          <t>0~100% 10 단위로만 움직임, 목록 행에 진행률 반영</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2340,7 +2488,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>P1-03-13</t>
+          <t>P1-03-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2350,12 +2498,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>NFR-06</t>
+          <t>P1-03, TASK-04</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2365,17 +2513,17 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>로그인 상태(qa- 계정), 프로젝트·태그 있음</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 업무 상세 열기</t>
+          <t>1) 상세에서 프로젝트 지정, 태그 2개 붙이고 하나 떼기</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>전체 화면 패널, 가로 스크롤 없음, 닫기 가능</t>
+          <t>목록 행에 프로젝트 칩·태그 반영</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2386,17 +2534,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>P1-04-01</t>
+          <t>P1-03-08</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-01, 02</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>P1-04, TASK-06</t>
+          <t>P1-03, TASK-01, UX-03</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2411,17 +2559,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 10개 이상</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1) 제목 검색어 입력</t>
+          <t>1) 목록에서 행 선택 후 Delete 키 2) 토스트의 되돌리기 3) 다시 Delete 후 5초 대기</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>제목에 검색어가 포함된 업무만 표시</t>
+          <t>보관(소프트 삭제) + 되돌리기 토스트, 되돌리기로 복원, 5초 뒤 토스트 사라지고 목록에서 빠짐</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2432,17 +2580,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>P1-04-02</t>
+          <t>P1-03-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>P1-04, TASK-06</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2457,17 +2605,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 보관된 업무 id</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1) 상태·프로젝트·태그·마감 기간 필터 칩을 각각, 그리고 함께 적용</t>
+          <t>1) /tasks/&lt;보관된 id&gt; 직접 접속</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>조건 교집합만 표시, 칩에 적용 수 표시</t>
+          <t>읽기 전용 + 복원 버튼, 복원하면 목록에 다시 나타남</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2478,17 +2626,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>P1-04-03</t>
+          <t>P1-03-10</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>P1-04, SCR-TASK-01</t>
+          <t>P1-03, D-30, D-58 (409)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2503,17 +2651,17 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 같은 업무를 두 탭에서</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1) 필터 적용 후 새로고침 2) 다른 화면 갔다가 뒤로 가기</t>
+          <t>1) 탭 A에서 제목 변경 2) 탭 B에서 진행률 변경</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>필터가 URL에 남아 그대로 복원</t>
+          <t>B 패널 상단에 충돌 띠 + [새로 불러오기], 새로 불러오면 A의 변경이 보임</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2524,22 +2672,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>P1-04-04</t>
+          <t>P1-03-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>P1-04</t>
+          <t>P1-03, D-30</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2549,17 +2697,17 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1) 결과가 없는 조건 적용 2) 필터 지우기</t>
+          <t>1) A의 업무 id로 B가 GET·PATCH·DELETE /api/worklog/tasks/{id}</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>"조건에 맞는 업무가 없어요" + 필터 지우기, 누르면 전체 목록</t>
+          <t>404(또는 403). 다른 사용자 업무 조회·수정 불가</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2570,7 +2718,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>P1-04-05</t>
+          <t>P1-03-12</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2580,12 +2728,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>P1-04, SCR-TASK-01 ④⑥</t>
+          <t>P1-03, 화면정의서 2.5</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2595,17 +2743,17 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무 0개</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1) 그룹 기준 마감순/프로젝트/상태 전환 2) 완료 업무 접기 영역 확인</t>
+          <t>1) /tasks 확인</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>그룹이 기준대로 묶임, 완료 업무는 최근 7일만 접힌 영역에</t>
+          <t>빈 상태: 빠른 입력 문법 안내</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2616,22 +2764,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>P1-05-01</t>
+          <t>P1-03-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02</t>
+          <t>NFR-06</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2641,17 +2789,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1) 일정 만들기 → 자세히에서 제목·날짜·시작·종료·메모 입력 후 저장 2) 다시 열어 수정 3) 삭제</t>
+          <t>1) 모바일에서 업무 상세 열기</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>생성·수정 반영, 삭제는 확인창 없이 + 되돌리기 토스트</t>
+          <t>전체 화면 패널, 가로 스크롤 없음, 닫기 가능</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2662,17 +2810,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>P1-05-02</t>
+          <t>P1-04-01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02</t>
+          <t>P1-04, TASK-06</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2687,17 +2835,17 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무 10개 이상</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1) 종일 일정 생성</t>
+          <t>1) 제목 검색어 입력</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>주·일 보기 종일 행, 월 보기 칩으로 표시</t>
+          <t>제목에 검색어가 포함된 업무만 표시</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2708,17 +2856,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>P1-05-03</t>
+          <t>P1-04-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02, 2.5</t>
+          <t>P1-04, TASK-06</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2738,12 +2886,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1) 종료를 시작보다 앞으로 지정해 저장</t>
+          <t>1) 상태·프로젝트·태그·마감 기간 필터 칩을 각각, 그리고 함께 적용</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>해당 칸 아래 오류(서버 errors[] 포함), 저장 안 됨</t>
+          <t>조건 교집합만 표시, 칩에 적용 수 표시</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2754,17 +2902,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>P1-05-04</t>
+          <t>P1-04-03</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>P1-05, TIME-06</t>
+          <t>P1-04, SCR-TASK-01</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2784,12 +2932,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 시간에 일정 2개 생성</t>
+          <t>1) 필터 적용 후 새로고침 2) 다른 화면 갔다가 뒤로 가기</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>겹침 경고 없이 생성, 주 보기에서 나란히 배치</t>
+          <t>필터가 URL에 남아 그대로 복원</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2800,17 +2948,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>P1-05-05</t>
+          <t>P1-04-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>P1-05, D-30, D-58 (409)</t>
+          <t>P1-04</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2825,17 +2973,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 일정을 두 탭에서</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1) A에서 제목 수정 2) B에서 시간 수정</t>
+          <t>1) 결과가 없는 조건 적용 2) 필터 지우기</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>B 모달 상단 충돌 띠 + [새로 불러오기]</t>
+          <t>"조건에 맞는 업무가 없어요" + 필터 지우기, 누르면 전체 목록</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2846,17 +2994,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>P1-05-06</t>
+          <t>P1-04-05</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>P1-05</t>
+          <t>P1-04, SCR-TASK-01 ④⑥</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2871,17 +3019,17 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 1개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1) 일정에 업무 연결(검색) 2) 해제 3) 새 업무로 연결</t>
+          <t>1) 그룹 기준 마감순/프로젝트/상태 전환 2) 완료 업무 접기 영역 확인</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>연결·해제 반영, 일정 프로젝트는 업무를 따름, 업무 상세 연결 일정 목록에도 반영</t>
+          <t>그룹이 기준대로 묶임, 완료 업무는 최근 7일만 접힌 영역에</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2892,22 +3040,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>P1-05-07</t>
+          <t>P1-05-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>P1-05</t>
+          <t>P1-05, SCH-02</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2917,17 +3065,17 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1) A의 일정 id로 B가 조회·수정·삭제</t>
+          <t>1) 일정 만들기 → 자세히에서 제목·날짜·시작·종료·메모 입력 후 저장 2) 다시 열어 수정 3) 삭제</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>404(또는 403)</t>
+          <t>생성·수정 반영, 삭제는 확인창 없이 + 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2938,7 +3086,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>P1-06-01</t>
+          <t>P1-05-02</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2948,7 +3096,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05, SCH-02</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2968,12 +3116,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1) 매일 반복, 종료 날짜 지정 2) 매월 반복, 종료 없음</t>
+          <t>1) 종일 일정 생성</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>지정 범위 회차만 표시, 종료 없음은 먼 미래 달에도 표시</t>
+          <t>주·일 보기 종일 행, 월 보기 칩으로 표시</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2984,7 +3132,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>P1-06-02</t>
+          <t>P1-05-03</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2994,7 +3142,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05, SCH-02, 2.5</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3014,12 +3162,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1) 매주 화·목 반복 생성</t>
+          <t>1) 종료를 시작보다 앞으로 지정해 저장</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>선택한 요일에만 회차 표시</t>
+          <t>해당 칸 아래 오류(서버 errors[] 포함), 저장 안 됨</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3030,17 +3178,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>P1-06-03</t>
+          <t>P1-05-04</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03, D-24</t>
+          <t>P1-05, TIME-06</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3055,17 +3203,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1) 한 회차 제목 수정 → 범위 다이얼로그 확인 2) '이 일정만' 3) 다른 회차 수정 → '모든 일정'</t>
+          <t>1) 같은 시간에 일정 2개 생성</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>선택지는 '이 일정만 / 모든 일정' 두 개('이후 일정' 없음), 이 일정만은 그 회차만, 모든 일정은 전 회차 변경</t>
+          <t>겹침 경고 없이 생성, 주 보기에서 나란히 배치</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3076,17 +3224,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>P1-06-04</t>
+          <t>P1-05-05</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05, D-30, D-58 (409)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3101,17 +3249,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>로그인 상태(qa- 계정), 같은 일정을 두 탭에서</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1) 한 회차 삭제 → '이 일정만' 2) 다른 회차 삭제 → '모든 일정'</t>
+          <t>1) A에서 제목 수정 2) B에서 시간 수정</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>해당 회차만 사라짐 / 반복 전체 사라짐, 되돌리기 토스트</t>
+          <t>B 모달 상단 충돌 띠 + [새로 불러오기]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3122,17 +3270,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>P1-06-05</t>
+          <t>P1-05-06</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3147,17 +3295,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>로그인 상태(qa- 계정), 업무 1개</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1) 주 보기에서 한 회차를 끌어 이동</t>
+          <t>1) 일정에 업무 연결(검색) 2) 해제 3) 새 업무로 연결</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>범위 선택 다이얼로그가 뜨고, 취소하면 원래 자리로 돌아감</t>
+          <t>연결·해제 반영, 일정 프로젝트는 업무를 따름, 업무 상세 연결 일정 목록에도 반영</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3168,22 +3316,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>P1-06-06</t>
+          <t>P1-05-07</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>P1-06</t>
+          <t>P1-05</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3193,17 +3341,17 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1) 범위 다이얼로그에서 Esc·키보드로 선택</t>
+          <t>1) A의 일정 id로 B가 조회·수정·삭제</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Esc로 닫힘(변경 없음), 키보드만으로 선택·확인 가능</t>
+          <t>404(또는 403)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3214,17 +3362,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>P1-07-01</t>
+          <t>P1-06-01</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3244,12 +3392,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1) 사이드바 캘린더 진입 2) 주 보기 구성 확인</t>
+          <t>1) 매일 반복, 종료 날짜 지정 2) 매월 반복, 종료 없음</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>기본 주 보기(/calendar/week/:date), 오늘 열 강조, 기본 08~19시·스크롤로 0~24시, 현재 시각선, 종일 행</t>
+          <t>지정 범위 회차만 표시, 종료 없음은 먼 미래 달에도 표시</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3260,17 +3408,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>P1-07-02</t>
+          <t>P1-06-02</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01~05</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3290,12 +3438,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1) 보기 전환 버튼으로 일·주·월·연·목록 이동 2) 각 URL로 직접 접속·새로고침</t>
+          <t>1) 매주 화·목 반복 생성</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>각 보기가 정의된 경로로 열리고 새로고침해도 유지</t>
+          <t>선택한 요일에만 회차 표시</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3306,17 +3454,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>P1-07-03</t>
+          <t>P1-06-03</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, UX-09</t>
+          <t>P1-06, SCH-03, D-24</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3331,17 +3479,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 한글 입력 상태 포함</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1) 그리드에 포커스를 두고 D·W·M·Y·A, T, J/K, C, P 누르기 2) 한글 입력 상태(ㅇ·ㅈ 등)로 같은 키</t>
+          <t>1) 한 회차 제목 수정 → 범위 다이얼로그 확인 2) '이 일정만' 3) 다른 회차 수정 → '모든 일정'</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>보기 전환·오늘·이전/다음·만들기·업무 패널이 동작, 한글 상태에서도 동작(event.code)</t>
+          <t>선택지는 '이 일정만 / 모든 일정' 두 개('이후 일정' 없음), 이 일정만은 그 회차만, 모든 일정은 전 회차 변경</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3352,17 +3500,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>P1-07-04</t>
+          <t>P1-06-04</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, SCR-SET-02</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>P1-07, UX-09, WCAG 2.1.4, D-60</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3377,17 +3525,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창에 포커스를 두고 D·W 입력 2) 설정에서 단축키 끄기 후 캘린더에서 D·W</t>
+          <t>1) 한 회차 삭제 → '이 일정만' 2) 다른 회차 삭제 → '모든 일정'</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>입력창·모달에서는 글자만 입력되고 보기 안 바뀜, 끄면 단일 문자 단축키 모두 무시. 설정은 다른 브라우저에서 로그인해도 유지(identity 저장, D-60)</t>
+          <t>해당 회차만 사라짐 / 반복 전체 사라짐, 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3398,17 +3546,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>P1-07-05</t>
+          <t>P1-06-05</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 03</t>
+          <t>SCR-CAL-01, 08</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, D-25</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3423,17 +3571,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1) 공휴일이 있는 주·월로 이동(예: 2026-10-09 한글날)</t>
+          <t>1) 주 보기에서 한 회차를 끌어 이동</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>요일 머리·날짜가 빨강 + 공휴일 명칭, 주말·공휴일 음영</t>
+          <t>범위 선택 다이얼로그가 뜨고, 취소하면 원래 자리로 돌아감</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3444,22 +3592,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>P1-07-06</t>
+          <t>P1-06-06</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-06</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3469,17 +3617,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트 2개 일정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1) 좌측 프로젝트 필터 토글</t>
+          <t>1) 범위 다이얼로그에서 Esc·키보드로 선택</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>끈 프로젝트의 일정이 숨겨짐, 다시 켜면 표시</t>
+          <t>Esc로 닫힘(변경 없음), 키보드만으로 선택·확인 가능</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3490,7 +3638,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>P1-07-07</t>
+          <t>P1-07-01</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3520,12 +3668,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1) 미니 달력에서 다른 주 날짜 클릭</t>
+          <t>1) 사이드바 캘린더 진입 2) 주 보기 구성 확인</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>해당 주로 이동, 미니 달력에 이번 주 강조</t>
+          <t>기본 주 보기(/calendar/week/:date), 오늘 열 강조, 기본 08~19시·스크롤로 0~24시, 현재 시각선, 종일 행</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3536,17 +3684,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>P1-07-08</t>
+          <t>P1-07-02</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 06</t>
+          <t>SCR-CAL-01~05</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, SCH-04</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3566,12 +3714,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1) 빈 칸 클릭 2) 빈 칸 드래그(10:00~11:45)</t>
+          <t>1) 보기 전환 버튼으로 일·주·월·연·목록 이동 2) 각 URL로 직접 접속·새로고침</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>클릭은 1시간, 드래그는 15분 단위로 맞춘 범위의 빠른 생성 팝오버</t>
+          <t>각 보기가 정의된 경로로 열리고 새로고침해도 유지</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3582,7 +3730,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>P1-07-09</t>
+          <t>P1-07-03</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3592,7 +3740,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-04, UX-03</t>
+          <t>P1-07, SCH-01, UX-09</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3607,17 +3755,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 일정 1개</t>
+          <t>로그인 상태(qa- 계정), 한글 입력 상태 포함</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1) 블록을 다른 시간·요일로 끌기 2) 아래 끝을 끌어 길이 조절 3) 되돌리기</t>
+          <t>1) 그리드에 포커스를 두고 D·W·M·Y·A, T, J/K, C, P 누르기 2) 한글 입력 상태(ㅇ·ㅈ 등)로 같은 키</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>15분 단위로 이동·조절, 되돌리기 토스트로 원복</t>
+          <t>보기 전환·오늘·이전/다음·만들기·업무 패널이 동작, 한글 상태에서도 동작(event.code)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3628,17 +3776,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>P1-07-10</t>
+          <t>P1-07-04</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-02</t>
+          <t>SCR-CAL-01, SCR-SET-02</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, UX-09, WCAG 2.1.4, D-60</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3653,17 +3801,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 시간 없는 기록이 있는 날(P2 전이면 생략)</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1) 일 보기 구성 확인</t>
+          <t>1) 입력창에 포커스를 두고 D·W 입력 2) 설정에서 단축키 끄기 후 캘린더에서 D·W</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>하루 그리드, 우측 '이날의 기록' 패널</t>
+          <t>입력창·모달에서는 글자만 입력되고 보기 안 바뀜, 끄면 단일 문자 단축키 모두 무시. 설정은 다른 브라우저에서 로그인해도 유지(identity 저장, D-60)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3674,17 +3822,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>P1-07-11</t>
+          <t>P1-07-05</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-03</t>
+          <t>SCR-CAL-01, 03</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, SCH-01, D-25</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3699,17 +3847,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 하루에 일정 5개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1) 월 보기 확인 2) +n개 더보기 3) 날짜 숫자 클릭 4) 빈 칸 클릭 5) 칩을 다른 날로 끌기</t>
+          <t>1) 공휴일이 있는 주·월로 이동(예: 2026-10-09 한글날)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>6주×7일, 칩 최대 3개 + '+2개 더보기' 팝오버, 숫자 → 일 보기, 빈 칸 → 종일 빠른 생성, 칩 이동</t>
+          <t>요일 머리·날짜가 빨강 + 공휴일 명칭, 주말·공휴일 음영</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3720,12 +3868,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>P1-07-12</t>
+          <t>P1-07-06</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-04</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3745,17 +3893,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 프로젝트 2개 일정</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1) 연 보기 확인 2) 날짜 클릭 3) 월 이름 클릭 4) 390px</t>
+          <t>1) 좌측 프로젝트 필터 토글</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>12개월(데스크톱 4×3, 모바일 1열), 일정 밀도 점 3단계, 날짜 → 일 보기, 월 이름 → 월 보기</t>
+          <t>끈 프로젝트의 일정이 숨겨짐, 다시 켜면 표시</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3766,12 +3914,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>P1-07-13</t>
+          <t>P1-07-07</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-05</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3791,17 +3939,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 반복 일정 포함</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 보기 확인 2) 아래로 스크롤 3) 지난 일정 보기</t>
+          <t>1) 미니 달력에서 다른 주 날짜 클릭</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>오늘부터 날짜별 그룹, 반복 아이콘, 무한 스크롤로 다음 일정 로드, 지난 일정 표시</t>
+          <t>해당 주로 이동, 미니 달력에 이번 주 강조</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3812,22 +3960,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>P1-07-14</t>
+          <t>P1-07-08</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-05</t>
+          <t>SCR-CAL-01, 06</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>P1-07</t>
+          <t>P1-07, SCH-01, SCH-04</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3837,17 +3985,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>일정 없는 새 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 보기</t>
+          <t>1) 빈 칸 클릭 2) 빈 칸 드래그(10:00~11:45)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>"다가오는 일정이 없어요"</t>
+          <t>클릭은 1시간, 드래그는 15분 단위로 맞춘 범위의 빠른 생성 팝오버</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3858,22 +4006,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>P1-07-15</t>
+          <t>P1-07-09</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01~05</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, 2.4</t>
+          <t>P1-07, SCH-04, UX-03</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3883,17 +4031,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px·800px</t>
+          <t>로그인 상태(qa- 계정), 일정 1개</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 캘린더 진입 2) 태블릿 폭</t>
+          <t>1) 블록을 다른 시간·요일로 끌기 2) 아래 끝을 끌어 길이 조절 3) 되돌리기</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>모바일 기본 보기는 일 보기, 가로 스크롤 없음. 태블릿은 업무 패널 접힘</t>
+          <t>15분 단위로 이동·조절, 되돌리기 토스트로 원복</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3904,17 +4052,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>P1-07-16</t>
+          <t>P1-07-10</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-02</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>P1-07, D-37</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3929,17 +4077,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 시간 없는 기록이 있는 날(P2 전이면 생략)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1) 연말·연초(12월 마지막 주) 주 보기</t>
+          <t>1) 일 보기 구성 확인</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>연도가 바뀌는 주가 끊기지 않고 표시, 1/1 공휴일 표시</t>
+          <t>하루 그리드, 우측 '이날의 기록' 패널</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3950,17 +4098,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>P1-08-01</t>
+          <t>P1-07-11</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-03</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCH-07</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3975,17 +4123,17 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 일정 없는 업무(마감 초과·날짜 없음 포함)</t>
+          <t>로그인 상태(qa- 계정), 하루에 일정 5개</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1) 캘린더 업무 패널 확인</t>
+          <t>1) 월 보기 확인 2) +n개 더보기 3) 날짜 숫자 클릭 4) 빈 칸 클릭 5) 칩을 다른 날로 끌기</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>기본 열림, 마감순, 마감 초과 강조, 프로젝트 칩·마감 표시, 날짜 없는 업무 접힘</t>
+          <t>6주×7일, 칩 최대 3개 + '+2개 더보기' 팝오버, 숫자 → 일 보기, 빈 칸 → 종일 빠른 생성, 칩 이동</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3996,17 +4144,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>P1-08-02</t>
+          <t>P1-07-12</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09, 01</t>
+          <t>SCR-CAL-04</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCH-04, SCH-07</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4026,12 +4174,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1) 패널 카드를 그리드 10:15 칸으로 끌기</t>
+          <t>1) 연 보기 확인 2) 날짜 클릭 3) 월 이름 클릭 4) 390px</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>10:15~11:15 일정 생성(15분 단위), 업무와 연결, 패널에서 빠짐</t>
+          <t>12개월(데스크톱 4×3, 모바일 1열), 일정 밀도 점 3단계, 날짜 → 일 보기, 월 이름 → 월 보기</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4042,17 +4190,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>P1-08-03</t>
+          <t>P1-07-13</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-05</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>P1-08</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4067,17 +4215,17 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 모든 업무가 배치됨</t>
+          <t>로그인 상태(qa- 계정), 반복 일정 포함</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1) 패널 확인</t>
+          <t>1) 목록 보기 확인 2) 아래로 스크롤 3) 지난 일정 보기</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>"배치할 업무가 없어요"</t>
+          <t>오늘부터 날짜별 그룹, 반복 아이콘, 무한 스크롤로 다음 일정 로드, 지난 일정 표시</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4088,22 +4236,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>P1-08-04</t>
+          <t>P1-07-14</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-05</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>P1-08, UX-09</t>
+          <t>P1-07</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4113,17 +4261,17 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>일정 없는 새 계정</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1) P 키로 패널 닫기·열기 2) 패널 안 빠른 입력으로 업무 추가</t>
+          <t>1) 목록 보기</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>토글 동작, 추가한 업무가 패널에 나타남</t>
+          <t>"다가오는 일정이 없어요"</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4134,22 +4282,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>P1-08-05</t>
+          <t>P1-07-15</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-CAL-01~05</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCR-HOME-01 ④</t>
+          <t>NFR-06, 2.4</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4159,17 +4307,17 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 390px·800px</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1) 홈 남은 업무를 일정 영역으로 끌기</t>
+          <t>1) 모바일에서 캘린더 진입 2) 태블릿 폭</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>P1 범위 확인: 오늘 일정 영역(③)은 P2라 이번에는 대상 없음 → N/A 예상</t>
+          <t>모바일 기본 보기는 일 보기, 가로 스크롤 없음. 태블릿은 업무 패널 접힘</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4180,17 +4328,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>P1-09-01</t>
+          <t>P1-07-16</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
+          <t>P1-07, D-37</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4210,45 +4358,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1) '14-16 견적서 작성 @영업 #긴급 !높음 ~금' 입력</t>
+          <t>1) 연말·연초(12월 마지막 주) 주 보기</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>칩: 시간(오늘 14:00–16:00) · 프로젝트 @영업 · 태그 #긴급 · 우선순위 높음 · 마감 이번 주 금요일 실제 날짜, 종류별 색 구분, 제목 '견적서 작성'</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] [재검증, a82f5d8 수정] 칩 class에 undefined 없음. 시간=accent(#E9E8FA/#3C32AB), 프로젝트=노랑(#FFF0C7), 우선순위 높음=빨강 계열(#FDE2DD/#A02613), 우선순위 보통·낮음과 마감=의도된 회색(#EEF0F6)</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>연도가 바뀌는 주가 끊기지 않고 표시, 1/1 공휴일 표시</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>[최초 2026-10-06 FAIL: 마감 칩 class 'undefined', 증거 evidence/P1/P1-09-01.png] 회색 칩은 pm 전달 기준(의도된 회색)으로 판정. 기호 변경 전 코드(#=프로젝트)로 확인. #태그·@프로젝트 기대 결과는 frontend 다음 커밋 후 재실행</t>
-        </is>
-      </c>
+      <c r="L78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>P1-09-02</t>
+          <t>P1-08-01</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04</t>
+          <t>P1-08, SCH-07</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4263,50 +4399,38 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 일정 없는 업무(마감 초과·날짜 없음 포함)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
+          <t>1) 캘린더 업무 패널 확인</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>기본 열림, 마감순, 마감 초과 강조, 프로젝트 칩·마감 표시, 날짜 없는 업무 접힘</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>Enter 저장: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>P1-09-03</t>
+          <t>P1-08-02</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09, 01</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-08, SCH-04, SCH-07</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4326,45 +4450,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
+          <t>1) 패널 카드를 그리드 10:15 칸으로 끌기</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>10:15~11:15 일정 생성(15분 단위), 업무와 연결, 패널에서 빠짐</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
-        </is>
-      </c>
+      <c r="L80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>P1-09-04</t>
+          <t>P1-08-03</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>P1-09, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
+          <t>P1-08</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4379,50 +4491,38 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 모든 업무가 배치됨</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 프로젝트 '@신규' 입력</t>
+          <t>1) 패널 확인</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>"배치할 업무가 없어요"</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>새 프로젝트 칩: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>P1-09-13</t>
+          <t>P1-08-04</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>P1-09, TASK-04, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
+          <t>P1-08, UX-09</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4442,12 +4542,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1) '보고서 #긴급 #검토' 입력 2) 없는 태그 '#새태그' 입력 3) Enter 저장 후 업무 상세 확인</t>
+          <t>1) P 키로 패널 닫기·열기 2) 패널 안 빠른 입력으로 업무 추가</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>태그 칩 2개(#긴급·#검토), 프로젝트 칩과 다른 색. 저장하면 업무에 태그 2개 연결(여러 개 허용 — 구현 범위 확인), 없는 태그 처리 방식은 구현 확인</t>
+          <t>토글 동작, 추가한 업무가 패널에 나타남</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4458,17 +4558,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>P1-09-05</t>
+          <t>P1-08-05</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>P1-09</t>
+          <t>P1-08, SCR-HOME-01 ④</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4488,35 +4588,23 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '@영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
+          <t>1) 홈 남은 업무를 일정 영역으로 끌기</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] Esc → 입력 비움·미리보기 사라짐. 빈 입력·공백만 Enter → 아무 반응 없음(토스트·오류 없음). '#영업 !높음'·'~금' → 칩은 보이고 '할 일 이름을 적어 주세요' 안내</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>P1 범위 확인: 오늘 일정 영역(③)은 P2라 이번에는 대상 없음 → N/A 예상</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>[기호 변경(# 태그·@ 프로젝트) 전 실행 결과 — frontend 수정 후 재실행 예정] pm 전달 기준(완전히 빈 입력은 조용히 무시, 제목만 비면 안내)으로 기대 결과를 고치고 칩 수정 드롭다운은 P1-09-12로 분리</t>
-        </is>
-      </c>
+      <c r="L83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>P1-09-12</t>
+          <t>P1-09-01</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4526,7 +4614,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCR-COM-02 주요 동작</t>
+          <t>P1-09, REC-04, D-62, D-67</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4546,35 +4634,35 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1) 해석 칩 클릭</t>
+          <t>1) '14-16 견적서 작성 @영업 #긴급 !높음 ~금' 입력</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>그 값만 바꾸는 드롭다운</t>
+          <t>칩: 시간(오늘 14:00–16:00) · 프로젝트 @영업 · 태그 #긴급 · 우선순위 높음 · 마감 이번 주 금요일 실제 날짜, 종류별 색 구분, 제목 '견적서 작성'</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] '14-16 견적서 작성 @영업 #긴급 !높음 ~금' → 칩 '오늘 14:00–16:00'(accent) · '영업'(프로젝트 색 P2 주황) · '#긴급 새'(점선 테두리, 없는 태그) · '우선순위 높음'(빨강 계열) · '마감 10/9(금)'(회색), 안내 '일정과 업무가 함께 만들어져요'. 있는 태그 '#견적'은 흰 바탕 실선 테두리로 프로젝트 칩과 구분</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
+          <t>[이전: 2026-10-06 기호 변경 전 코드에서 FAIL→재검증 PASS, 증거 evidence/P1/P1-09-01.png]</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>P1-09-06</t>
+          <t>P1-09-02</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4584,7 +4672,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-09, REC-04</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4604,35 +4692,35 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
+          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
+          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
+          <t>Enter 저장: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>P1-09-07</t>
+          <t>P1-09-03</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4642,7 +4730,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>UX-09</t>
+          <t>P1-09, REC-04, D-62</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4662,17 +4750,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
+          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
+          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
@@ -4681,12 +4769,16 @@
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>P1-09-11</t>
+          <t>P1-09-04</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4696,7 +4788,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>P1-09, UX-09</t>
+          <t>P1-09, D-67</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4706,7 +4798,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4716,45 +4808,45 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
+          <t>1) 없는 프로젝트 '@신규' 입력</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
+          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 @신규프로젝트' → '+ 새 프로젝트 "신규프로젝트" 만들기' 칩(button). 키보드 Enter로 눌러 생성 → 프로젝트 칩(색 P4)으로 바뀜, 설정 프로젝트 목록에 추가. '@Alpha' 만든 뒤 '@alpha'는 기존 Alpha로 인식(대소문자 무시)</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
+          <t>업무 저장(Enter)은 API 연결 전이라 확인 안 함</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>P1-09-08</t>
+          <t>P1-09-13</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SCR-ONB-02</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, 빠른 입력 기호 변경(사용자 결정, pm 전달 2026-10-06: #=태그·@=프로젝트)</t>
+          <t>P1-09, TASK-04, D-67</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4774,45 +4866,45 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
+          <t>1) '보고서 #긴급 #검토' 입력 2) 없는 태그 '#새태그' 입력 3) Enter 저장 후 업무 상세 확인</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>문법 표(시간·@프로젝트·#태그·!우선순위·~마감·날짜(시간 없이 쓰면 마감일))와 예시 3개(새 기호), 예시 클릭 시 입력창에 채워짐, Esc로 닫으면 ? 버튼으로 포커스 복귀</t>
+          <t>태그 칩 2개(#긴급·#검토), 프로젝트 칩과 다른 색. 저장하면 업무에 태그 2개 연결(여러 개 허용 — 구현 범위 확인), 없는 태그 처리 방식은 구현 확인</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] [재검증, a82f5d8 수정] 도움말을 Esc로 닫으면 포커스가 ? 버튼(문법 도움말)으로 돌아옴, 다음 Tab도 정상. 문법 표에 '날짜 (시간 없이 쓰면 마감일)' 반영</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 #견적 #결제 #견적' → 태그 칩 2개(같은 이름 하나로), '#새태그'·'#1번' → 점선 '새' 칩. 규칙에 안 맞는 'C# 공부'·'메일 a@b.com 확인'·'보고서 @ #'은 칩 없이 제목에 남음. '@개발 @영업'은 처음 것(개발)만 프로젝트</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>[최초 2026-10-06 FAIL: Esc 후 포커스 BODY, 증거 evidence/P1/P1-09-08.png] 문법 표·예시는 아직 #=프로젝트. 기호 변경 전 코드(#=프로젝트)로 확인. #태그·@프로젝트 기대 결과는 frontend 다음 커밋 후 재실행</t>
+          <t>표시는 확인. 저장 시 태그 생성·연결은 Enter 저장 API 연결 전</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>P1-09-09</t>
+          <t>P1-09-05</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-06</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCH-02</t>
+          <t>P1-09</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4827,40 +4919,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 @영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
+          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '@영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 토글 기본 켜짐(끄면 일정만), Esc는 임시 블록 제거</t>
+          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] Esc → 입력 비움, 빈 입력 Enter 무시, '@영업 #견적'처럼 제목이 비면 칩과 '할 일 이름을 적어 주세요'</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
-        </is>
-      </c>
+      <c r="L89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>P1-09-10</t>
+          <t>P1-09-12</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4870,7 +4958,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>P1-09, SCR-COM-02 주요 동작</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4885,17 +4973,17 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 포커스</t>
+          <t>1) 해석 칩 클릭</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 상위 3개 제안</t>
+          <t>그 값만 바꾸는 드롭다운</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4911,24 +4999,24 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
+          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>P1-10-01</t>
+          <t>P1-09-06</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-09, REC-04, D-62</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4948,17 +5036,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
+          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
+          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -4969,24 +5057,24 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎) / [재검증 a5bb168] vite dev에서도 입력창 Ctrl+K → 팔레트 검색 입력에 포커스, Esc로 닫히고 빠른 입력창 값 유지(관찰 ① 해소)</t>
+          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>P1-10-02</t>
+          <t>P1-09-07</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>UX-09</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5006,17 +5094,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
+          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
+          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
@@ -5025,26 +5113,22 @@
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
-        </is>
-      </c>
+      <c r="L92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>P1-10-08</t>
+          <t>P1-09-11</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01, SCR-COM-03 ②</t>
+          <t>P1-09, UX-09</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5054,22 +5138,22 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 제목 일부·일지 내용 입력</t>
+          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>업무 검색·일지 검색 결과 그룹</t>
+          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5085,24 +5169,24 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
+          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>P1-10-03</t>
+          <t>P1-09-08</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-ONB-02</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-09, REC-04, D-67</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5122,17 +5206,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
+          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
+          <t>문법 표(시간·@프로젝트·#태그·!우선순위·~마감·날짜(시간 없이 쓰면 마감일))와 예시 3개(새 기호), 예시 클릭 시 입력창에 채워짐, Esc로 닫으면 ? 버튼으로 포커스 복귀</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] 문법 표: 시간 / @영업 프로젝트(없으면 새로 만들지 물어봐요) / #결제 #견적 태그(여러 개 가능, 없으면 저장할 때 만들어요) / !높음·!낮음 / ~금·~10/12 마감일 / 오늘·내일·다음주 수요일 날짜(시간 없이 쓰면 마감일). 예시 3개 @·# 기호로 갱신. Esc로 닫으면 ? 버튼으로 포커스</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -5143,24 +5227,24 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
+          <t>[이전 FAIL 증거 evidence/P1/P1-09-08.png]</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>P1-10-04</t>
+          <t>P1-09-09</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-CAL-06</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>P1-09, SCH-02</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5175,17 +5259,17 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
+          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 @영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
+          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 토글 기본 켜짐(끄면 일정만), Esc는 임시 블록 제거</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5201,24 +5285,24 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>P1-10-09</t>
+          <t>P1-09-10</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03, UX-09</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5233,51 +5317,55 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
+          <t>1) 빠른 입력 포커스</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
+          <t>자주 하는 업무 상위 3개 제안</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>P1-10-05</t>
+          <t>P1-10-01</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5287,50 +5375,50 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 업무 보관</t>
+          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>토스트가 하단 탭 위에 표시</t>
+          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
+          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎) / [재검증 a5bb168] vite dev에서도 입력창 Ctrl+K → 팔레트 검색 입력에 포커스, Esc로 닫히고 빠른 입력창 값 유지(관찰 ① 해소)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>P1-10-06</t>
+          <t>P1-10-02</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-04</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5345,22 +5433,22 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 직후 첫 화면</t>
+          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
+          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 데모 계정 첫 화면: 날짜·인사·빠른 기록 입력창, '오늘 할 일을 한 줄로 적어 보세요' + 안내 + 예시 3개(클릭 시 입력창 채움·포커스). 390px에서 가로 스크롤 없음, 예시 버튼 높이 44px</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
@@ -5371,14 +5459,14 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>'데이터 없음' 판정은 업무 API 이후. 지금은 항상 빈 상태를 보여 줌(P1-11에서 확인)</t>
+          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>P1-10-07</t>
+          <t>P1-10-08</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5388,12 +5476,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>UX-09, 2.5</t>
+          <t>P1-10, UX-01, SCR-COM-03 ②</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5403,50 +5491,50 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
+          <t>1) 업무 제목 일부·일지 내용 입력</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+          <t>업무 검색·일지 검색 결과 그룹</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고) / [재검증 a5bb168] dev 모드에서도 같은 결과</t>
+          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>P1-11-01</t>
+          <t>P1-10-03</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5461,38 +5549,50 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 직후 홈 확인</t>
+          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
+          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>P1-11-02</t>
+          <t>P1-10-04</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5512,33 +5612,45 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
+          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>P1-11-03</t>
+          <t>P1-10-09</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-03, UX-09</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5553,43 +5665,51 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
+          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
+          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>P1-11-04</t>
+          <t>P1-10-05</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05, D-25</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5599,28 +5719,40 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1) 다가오는 일정 영역</t>
+          <t>1) 모바일에서 업무 보관</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
+          <t>토스트가 하단 탭 위에 표시</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>P1-11-05</t>
+          <t>P1-10-06</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5630,7 +5762,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>P1-10, UX-04</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5645,38 +5777,50 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>막 가입한 계정</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1) 홈 빠른 입력으로 업무 추가</t>
+          <t>1) 가입 직후 첫 화면</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
+          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>[재검증 2026-10-06, 444466e 소스 확인] 홈 빈 상태 안내가 '시간·@프로젝트·#태그·!우선순위·~마감을 같이 적으면 알아서 나눠 저장해요.'로 바뀜(453401f)</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>[최초 FAIL 증거 evidence/P1/P1-10-06.png] 이번엔 소스로만 확인. 화면은 다음 실행 때 함께 봄</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>P1-11-06</t>
+          <t>P1-10-07</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, 2.4</t>
+          <t>UX-09, 2.5</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5691,28 +5835,40 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1) 폭별 카드 배치</t>
+          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
+          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고) / [재검증 a5bb168] dev 모드에서도 같은 결과</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>P1-11-07</t>
+          <t>P1-11-01</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5722,12 +5878,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>2.5 (로딩)</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5737,17 +5893,17 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1) 느린 네트워크로 홈 진입</t>
+          <t>1) 로그인 직후 홈 확인</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
+          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5758,17 +5914,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>P1-12-01</t>
+          <t>P1-11-02</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5783,17 +5939,17 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 미인증 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
+          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
+          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5804,17 +5960,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02</t>
+          <t>P1-11-03</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-01</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08, D-41, D-53</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5824,22 +5980,22 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 qa- 주소(사용자 승인)</t>
+          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
+          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
+          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5850,42 +6006,42 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>P1-12-03</t>
+          <t>P1-11-04</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-01</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>P1-12, D-57</t>
+          <t>P1-11, SCH-05, D-25</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02 메일</t>
+          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
+          <t>1) 다가오는 일정 영역</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
+          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5896,17 +6052,17 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>P1-12-04</t>
+          <t>P1-11-05</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5916,22 +6072,22 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
+          <t>1) 홈 빠른 입력으로 업무 추가</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
+          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5942,42 +6098,42 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>P1-12-05</t>
+          <t>P1-11-06</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>NFR-06, 2.4</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번 입력</t>
+          <t>1) 폭별 카드 배치</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
+          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5988,42 +6144,42 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>P1-12-06</t>
+          <t>P1-11-07</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>2.5 (로딩)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 발급 후 10분 경과</t>
+          <t>1) 느린 네트워크로 홈 진입</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
+          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -6034,12 +6190,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>P1-12-07</t>
+          <t>P1-12-01</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6054,22 +6210,22 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>막 가입한 미인증 계정</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 다시 받기 직후 다시 누르기</t>
+          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
+          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -6080,17 +6236,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>P1-12-08</t>
+          <t>P1-12-02</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-MAIL-01</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08, D-64</t>
+          <t>P1-12, AUTH-08, D-41, D-53</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6100,22 +6256,22 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>로컬(실제 메일 10통 발송 회피)</t>
+          <t>수신 가능한 qa- 주소(사용자 승인)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 직후 자동 발송 1통 포함, 24시간 안에 11번째 발송 요청 2) 첫 발송 24시간 뒤 다시 요청</t>
+          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
+          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -6126,22 +6282,22 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>P1-12-09</t>
+          <t>P1-12-03</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-MAIL-01</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>P1-12, D-64</t>
+          <t>P1-12, D-57</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6151,17 +6307,17 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>코드 2번 발급</t>
+          <t>P1-12-02 메일</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1) 먼저 받은 코드로 인증</t>
+          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
+          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -6172,12 +6328,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>P1-12-10</t>
+          <t>P1-12-04</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6187,27 +6343,27 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
+          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>거부(코드는 계정별), 비로그인 401</t>
+          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6218,42 +6374,42 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>P1-12-12</t>
+          <t>P1-12-05</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>P1-12, P1-13, D-65</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>로컬(운영 IP 제한 회피), 계정 여러 개</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 IP에서 인증 코드·재설정 코드 메일을 합쳐 1시간에 11번 요청 2) X-Client-Ip 헤더 없이 요청</t>
+          <t>1) 틀린 코드 5번 입력</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
+          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6264,17 +6420,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>P1-12-11</t>
+          <t>P1-12-06</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>P1-12</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6284,22 +6440,22 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>인증 완료 계정</t>
+          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입</t>
+          <t>1) 코드 발급 후 10분 경과</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>배너 표시 안 됨</t>
+          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -6310,17 +6466,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>P1-13-01</t>
+          <t>P1-12-07</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>P1-13, SCR-AUTH-02 ④</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6330,22 +6486,22 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
+          <t>1) 코드 다시 받기 직후 다시 누르기</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>/password/forgot 이동</t>
+          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -6356,42 +6512,42 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>P1-13-02</t>
+          <t>P1-12-08</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-65</t>
+          <t>P1-12, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>로컬(실제 메일 10통 발송 회피)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
+          <t>1) 가입 직후 자동 발송 1통 포함, 24시간 안에 11번째 발송 요청 2) 첫 발송 24시간 뒤 다시 요청</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
+          <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -6402,17 +6558,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>P1-13-03</t>
+          <t>P1-12-09</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, D-64</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -6422,22 +6578,22 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>코드 2번 발급</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1) 빈 값·형식 오류 이메일 제출</t>
+          <t>1) 먼저 받은 코드로 인증</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
+          <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -6448,42 +6604,42 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>P1-13-04</t>
+          <t>P1-12-10</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-02</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-41</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 계정</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1) 재설정 메일 확인</t>
+          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
+          <t>거부(코드는 계정별), 비로그인 401</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -6494,42 +6650,42 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>P1-13-05</t>
+          <t>P1-12-12</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, P1-13, D-65</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>로컬(운영 IP 제한 회피), 계정 여러 개</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
+          <t>1) 같은 IP에서 인증 코드·재설정 코드 메일을 합쳐 1시간에 11번 요청 2) X-Client-Ip 헤더 없이 요청</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
+          <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6540,17 +6696,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>P1-13-06</t>
+          <t>P1-12-11</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-38</t>
+          <t>P1-12</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6560,22 +6716,22 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>코드 확인됨</t>
+          <t>인증 완료 계정</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
+          <t>1) 앱 화면 진입</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
+          <t>배너 표시 안 됨</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -6586,17 +6742,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>P1-13-07</t>
+          <t>P1-13-01</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, AUTH-08, D-64</t>
+          <t>P1-13, SCR-AUTH-02 ④</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -6606,22 +6762,22 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
+          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
+          <t>/password/forgot 이동</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -6632,42 +6788,42 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>P1-13-12</t>
+          <t>P1-13-02</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02, 05</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>P1-13, P1-14, D-64</t>
+          <t>P1-13, AUTH-03, D-65</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>로컬, 10회 실패로 잠긴 계정</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1) 잠긴 상태에서 비밀번호 재설정 완료 2) 곧바로 새 비밀번호로 로그인</t>
+          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>잠금이 풀려 바로 로그인 성공</t>
+          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -6678,12 +6834,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>P1-13-08</t>
+          <t>P1-13-03</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6698,22 +6854,22 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번</t>
+          <t>1) 빈 값·형식 오류 이메일 제출</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
+          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -6724,17 +6880,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>P1-13-09</t>
+          <t>P1-13-04</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-MAIL-02</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-13, AUTH-03, D-41</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -6744,22 +6900,22 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>수신 가능한 계정</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
+          <t>1) 재설정 메일 확인</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
+          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -6770,17 +6926,17 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>P1-13-10</t>
+          <t>P1-13-05</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02, 04</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>P1-13, P1-14</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -6790,22 +6946,22 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>잠긴 계정</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 안내의 재설정 링크</t>
+          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>/password/forgot 이동</t>
+          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6816,42 +6972,42 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>P1-13-11</t>
+          <t>P1-13-06</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04, 05</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, NFR-13</t>
+          <t>P1-13, AUTH-03, D-38</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>비로그인, 390px, 오프라인 전환</t>
+          <t>코드 확인됨</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
+          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
+          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -6862,17 +7018,17 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>P1-14-01</t>
+          <t>P1-13-07</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, AUTH-03, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -6882,22 +7038,22 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>qa- 계정</t>
+          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
+          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
+          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -6908,17 +7064,17 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>P1-14-02</t>
+          <t>P1-13-12</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-02, 05</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, P1-14, D-64</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -6928,22 +7084,22 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>qa- 계정</t>
+          <t>로컬, 10회 실패로 잠긴 계정</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
+          <t>1) 잠긴 상태에서 비밀번호 재설정 완료 2) 곧바로 새 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
+          <t>잠금이 풀려 바로 로그인 성공</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6954,17 +7110,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>P1-14-03</t>
+          <t>P1-13-08</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -6974,22 +7130,22 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 해제 시점 이후 로그인</t>
+          <t>1) 틀린 코드 5번</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
+          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -7000,42 +7156,42 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>P1-14-04</t>
+          <t>P1-13-09</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>P1-14, D-61</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>없는 이메일</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 이메일로 10회 이상 실패</t>
+          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
+          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -7046,42 +7202,42 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>P1-14-05</t>
+          <t>P1-13-10</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-02, 04</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09, D-61</t>
+          <t>P1-13, P1-14</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>로컬(운영 IP 차단 위험 회피)</t>
+          <t>잠긴 계정</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
+          <t>1) 잠금 안내의 재설정 링크</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
+          <t>/password/forgot 이동</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
@@ -7092,22 +7248,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>P1-14-06</t>
+          <t>P1-13-11</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-04, 05</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>P1-14, p1-14-springdoc-429</t>
+          <t>NFR-06, NFR-13</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7115,15 +7271,19 @@
           <t>운영</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>비로그인, 390px, 오프라인 전환</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
+          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
+          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -7134,17 +7294,17 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>P1-X-01</t>
+          <t>P1-14-01</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01 (P1 완성)</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7159,17 +7319,17 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>qa- 계정</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
+          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
+          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -7180,22 +7340,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>P1-X-02</t>
+          <t>P1-14-02</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7205,17 +7365,17 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>qa- 계정</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>1) 화면 전환 중 표시</t>
+          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
+          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -7226,17 +7386,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>P1-X-03</t>
+          <t>P1-14-03</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ④</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>NFR-13 (P0 TC-81 재확인)</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -7246,22 +7406,22 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
+          <t>1) 잠금 해제 시점 이후 로그인</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
+          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -7272,22 +7432,22 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>P1-X-04</t>
+          <t>P1-14-04</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ③</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>NFR-13</t>
+          <t>P1-14, D-61</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7297,17 +7457,17 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>없는 이메일</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
+          <t>1) 없는 이메일로 10회 이상 실패</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
+          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -7318,7 +7478,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>P1-X-05</t>
+          <t>P1-14-05</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7328,7 +7488,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>NFR-02, NFR-14</t>
+          <t>P1-14, AUTH-09, D-61</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -7338,22 +7498,22 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>로컬(운영 IP 차단 위험 회피)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
+          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>모두 403 ORIGIN_REJECTED</t>
+          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -7364,7 +7524,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>P1-X-06</t>
+          <t>P1-14-06</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7374,7 +7534,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>D-30</t>
+          <t>P1-14, p1-14-springdoc-429</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -7387,19 +7547,15 @@
           <t>운영</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
+      <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
+          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
+          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -7410,22 +7566,22 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>P1-X-07</t>
+          <t>P1-X-01</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>—(배포)</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>D-56</t>
+          <t>SCR-COM-01 (P1 완성)</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7435,17 +7591,17 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>배포 브랜치 main 전환 후</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
+          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
+          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -7456,22 +7612,22 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>P1-X-08</t>
+          <t>P1-X-02</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>—(배포)</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>P0-09</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7481,17 +7637,17 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
+          <t>1) 화면 전환 중 표시</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
+          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -7502,22 +7658,22 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>P1-X-09</t>
+          <t>P1-X-03</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SCR-SYS-02 ④</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>2.6 문구 말투, D-36</t>
+          <t>NFR-13 (P0 TC-81 재확인)</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7532,12 +7688,12 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면 문구 말투 확인</t>
+          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
+          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -7548,22 +7704,22 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>P1-X-10</t>
+          <t>P1-X-04</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SCR-SYS-02 ③</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>화면정의서 2.5 (키보드·터치)</t>
+          <t>NFR-13</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7578,12 +7734,12 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -7591,10 +7747,286 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-05</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>—(API)</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>NFR-02, NFR-14</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>모두 403 ORIGIN_REJECTED</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-06</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>—(API)</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-07</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>—(배포)</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>D-56</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>배포 브랜치 main 전환 후</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-08</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>—(배포)</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>P0-09</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>브라우저</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-09</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>2.6 문구 말투, D-36</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 새 화면 문구 말투 확인</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-10</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>화면정의서 2.5 (키보드·터치)</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L146"/>
+  <autoFilter ref="A1:L152"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8033,7 +8465,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1-09·10, P1-01, 재검증)</t>
+          <t>2026-10-06 (P1-09·10, P1-01, P1-02, 재검증)</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8489,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>151</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8501,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>기능 117, 사용성 15, 보안 9, 배포 4</t>
+          <t>기능 119, 사용성 19, 보안 9, 배포 4</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8513,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>미실행 111, PASS 21, BLOCKED 12, FAIL 1</t>
+          <t>미실행 103, PASS 32, BLOCKED 13, FAIL 3</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8525,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>P1-01-11 단축키를 꺼도 빠른 입력창 N 안내 표시 (P1-09-01·08은 재검증 PASS)</t>
+          <t>P1-02-07 새로고침 시 태그 지연 삭제 취소(정책 확인), P1-02-09 프로젝트·태그 화면 터치 영역 44px 미만, P1-02-10 태그 편집 후 포커스 유실. 해결: P1-09-01·08, P1-01-11, P1-10-06(453401f, 소스 확인)</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L152"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] [재검증 e39aa14] 콤보박스: 열면 '추천'(Asia/Seoul) + '전체' 418개(UTC-11:00부터 오프셋 순), 'Asia/Seoul (UTC+09:00)' 표기. '서울'·'도쿄'·'뉴욕'·'kolkata'·'seoul' → 1건, '+9' → 10건, '+5:30' → Colombo·Kolkata, '-3' → 36건, 'zzz' → '찾는 시간대가 없어요'. ↓↑로 이동(aria-activedescendant), Enter로 선택·저장, 클릭 선택도 저장, Esc·Tab으로 벗어나면 원래 값. Asia/Calcutta·Saigon·Katmandu·Rangoon·Kiev 등 옛 이름 없음(Kolkata·Ho_Chi_Minh·Kyiv 있음)</t>
+          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] [재검증 e39aa14] 콤보박스: 열면 '추천'(Asia/Seoul) + '전체' 418개(UTC-11:00부터 오프셋 순), 'Asia/Seoul (UTC+09:00)' 표기. '서울'·'도쿄'·'뉴욕'·'kolkata'·'seoul' → 1건, '+9' → 10건, '+5:30' → Colombo·Kolkata, '-3' → 36건, 'zzz' → '찾는 시간대가 없어요'. ↓↑로 이동(aria-activedescendant), Enter로 선택·저장, 클릭 선택도 저장, Esc·Tab으로 벗어나면 원래 값. Asia/Calcutta·Saigon·Katmandu·Rangoon·Kiev 등 옛 이름 없음(Kolkata·Ho_Chi_Minh·Kyiv 있음) / [재검증 0b9713d, 21c8f0e] 목록 폭: 1280px 360px(오른쪽 끝 = 화면-16), 800px 360px, 390px 358px(화면-32), 320px 288px + 긴 이름 11개 말줄임·title에 전체 이름. 모두 한 줄, 가로 스크롤 없음</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1633,7 +1633,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>목록 폭이 좁아(약 210px) 긴 이름이 두 줄로 꺾임 — 보기 관찰. [관찰 2026-10-06: select 418개 나열·옛 이름 섞임]</t>
+          <t>[관찰 2026-10-06: 목록 폭 약 210px라 긴 이름이 두 줄로 꺾임 → 0b9713d로 해결] [관찰 2026-10-06: select에 418개 나열·옛 이름 섞임]</t>
         </is>
       </c>
     </row>
@@ -1962,18 +1962,18 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 토스트가 떠 있는 동안 새로고침 → 삭제 요청이 나가지 않아 태그가 다시 나타남(화면에서는 지웠는데 남음). 같은 상황에서 앱 안 다른 탭(설정 › 일반)으로 이동 → 토스트가 닫힐 때 삭제됨. 이탈 방식에 따라 결과가 다름</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] [재검증 29a1e96] 다른 브라우저 탭으로 전환 → 토스트가 떠 있는 동안에도 삭제 확정(PASS). 새로고침·탭 닫기는 dev:mock에서 확인 불가: mock 응답이 300ms 지연 뒤 localStorage에 쓰므로 페이지가 먼저 사라져 기록되지 않음(코드는 DELETE를 keepalive로 보냄)</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>기대 결과는 사용자 결정(새로고침·탭 닫기에도 삭제 확정, pm 전달 2026-10-06)으로 고침. 실행 시점 코드는 새로고침하면 삭제가 취소돼 FAIL</t>
+          <t>새로고침·탭 닫기 확정은 실서버(운영 배포 뒤 또는 로컬 백엔드)에서 재확인 필요. 최초 FAIL 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -2074,22 +2074,18 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 390px: 가로 스크롤 없음. 그러나 터치 영역이 44px 미만 — 프로젝트 보관 버튼 54x36, 색 선택 34x34, 태그 ✎ 32x32</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-02-09.png</t>
-        </is>
-      </c>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] [재검증 29a1e96] 보이는 크기는 보관 54x36·색 34x34·✎ 32x32 그대로지만 ::after 투명 영역이 54x44·44x44·44x44. 중심에서 상하좌우 21px 지점을 눌러도 같은 버튼(elementFromPoint)</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>설정 일반은 e39aa14에서 44px로 고쳤으나 프로젝트·태그 화면은 그대로</t>
+          <t>[최초 FAIL 증거 evidence/P1/P1-02-09.png]</t>
         </is>
       </c>
     </row>
@@ -2136,40 +2132,40 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 444466e 스냅숏, 2026-10-06] 태그 이름을 Enter로 저장하거나 Esc로 취소하면 포커스가 BODY로 사라짐(편집 칸이 없어지며 포커스 복귀 없음). 삭제 후에도 BODY</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] [재검증 29a1e96] 이름 바꾸고 Enter → 바뀐 태그의 ✎ 버튼으로, Esc → 그 태그 ✎ 버튼으로 포커스 복귀. 빈 이름 문구는 '태그 이름을 적어 주세요'로 바뀜</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>P1-09-08과 같은 유형(키보드 사용자가 위치를 잃음)</t>
+          <t>[최초 FAIL 2026-10-06] 삭제 뒤 포커스는 P1-02-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>P1-02-06</t>
+          <t>P1-02-11</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-SET-08</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>P1-02, SCR-COM-01 ①</t>
+          <t>P1-02, 화면정의서 2.5(키보드)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2179,50 +2175,50 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트 2개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1) 사이드바 프로젝트 클릭</t>
+          <t>1) 태그 ✎ → 삭제를 키보드(Enter)로 실행 2) 포커스 위치 확인</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>/tasks?project=&lt;id&gt;로 이동해 그 프로젝트로 필터, 남은 업무 수 표시</t>
+          <t>지운 태그 자리의 이웃 태그 또는 태그 제목으로 포커스(BODY로 사라지지 않음)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] 사이드바에 프로젝트 목록이 없음</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 14784f0 스냅숏, 2026-10-06] [재검증 4b5f035] ✎ → 삭제를 Enter로: 가운데 태그(결제) → 다음 태그(리뷰) ✎로 포커스, 마지막 태그 → 이전 태그 ✎(4번 연속), 하나 남은 태그(견적) → '태그' 제목(H2)</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>P1-04 구현 전(pm 결정 2026-10-06: 사이드바 프로젝트 목록·/tasks?project= 이동은 업무 목록 화면과 함께 P1-04 frontend 범위)</t>
+          <t>[최초 FAIL 2026-10-06 f32d598] 포커스가 BODY로 감</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>P1-03-01</t>
+          <t>P1-02-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01, 02</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-02, SCR-COM-01 ①</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2237,33 +2233,41 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 프로젝트 2개</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 목록 빠른 입력으로 업무 생성 2) 행 클릭해 상세 패널 열기</t>
+          <t>1) 사이드바 프로젝트 클릭</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>목록에 행 추가, 상세 패널(/tasks/:id) 열림, URL 직접 접근·새로고침도 같은 패널</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
+          <t>/tasks?project=&lt;id&gt;로 이동해 그 프로젝트로 필터, 남은 업무 수 표시</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 캘린더에서 사이드바 '영업, 남은 업무 3개' → /tasks?project=mock-project-sales, 프로젝트 칩 '영업', 3건, 주 메뉴 '업무' aria-current=page. 남은 수는 상태·프로젝트를 바꾸면 바로 갱신</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>P1-03-02</t>
+          <t>P1-03-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-TASK-01, 02</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2288,23 +2292,39 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1) 상세에서 제목 바로 편집, 메모 입력 2) 패널 닫고 다시 열기</t>
+          <t>1) 업무 목록 빠른 입력으로 업무 생성 2) 행 클릭해 상세 패널 열기</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>저장 버튼 없이 자동 저장, 값 유지</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>목록에 행 추가, 상세 패널(/tasks/:id) 열림, URL 직접 접근·새로고침도 같은 패널</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 빠른 입력 'QA 테스트 업무 #리뷰 @개발' Enter → 행 추가(업무 6→7, 토스트 '업무 1개를 추가했어요'+되돌리기), 행 클릭으로 /tasks/:id 패널, 새로고침해도 같은 패널. 결함: 패널이 열리면 목록 제목 폭이 0(1024·1280px), 1440px 124px, 1600px 284px</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-03-01.png</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤 (1024·1280·1440px)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>P1-03-03</t>
+          <t>P1-03-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2314,7 +2334,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-02</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2334,33 +2354,41 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1) 상태 할 일 → 진행 중 → 보류 → 완료로 변경</t>
+          <t>1) 상세에서 제목 바로 편집, 메모 입력 2) 패널 닫고 다시 열기</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>각 변경 저장, 완료 시 완료 일시 기록·표시, 상태 변경마다 되돌리기 토스트</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t>저장 버튼 없이 자동 저장, 값 유지</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 제목 끝에 ' 수정' 추가, 메모 입력 후 Tab → 저장 버튼 없이 저장. 닫고 다시 열어도, 새로고침해도 값 유지</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>P1-03-04</t>
+          <t>P1-03-03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-02, SCR-TASK-01</t>
+          <t>P1-03, TASK-02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2380,33 +2408,45 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 행의 완료 체크</t>
+          <t>1) 상태 할 일 → 진행 중 → 보류 → 완료로 변경</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>완료 처리. 결과 팝오버(SCR-TASK-03)는 P2라 이번에는 없음을 확인</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
+          <t>각 변경 저장, 완료 시 완료 일시 기록·표시, 상태 변경마다 되돌리기 토스트</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 할 일→진행 중→보류→완료 각각 저장(IN_PROGRESS·ON_HOLD·DONE), 완료 시 completedAt 기록(2026-10-06T04:29:27Z). 상태 변경 토스트 없음, 화면에 완료 일시 표시 없음</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>pm 판단 2026-10-06: 필드 자동 저장은 UX-03(되돌리기 토스트) 대상이 아님(설정 화면과 같은 기준), 개정대기에 문구 명확화. 완료 일시 표시는 화면정의서 요구 아님('기록'만)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>P1-03-05</t>
+          <t>P1-03-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-03</t>
+          <t>P1-03, TASK-02, SCR-TASK-01</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2426,23 +2466,35 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1) 우선순위 높음/보통/낮음 변경 2) 마감일 어제·오늘·다음 주 지정</t>
+          <t>1) 목록 행의 완료 체크</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>목록 행에 우선순위 표시, 마감 초과는 빨강, 임박 표시</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+          <t>완료 처리. 결과 팝오버(SCR-TASK-03)는 P2라 이번에는 없음을 확인</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 목록 완료 원 클릭 → '업무 1개를 완료했어요'+되돌리기, 행이 '완료 n개(최근 7일)'로 이동, 결과 팝오버 없음(P2). 되돌리기·체크 해제로 다시 열림. 결함: 완료 뒤 포커스가 BODY로 감</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>P1-03-06</t>
+          <t>P1-03-05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2452,7 +2504,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-05</t>
+          <t>P1-03, TASK-03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2472,23 +2524,39 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1) 진행률 슬라이더를 끌고 키보드 ←→로 조정</t>
+          <t>1) 우선순위 높음/보통/낮음 변경 2) 마감일 어제·오늘·다음 주 지정</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0~100% 10 단위로만 움직임, 목록 행에 진행률 반영</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>목록 행에 우선순위 표시, 마감 초과는 빨강, 임박 표시</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 마감일 어제(10/5) → '마감 초과' 그룹·10/5(월), 오늘 → '오늘', 10/13 → '다음' 10/13(화). 우선순위 높음 표시. 결함: 마감 초과 날짜와 '높음'이 빨강이 아니라 회색(.danger가 .due·.priority보다 앞에 선언됨). 마감일을 키보드로 입력하면 중간값(1013-06-06 등)이 키마다 저장됨</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-03-05.png</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤 (색, 날짜 입력 중간값 저장)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>P1-03-07</t>
+          <t>P1-03-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2498,7 +2566,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-04</t>
+          <t>P1-03, TASK-05</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2513,38 +2581,46 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트·태그 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1) 상세에서 프로젝트 지정, 태그 2개 붙이고 하나 떼기</t>
+          <t>1) 진행률 슬라이더를 끌고 키보드 ←→로 조정</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>목록 행에 프로젝트 칩·태그 반영</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
+          <t>0~100% 10 단위로만 움직임, 목록 행에 진행률 반영</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 슬라이더 min 0·max 100·step 10. →→→← = 10·20·30·20, End 100, Home 0. 마우스로 47% 위치까지 끌면 50. 목록 행 진행률 30%가 반영됨</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>P1-03-08</t>
+          <t>P1-03-07</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01, 02</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01, UX-03</t>
+          <t>P1-03, TASK-04</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2559,38 +2635,50 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 프로젝트·태그 있음</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1) 목록에서 행 선택 후 Delete 키 2) 토스트의 되돌리기 3) 다시 Delete 후 5초 대기</t>
+          <t>1) 상세에서 프로젝트 지정, 태그 2개 붙이고 하나 떼기</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>보관(소프트 삭제) + 되돌리기 토스트, 되돌리기로 복원, 5초 뒤 토스트 사라지고 목록에서 빠짐</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+          <t>목록 행에 프로젝트 칩·태그 반영</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 프로젝트 개발→영업, 태그 #견적·#보고 추가, #리뷰 빼기 → 목록 행 '영업 #견적 #보고', 사이드바 남은 수(개발 3→2, 영업 2→3) 반영. 결함: 태그 빼기(클릭·Enter) 뒤 포커스 BODY</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>P1-03-09</t>
+          <t>P1-03-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-TASK-01, 02</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>P1-03, TASK-01</t>
+          <t>P1-03, TASK-01, UX-03</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2605,28 +2693,40 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 보관된 업무 id</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1) /tasks/&lt;보관된 id&gt; 직접 접속</t>
+          <t>1) 목록에서 행 선택 후 Delete 키 2) 토스트의 되돌리기 3) 다시 Delete 후 5초 대기</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>읽기 전용 + 복원 버튼, 복원하면 목록에 다시 나타남</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>보관(소프트 삭제) + 되돌리기 토스트, 되돌리기로 복원, 5초 뒤 토스트 사라지고 목록에서 빠짐</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 제목 링크에 포커스 → Delete → '업무 1개를 보관했어요'+되돌리기, 되돌리기로 복원. 다시 Delete 후 6.5초 → 토스트 닫히고 목록에서 빠짐. 결함: 보관 뒤 포커스 BODY</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>P1-03-10</t>
+          <t>P1-03-09</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2636,7 +2736,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>P1-03, D-30, D-58 (409)</t>
+          <t>P1-03, TASK-01</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2651,43 +2751,59 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 업무를 두 탭에서</t>
+          <t>로그인 상태(qa- 계정), 보관된 업무 id</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1) 탭 A에서 제목 변경 2) 탭 B에서 진행률 변경</t>
+          <t>1) /tasks/&lt;보관된 id&gt; 직접 접속</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>B 패널 상단에 충돌 띠 + [새로 불러오기], 새로 불러오면 A의 변경이 보임</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>읽기 전용 + 복원 버튼, 복원하면 목록에 다시 나타남</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] /tasks/&lt;보관 id&gt; → 상태·우선순위·프로젝트·태그·진행률·메모 disabled, 제목 readOnly, [복원] → '업무를 복원했어요', 목록에 다시 나타남. 결함: 마감일 칸만 편집 가능 → 바꾸면 '보관한 업무라 바꿀 수 없어요' 토스트, 서버 값은 그대로인데 칸에는 바꾼 값이 남음(복원 뒤에도 패널 10-20, 목록 10/5)</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-03-09.png</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>P1-03-11</t>
+          <t>P1-03-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>P1-03, D-30</t>
+          <t>P1-03, D-30, D-58 (409)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2697,43 +2813,51 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>로그인 상태(qa- 계정), 같은 업무를 두 탭에서</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1) A의 업무 id로 B가 GET·PATCH·DELETE /api/worklog/tasks/{id}</t>
+          <t>1) 탭 A에서 제목 변경 2) 탭 B에서 진행률 변경</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>404(또는 403). 다른 사용자 업무 조회·수정 불가</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+          <t>B 패널 상단에 충돌 띠 + [새로 불러오기], 새로 불러오면 A의 변경이 보임</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 두 탭: A에서 제목 ' A' 추가 → B에서 진행률 → B 패널 위쪽에 노란 띠 '다른 곳에서 먼저 수정됐어요. 이 변경은 저장되지 않았어요'+[새로 불러오기] → A의 제목이 보이고 띠가 사라짐</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>P1-03-12</t>
+          <t>P1-03-11</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>P1-03, 화면정의서 2.5</t>
+          <t>P1-03, D-30</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2743,38 +2867,50 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 0개</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1) /tasks 확인</t>
+          <t>1) A의 업무 id로 B가 GET·PATCH·DELETE /api/worklog/tasks/{id}</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>빈 상태: 빠른 입력 문법 안내</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
+          <t>404(또는 403). 다른 사용자 업무 조회·수정 불가</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>dev:mock에서는 확인할 수 없음(실서버 계정 A·B로 API를 직접 호출해야 함)</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>pm: 병합 후 운영 확인 때</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>P1-03-13</t>
+          <t>P1-03-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-02</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>NFR-06</t>
+          <t>P1-03, 화면정의서 2.5</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2789,43 +2925,51 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>로그인 상태(qa- 계정), 업무 0개</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 업무 상세 열기</t>
+          <t>1) /tasks 확인</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>전체 화면 패널, 가로 스크롤 없음, 닫기 가능</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+          <t>빈 상태: 빠른 입력 문법 안내</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 업무 0개(mock 저장소를 비움): '아직 업무가 없어요 / 위 입력창에 한 줄로 적어 보세요. 예: 견적서 회신 @영업 #결제 !높음 ~금'</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>P1-04-01</t>
+          <t>P1-03-13</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SCR-TASK-01</t>
+          <t>SCR-TASK-02</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>P1-04, TASK-06</t>
+          <t>NFR-06</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2835,28 +2979,40 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 10개 이상</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1) 제목 검색어 입력</t>
+          <t>1) 모바일에서 업무 상세 열기</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>제목에 검색어가 포함된 업무만 표시</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
+          <t>전체 화면 패널, 가로 스크롤 없음, 닫기 가능</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 390px: 패널이 0,0 390x844 전체 화면, 문서 폭 390(가로 스크롤 없음), 닫기로 /tasks</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>패널 닫은 뒤(Esc·×, 1600px도) 포커스가 연 행으로 돌아가지 않고 BODY — 재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>P1-04-02</t>
+          <t>P1-04-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2881,28 +3037,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무 10개 이상</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1) 상태·프로젝트·태그·마감 기간 필터 칩을 각각, 그리고 함께 적용</t>
+          <t>1) 제목 검색어 입력</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>조건 교집합만 표시, 칩에 적용 수 표시</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+          <t>제목에 검색어가 포함된 업무만 표시</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] '리뷰' 입력 → ?q=리뷰, 제목에 포함된 '코드 리뷰 — PR #42'만 남음</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>P1-04-03</t>
+          <t>P1-04-02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2912,7 +3076,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>P1-04, SCR-TASK-01</t>
+          <t>P1-04, TASK-06</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2932,23 +3096,35 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1) 필터 적용 후 새로고침 2) 다른 화면 갔다가 뒤로 가기</t>
+          <t>1) 상태·프로젝트·태그·마감 기간 필터 칩을 각각, 그리고 함께 적용</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>필터가 URL에 남아 그대로 복원</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
+          <t>조건 교집합만 표시, 칩에 적용 수 표시</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 프로젝트 영업 + 태그 #보고·#견적(같은 칩 안은 OR) + 마감 기간 '마감 초과' + 기본 상태(할 일·진행 중) → 교집합 2건, URL ?project=&amp;tag=&amp;tag=&amp;due=overdue</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>칩에는 적용 개수 대신 값이 표시됨('프로젝트: 영업', '태그: #견적 #보고')</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>P1-04-04</t>
+          <t>P1-04-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2958,7 +3134,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>P1-04</t>
+          <t>P1-04, SCR-TASK-01</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2978,23 +3154,31 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1) 결과가 없는 조건 적용 2) 필터 지우기</t>
+          <t>1) 필터 적용 후 새로고침 2) 다른 화면 갔다가 뒤로 가기</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>"조건에 맞는 업무가 없어요" + 필터 지우기, 누르면 전체 목록</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+          <t>필터가 URL에 남아 그대로 복원</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 필터 적용 뒤 새로고침 → 칩·결과 그대로. 캘린더에 갔다가 뒤로 가기 → 같은 URL·필터</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>P1-04-05</t>
+          <t>P1-04-04</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3004,7 +3188,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>P1-04, SCR-TASK-01 ④⑥</t>
+          <t>P1-04</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3024,33 +3208,45 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1) 그룹 기준 마감순/프로젝트/상태 전환 2) 완료 업무 접기 영역 확인</t>
+          <t>1) 결과가 없는 조건 적용 2) 필터 지우기</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>그룹이 기준대로 묶임, 완료 업무는 최근 7일만 접힌 영역에</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
+          <t>"조건에 맞는 업무가 없어요" + 필터 지우기, 누르면 전체 목록</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 공통+#견적 → '조건에 맞는 업무가 없어요' + [필터 지우기] → 전체 7건, URL 비워짐</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>필터 지우기 뒤 포커스 BODY — 재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>P1-05-01</t>
+          <t>P1-04-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-TASK-01</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02</t>
+          <t>P1-04, SCR-TASK-01 ④⑥</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3070,23 +3266,31 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1) 일정 만들기 → 자세히에서 제목·날짜·시작·종료·메모 입력 후 저장 2) 다시 열어 수정 3) 삭제</t>
+          <t>1) 그룹 기준 마감순/프로젝트/상태 전환 2) 완료 업무 접기 영역 확인</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>생성·수정 반영, 삭제는 확인창 없이 + 되돌리기 토스트</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
+          <t>그룹이 기준대로 묶임, 완료 업무는 최근 7일만 접힌 영역에</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 마감순(마감 초과·오늘·이번 주·날짜 없음) / 프로젝트(개발·영업·공통·프로젝트 없음) / 상태(할 일·진행 중), ?group= 유지. 접힌 완료 영역은 최근 7일만(9/20 완료는 빠지고 10/1 완료는 들어감 — 주입해서 확인)</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>P1-05-02</t>
+          <t>P1-05-01</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3096,7 +3300,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02</t>
+          <t>P1-05, SCH-02, D-72</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3116,12 +3320,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1) 종일 일정 생성</t>
+          <t>1) 일정 만들기 → 자세히에서 제목·날짜·시작·종료·메모 입력 후 저장 2) 다시 열어 수정 3) 삭제</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>주·일 보기 종일 행, 월 보기 칩으로 표시</t>
+          <t>생성·수정 반영. 삭제는 확인창 없이 바로 빠지고 되돌리기 토스트, 토스트가 닫힐 때·새로고침·탭 닫기·탭 전환 때 확정(D-72)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3132,7 +3336,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>P1-05-03</t>
+          <t>P1-05-02</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3142,7 +3346,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>P1-05, SCH-02, 2.5</t>
+          <t>P1-05, SCH-02</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3162,12 +3366,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1) 종료를 시작보다 앞으로 지정해 저장</t>
+          <t>1) 종일 일정 생성</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>해당 칸 아래 오류(서버 errors[] 포함), 저장 안 됨</t>
+          <t>주·일 보기 종일 행, 월 보기 칩으로 표시</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3178,7 +3382,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>P1-05-04</t>
+          <t>P1-05-03</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3188,7 +3392,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>P1-05, TIME-06</t>
+          <t>P1-05, SCH-02, 2.5</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3208,12 +3412,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 시간에 일정 2개 생성</t>
+          <t>1) 종료를 시작보다 앞으로 지정해 저장</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>겹침 경고 없이 생성, 주 보기에서 나란히 배치</t>
+          <t>해당 칸 아래 오류(서버 errors[] 포함), 저장 안 됨</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3224,7 +3428,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>P1-05-05</t>
+          <t>P1-05-04</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3234,7 +3438,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>P1-05, D-30, D-58 (409)</t>
+          <t>P1-05, TIME-06</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3249,17 +3453,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 일정을 두 탭에서</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1) A에서 제목 수정 2) B에서 시간 수정</t>
+          <t>1) 같은 시간에 일정 2개 생성</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>B 모달 상단 충돌 띠 + [새로 불러오기]</t>
+          <t>겹침 경고 없이 생성, 주 보기에서 나란히 배치</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3270,7 +3474,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>P1-05-06</t>
+          <t>P1-05-05</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3280,7 +3484,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>P1-05</t>
+          <t>P1-05, D-30, D-58 (409)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3295,17 +3499,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무 1개</t>
+          <t>로그인 상태(qa- 계정), 같은 일정을 두 탭에서</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1) 일정에 업무 연결(검색) 2) 해제 3) 새 업무로 연결</t>
+          <t>1) A에서 제목 수정 2) B에서 시간 수정</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>연결·해제 반영, 일정 프로젝트는 업무를 따름, 업무 상세 연결 일정 목록에도 반영</t>
+          <t>B 모달 상단 충돌 띠 + [새로 불러오기]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3316,12 +3520,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>P1-05-07</t>
+          <t>P1-05-06</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3331,7 +3535,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3341,17 +3545,17 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>로그인 상태(qa- 계정), 업무 1개</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1) A의 일정 id로 B가 조회·수정·삭제</t>
+          <t>1) 일정에 업무 연결(검색) 2) 해제 3) 새 업무로 연결</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>404(또는 403)</t>
+          <t>연결·해제 반영, 일정 프로젝트는 업무를 따름, 업무 상세 연결 일정 목록에도 반영</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3362,22 +3566,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>P1-06-01</t>
+          <t>P1-05-07</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3387,17 +3591,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1) 매일 반복, 종료 날짜 지정 2) 매월 반복, 종료 없음</t>
+          <t>1) A의 일정 id로 B가 조회·수정·삭제</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>지정 범위 회차만 표시, 종료 없음은 먼 미래 달에도 표시</t>
+          <t>404(또는 403)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3408,17 +3612,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>P1-06-02</t>
+          <t>P1-05-08</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-07</t>
+          <t>SCR-CAL-01, 07</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-05, D-70</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3438,12 +3642,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1) 매주 화·목 반복 생성</t>
+          <t>1) 일정을 만든 뒤 설정에서 시간대 변경 2) 서머타임이 있는 시간대(예: America/New_York)에서 3월·11월 전환 주 확인</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>선택한 요일에만 회차 표시</t>
+          <t>일정은 만든 시간대 기준으로 고정되어 표시 시각만 바뀜, 서머타임 전환 주에도 시각이 어긋나지 않음</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3454,17 +3658,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>P1-06-03</t>
+          <t>P1-06-01</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03, D-24</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3479,17 +3683,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1) 한 회차 제목 수정 → 범위 다이얼로그 확인 2) '이 일정만' 3) 다른 회차 수정 → '모든 일정'</t>
+          <t>1) 매일 반복, 종료 날짜 지정 2) 매월 반복, 종료 없음</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>선택지는 '이 일정만 / 모든 일정' 두 개('이후 일정' 없음), 이 일정만은 그 회차만, 모든 일정은 전 회차 변경</t>
+          <t>지정 범위 회차만 표시, 종료 없음은 먼 미래 달에도 표시</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3500,12 +3704,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>P1-06-04</t>
+          <t>P1-06-02</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-08</t>
+          <t>SCR-CAL-07</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3525,17 +3729,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1) 한 회차 삭제 → '이 일정만' 2) 다른 회차 삭제 → '모든 일정'</t>
+          <t>1) 매주 화·목 반복 생성</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>해당 회차만 사라짐 / 반복 전체 사라짐, 되돌리기 토스트</t>
+          <t>선택한 요일에만 회차 표시</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3546,17 +3750,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>P1-06-05</t>
+          <t>P1-06-03</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 08</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>P1-06, SCH-03</t>
+          <t>P1-06, SCH-03, D-24</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3576,23 +3780,35 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1) 주 보기에서 한 회차를 끌어 이동</t>
+          <t>1) 한 회차 제목 수정 → 범위 다이얼로그 확인 2) '이 일정만' 3) 다른 회차 수정 → '모든 일정'</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>범위 선택 다이얼로그가 뜨고, 취소하면 원래 자리로 돌아감</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
+          <t>선택지는 '이 일정만 / 모든 일정' 두 개('이후 일정' 없음), 이 일정만은 그 회차만, 모든 일정은 전 회차 변경</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] '이 일정만' 이동은 그 회차만 바뀜(드래그 경로로 확인). 상세 모달 수정 경로는 미실행</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>실행 중단(사용자 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>P1-06-06</t>
+          <t>P1-06-04</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3602,12 +3818,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>P1-06</t>
+          <t>P1-06, SCH-03</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3617,17 +3833,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1) 범위 다이얼로그에서 Esc·키보드로 선택</t>
+          <t>1) 한 회차 삭제 → '이 일정만' 2) 다른 회차 삭제 → '모든 일정'</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Esc로 닫힘(변경 없음), 키보드만으로 선택·확인 가능</t>
+          <t>해당 회차만 사라짐 / 반복 전체 사라짐, 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3638,17 +3854,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>P1-07-01</t>
+          <t>P1-06-05</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-01, 08</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-06, SCH-03, D-71</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3663,43 +3879,55 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 매주 반복 일정</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1) 사이드바 캘린더 진입 2) 주 보기 구성 확인</t>
+          <t>1) 주 보기에서 매주 반복 일정의 한 회차를 끌어 이동 → 범위 다이얼로그 2) 취소 3) 다시 끌어 '모든 일정' 4) 되돌리기</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>기본 주 보기(/calendar/week/:date), 오늘 열 강조, 기본 08~19시·스크롤로 0~24시, 현재 시각선, 종일 행</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
+          <t>범위 선택 다이얼로그, 취소하면 원위치. '모든 일정'이면 매주 반복은 요일도 함께 밀림. 되돌리기는 원래 시각만 복원(회차별 변경은 초기화, D-71)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] 실제 마우스 드래그: 반복 '팀 스탠드업' 회차를 끌면 '반복 일정을 옮길까요?' 대화상자(이 일정만/모든 일정, 취소/확인, role=alertdialog). 취소 → 원위치, 포커스는 캘린더 제목(H1). '이 일정만' → 그 회차만 11:00으로. '모든 일정' → 4회차 모두 11:00 + '모든 일정을 옮겼어요 [되돌리기]'</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>후반부 결과가 불안정: '모든 일정' 뒤 Ctrl+Z로 원래 시각 복원이 안 됐고, 이후 같은 드래그가 대화상자를 열지 않음. 화면 상태가 꼬였을 가능성이 있어 결함으로 보내지 않고 새 브라우저로 재실행 필요. 실행 중단(사용자 지시). 월요일(10/5 대체공휴일)에는 스탠드업 회차가 없음 — 반복 규칙 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>P1-07-02</t>
+          <t>P1-06-06</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01~05</t>
+          <t>SCR-CAL-08</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-06</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3714,12 +3942,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1) 보기 전환 버튼으로 일·주·월·연·목록 이동 2) 각 URL로 직접 접속·새로고침</t>
+          <t>1) 범위 다이얼로그에서 Esc·키보드로 선택</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>각 보기가 정의된 경로로 열리고 새로고침해도 유지</t>
+          <t>Esc로 닫힘(변경 없음), 키보드만으로 선택·확인 가능</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3730,7 +3958,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>P1-07-03</t>
+          <t>P1-07-01</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3740,7 +3968,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, UX-09</t>
+          <t>P1-07, SCH-01, frontend2 P1-07 완료 보고(pm 전달 2026-10-06)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3755,38 +3983,50 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 한글 입력 상태 포함</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1) 그리드에 포커스를 두고 D·W·M·Y·A, T, J/K, C, P 누르기 2) 한글 입력 상태(ㅇ·ㅈ 등)로 같은 키</t>
+          <t>1) 사이드바 캘린더 진입 2) 주 보기 구성 확인</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>보기 전환·오늘·이전/다음·만들기·업무 패널이 동작, 한글 상태에서도 동작(event.code)</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
+          <t>/calendar → /calendar/week/오늘(모바일은 day). 상단 바(기간 제목·오늘·이전/다음·보기 전환), 좌측(일정 만들기·미니 달력·프로젝트 필터), 0~24시 그리드(처음 08시로 스크롤), 종일 행, 현재 시각선, 오늘 열 강조, 주말·공휴일 음영</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] /calendar → /calendar/week/2026-10-06. 상단 바(2026년 10월 5일 – 11일·오늘·‹ ›·일 주 월 연 목록), 좌측(일정 만들기·미니 달력·프로젝트 필터 4개), 종일 행, 시간 그리드(08:00부터 보임), 오늘 열 강조. 10/5 '대체공휴일(개천절)'·10/9 '한글날' 빨강 표시</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 색: 그리드의 일정 블록이 모두 같은 보라 점선으로 보임 — mock 일정에 projectId가 없는지 확인 필요(다음 실행)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>P1-07-04</t>
+          <t>P1-07-02</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, SCR-SET-02</t>
+          <t>SCR-CAL-01~05</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>P1-07, UX-09, WCAG 2.1.4, D-60</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3806,12 +4046,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창에 포커스를 두고 D·W 입력 2) 설정에서 단축키 끄기 후 캘린더에서 D·W</t>
+          <t>1) 보기 전환으로 일·주·월·연·목록 이동 2) /calendar/day|week|month|year/:date, /calendar/list 직접 접속·새로고침 3) 이전/다음·오늘 후 뒤로 가기</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>입력창·모달에서는 글자만 입력되고 보기 안 바뀜, 끄면 단일 문자 단축키 모두 무시. 설정은 다른 브라우저에서 로그인해도 유지(identity 저장, D-60)</t>
+          <t>각 보기가 정의된 경로로 열리고 새로고침·뒤로 가기에도 같은 상태(URL이 상태 기준)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3822,17 +4062,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>P1-07-05</t>
+          <t>P1-07-03</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 03</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, D-25</t>
+          <t>P1-07, SCH-01, UX-09, frontend2 P1-07 완료 보고(pm 전달 2026-10-06)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3847,17 +4087,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 한글 입력 상태 포함</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1) 공휴일이 있는 주·월로 이동(예: 2026-10-09 한글날)</t>
+          <t>1) 그리드에 포커스를 두고 D·W·M·Y·A, T, J/K, C 누르기 2) 한글 입력 상태로 같은 키 3) P 키</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>요일 머리·날짜가 빨강 + 공휴일 명칭, 주말·공휴일 음영</t>
+          <t>보기 전환·오늘·이전/다음·만들기 동작, 한글 상태에서도 동작(event.code). P(업무 패널)는 P1-08 범위 — 완료 보고에 없어 동작 여부만 기록</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3868,17 +4108,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>P1-07-06</t>
+          <t>P1-07-04</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-01, SCR-SET-02</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, UX-09, WCAG 2.1.4, D-60</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3893,17 +4133,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 프로젝트 2개 일정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1) 좌측 프로젝트 필터 토글</t>
+          <t>1) 입력창에 포커스를 두고 D·W 입력 2) 설정에서 단축키 끄기 후 캘린더에서 D·W</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>끈 프로젝트의 일정이 숨겨짐, 다시 켜면 표시</t>
+          <t>입력창·모달에서는 글자만 입력되고 보기 안 바뀜, 끄면 단일 문자 단축키 모두 무시. 설정은 다른 브라우저에서 로그인해도 유지(identity 저장, D-60)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3914,17 +4154,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>P1-07-07</t>
+          <t>P1-07-05</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-01, 03</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, SCH-01, D-25 (shared/holidays/KR.json 2026·2027)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3944,12 +4184,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1) 미니 달력에서 다른 주 날짜 클릭</t>
+          <t>1) 2026-10-09(한글날)·2026-12-25가 있는 주·월로 이동 2) 연 보기에서 같은 날 확인</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>해당 주로 이동, 미니 달력에 이번 주 강조</t>
+          <t>요일 머리·날짜가 빨강 + 공휴일 명칭, 주말·공휴일 음영</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3960,17 +4200,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>P1-07-08</t>
+          <t>P1-07-06</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01, 06</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01, SCH-04</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3985,17 +4225,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 프로젝트 2개 일정</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1) 빈 칸 클릭 2) 빈 칸 드래그(10:00~11:45)</t>
+          <t>1) 좌측 프로젝트 필터 토글</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>클릭은 1시간, 드래그는 15분 단위로 맞춘 범위의 빠른 생성 팝오버</t>
+          <t>끈 프로젝트의 일정이 숨겨지고 다시 켜면 표시, 숨김 상태는 새로고침 뒤에도 유지(브라우저 저장), 프로젝트 없는 일정은 늘 보임</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -4006,7 +4246,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>P1-07-09</t>
+          <t>P1-07-07</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4016,7 +4256,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-04, UX-03</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4031,17 +4271,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 일정 1개</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1) 블록을 다른 시간·요일로 끌기 2) 아래 끝을 끌어 길이 조절 3) 되돌리기</t>
+          <t>1) 미니 달력에서 다른 주 날짜 클릭</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>15분 단위로 이동·조절, 되돌리기 토스트로 원복</t>
+          <t>해당 주로 이동, 미니 달력에 이번 주 강조</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -4052,17 +4292,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>P1-07-10</t>
+          <t>P1-07-08</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-02</t>
+          <t>SCR-CAL-01, 06</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, SCH-01, SCH-04</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4077,38 +4317,46 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 시간 없는 기록이 있는 날(P2 전이면 생략)</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1) 일 보기 구성 확인</t>
+          <t>1) 빈 칸 클릭 2) 빈 칸 드래그(10:00~11:45)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>하루 그리드, 우측 '이날의 기록' 패널</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
+          <t>클릭은 1시간, 드래그는 15분 단위로 맞춘 범위로 빠른 생성 팝오버(CAL-06). 실제 브라우저 마우스 드래그로 확인(jsdom 미확인 영역)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] 실제 마우스 드래그: 목요일 12:00 칸에서 13:30 칸까지 끌기 → '새 일정 10월 8일 (목) 12:00–13:45' 빠른 생성 팝오버(15분 단위), 제목 입력·Enter → '일정을 만들었어요' 토스트와 블록 생성</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>P1-07-11</t>
+          <t>P1-07-09</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-03</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>P1-07, SCH-01</t>
+          <t>P1-07, SCH-04, UX-03</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4123,33 +4371,45 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 하루에 일정 5개</t>
+          <t>로그인 상태(qa- 계정), 일정 1개</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1) 월 보기 확인 2) +n개 더보기 3) 날짜 숫자 클릭 4) 빈 칸 클릭 5) 칩을 다른 날로 끌기</t>
+          <t>1) 블록을 다른 시간·요일로 끌기 2) 아래 끝을 끌어 길이 조절 3) 되돌리기 4) 종일 행에서 종일 일정 끌기</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>6주×7일, 칩 최대 3개 + '+2개 더보기' 팝오버, 숫자 → 일 보기, 빈 칸 → 종일 빠른 생성, 칩 이동</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
+          <t>15분 단위로 이동·조절, 되돌리기 토스트로 원복, 종일 막대도 날짜 이동. 실제 브라우저 마우스 드래그로 확인</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] 실제 마우스 드래그: 블록을 하루 오른쪽·24px 아래로 → 금 12:30–14:15로 이동(30분, 15분 단위) + '일정을 옮겼어요 [되돌리기]'. 아래 끝 손잡이(높이 8px)를 40px 끌기 → 15:00으로 길이 조절, 입력창 밖 Ctrl+Z → 14:15로 복원, 위로 크게 끌면 최소 15분(12:30–12:45). 종일 막대 '부산 출장'을 하루 왼쪽으로 끌면 이동은 되나 되돌리기 토스트가 보이지 않았음</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>종일 막대 이동의 되돌리기 토스트 유무는 같은 실행 후반에 결과가 불안정해(아래 P1-06-05 비고) 재확인 필요. 실행 중단(사용자 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>P1-07-12</t>
+          <t>P1-07-10</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-04</t>
+          <t>SCR-CAL-02</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4174,12 +4434,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1) 연 보기 확인 2) 날짜 클릭 3) 월 이름 클릭 4) 390px</t>
+          <t>1) 일 보기 구성 확인 2) 빈 칸 클릭·드래그</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>12개월(데스크톱 4×3, 모바일 1열), 일정 밀도 점 3단계, 날짜 → 일 보기, 월 이름 → 월 보기</t>
+          <t>하루 시간 그리드(주 보기와 같은 조작). '이날의 기록' 패널은 P2라 없음</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4190,12 +4450,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>P1-07-13</t>
+          <t>P1-07-11</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-05</t>
+          <t>SCR-CAL-03</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4215,17 +4475,17 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 반복 일정 포함</t>
+          <t>로그인 상태(qa- 계정), 하루에 일정 5개</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 보기 확인 2) 아래로 스크롤 3) 지난 일정 보기</t>
+          <t>1) 월 보기 확인 2) +n개 더보기 3) 날짜 숫자 클릭 4) 빈 칸 클릭 5) 칩을 다른 날로 끌기</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>오늘부터 날짜별 그룹, 반복 아이콘, 무한 스크롤로 다음 일정 로드, 지난 일정 표시</t>
+          <t>6주×7일, 칩 최대 3개 + '+n개' 팝오버, 날짜 숫자 → 일 보기, 빈 칸 → 종일 빠른 생성, 칩을 끌어 다른 날로 이동(실제 브라우저 드래그). 일지 상태 점은 P3라 없음</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4236,22 +4496,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>P1-07-14</t>
+          <t>P1-07-12</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-05</t>
+          <t>SCR-CAL-04</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>P1-07</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4261,17 +4521,17 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>일정 없는 새 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 보기</t>
+          <t>1) 연 보기 확인 2) 날짜 클릭 3) 월 이름 클릭 4) 390px</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>"다가오는 일정이 없어요"</t>
+          <t>12개월(데스크톱 4×3, 모바일 1열), 일정 밀도 점 3단계(없음/1~2/3+), 날짜 → 일 보기, 월 이름 → 월 보기. 일지 상태 표시는 P3라 없음</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4282,22 +4542,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>P1-07-15</t>
+          <t>P1-07-13</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01~05</t>
+          <t>SCR-CAL-05</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, 2.4</t>
+          <t>P1-07, SCH-01</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4307,17 +4567,17 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px·800px</t>
+          <t>로그인 상태(qa- 계정), 반복 일정 포함</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 캘린더 진입 2) 태블릿 폭</t>
+          <t>1) 목록 보기 확인 2) 아래로 계속 스크롤 3) 지난 일정 보기</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>모바일 기본 보기는 일 보기, 가로 스크롤 없음. 태블릿은 업무 패널 접힘</t>
+          <t>오늘부터 날짜별 그룹, 반복 아이콘, 스크롤하면 30일씩 더 불러옴(400일 상한), 지난 일정 표시</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4328,22 +4588,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>P1-07-16</t>
+          <t>P1-07-14</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-01</t>
+          <t>SCR-CAL-05</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>P1-07, D-37</t>
+          <t>P1-07</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4353,17 +4613,17 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>일정 없는 새 계정</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1) 연말·연초(12월 마지막 주) 주 보기</t>
+          <t>1) 목록 보기</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>연도가 바뀌는 주가 끊기지 않고 표시, 1/1 공휴일 표시</t>
+          <t>"다가오는 일정이 없어요"</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4374,22 +4634,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>P1-08-01</t>
+          <t>P1-07-15</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-01~05</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCH-07</t>
+          <t>NFR-06, 2.4</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4399,17 +4659,17 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 일정 없는 업무(마감 초과·날짜 없음 포함)</t>
+          <t>로그인 상태(qa- 계정), 390px·800px</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1) 캘린더 업무 패널 확인</t>
+          <t>1) 모바일에서 캘린더 진입 2) 태블릿 폭</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>기본 열림, 마감순, 마감 초과 강조, 프로젝트 칩·마감 표시, 날짜 없는 업무 접힘</t>
+          <t>모바일 기본 보기는 일 보기, 가로 스크롤 없음. 태블릿은 업무 패널 접힘</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4420,17 +4680,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>P1-08-02</t>
+          <t>P1-07-16</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09, 01</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCH-04, SCH-07</t>
+          <t>P1-07, D-37</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4450,12 +4710,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1) 패널 카드를 그리드 10:15 칸으로 끌기</t>
+          <t>1) 연말·연초(12월 마지막 주) 주 보기</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>10:15~11:15 일정 생성(15분 단위), 업무와 연결, 패널에서 빠짐</t>
+          <t>연도가 바뀌는 주가 끊기지 않고 표시, 1/1 공휴일 표시</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4466,22 +4726,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>P1-08-03</t>
+          <t>P1-07-17</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-01~04</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>P1-08</t>
+          <t>P1-07, 화면정의서 2.5(44px), pm 예외 판단</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4491,17 +4751,17 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 모든 업무가 배치됨</t>
+          <t>로그인 상태(qa- 계정), 390px·1280px</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1) 패널 확인</t>
+          <t>1) 44px 예외 5가지(미니 달력 날짜·연 보기 날짜·월 칸 칩·종일 막대·짧은 블록)의 대체 경로 확인 2) 그 밖의 버튼 터치 영역 측정</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>"배치할 업무가 없어요"</t>
+          <t>미니 달력 → 이전/다음·보기 전환, 연 보기 날짜 → 월 이름 버튼·월 보기, 월 칩 → 목록·일 보기, 종일 막대·짧은 블록 → Tab+Enter/Space로 상세 모달·목록 보기. 나머지 버튼은 44px 이상. 예외 5가지는 24x24px 이상이거나, 작으면 지름 24px 원이 이웃과 겹치지 않는 간격(WCAG 2.5.8, erp-design 확정 2026-10-06) — 15분 블록·월 칸 칩 크기·간격 측정값 기록</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4512,22 +4772,22 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>P1-08-04</t>
+          <t>P1-07-18</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-09</t>
+          <t>SCR-CAL-06, 07</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>P1-08, UX-09</t>
+          <t>P1-07, 화면정의서 2.5(키보드)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4542,12 +4802,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1) P 키로 패널 닫기·열기 2) 패널 안 빠른 입력으로 업무 추가</t>
+          <t>1) 빠른 생성 팝오버·상세 모달·'+n개' 팝오버를 열고 닫기 2) 상세 모달에서 일정 삭제</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>토글 동작, 추가한 업무가 패널에 나타남</t>
+          <t>닫으면 연 요소로 포커스 복귀, 연 요소가 사라졌으면(삭제) 캘린더 제목으로</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4558,22 +4818,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>P1-08-05</t>
+          <t>P1-07-19</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-CAL-01, 02</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>P1-08, SCR-HOME-01 ④</t>
+          <t>P1-07, D-76 (WCAG 2.2 SC 2.5.8, erp-design 확정)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4583,17 +4843,17 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 15분 일정 2개를 이어서(예: 10:00~10:15, 10:15~10:30)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1) 홈 남은 업무를 일정 영역으로 끌기</t>
+          <t>1) 주·일 보기에서 15분 블록 높이·위치 측정 2) 이어진 짧은 블록 배치 확인 3) 블록의 시간 글자·aria-label 확인</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>P1 범위 확인: 오늘 일정 영역(③)은 P2라 이번에는 대상 없음 → N/A 예상</t>
+          <t>15분 블록이 30분 블록과 같은 높이(22px, 위아래 1px 틈)로 그려지고 이어진 짧은 블록은 나란히 배치됨. 시간 글자·aria-label은 실제 시각(10:00~10:15)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4604,17 +4864,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>P1-09-01</t>
+          <t>P1-07-20</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-01, 02</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62, D-67</t>
+          <t>P1-07, D-76 (WCAG 2.2 SC 2.5.8, erp-design 확정)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4629,50 +4889,38 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 이어진 일정 2개</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1) '14-16 견적서 작성 @영업 #긴급 !높음 ~금' 입력</t>
+          <t>1) 두 블록 사이 1px 틈을 클릭 2) 같은 틈에서 드래그 시작</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>칩: 시간(오늘 14:00–16:00) · 프로젝트 @영업 · 태그 #긴급 · 우선순위 높음 · 마감 이번 주 금요일 실제 날짜, 종류별 색 구분, 제목 '견적서 작성'</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] '14-16 견적서 작성 @영업 #긴급 !높음 ~금' → 칩 '오늘 14:00–16:00'(accent) · '영업'(프로젝트 색 P2 주황) · '#긴급 새'(점선 테두리, 없는 태그) · '우선순위 높음'(빨강 계열) · '마감 10/9(금)'(회색), 안내 '일정과 업무가 함께 만들어져요'. 있는 태그 '#견적'은 흰 바탕 실선 테두리로 프로젝트 칩과 구분</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>빈 칸 동작(빠른 생성 팝오버, 드래그로 새 일정 만들기 등)이 일어나지 않음</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>[이전: 2026-10-06 기호 변경 전 코드에서 FAIL→재검증 PASS, 증거 evidence/P1/P1-09-01.png]</t>
-        </is>
-      </c>
+      <c r="L84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>P1-09-02</t>
+          <t>P1-07-21</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-01, 02</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04</t>
+          <t>P1-07, D-76 (WCAG 2.2 SC 2.5.8, erp-design 확정)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4692,50 +4940,38 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
+          <t>1) 23:45~24:00 일정 만들기 2) 위치 확인 3) 23:30~23:45 일정을 추가해 배치 확인</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>23:45 시작 15분 블록이 23:30 위치에 그려져 그리드 밖으로 넘치지 않음. 23:30에 다른 일정이 있으면 나란히 배치됨. 시간 글자·aria-label은 23:45</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>Enter 저장: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>P1-09-03</t>
+          <t>P1-07-22</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-03</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-07, D-76 (WCAG 2.2 SC 2.5.8, erp-design 확정)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4745,50 +4981,38 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 하루에 일정 3개인 날·5개인 날, 390px·1280px</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
+          <t>1) 월 보기에서 칩·더보기 높이 측정 2) 칸 안에 들어가는 개수 확인</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>칩·더보기 최소 24px. 3개인 날은 칩 3개, 4개 이상인 날은 칩 2개+더보기가 칸 안에 들어감(넘치거나 잘리지 않음)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
-        </is>
-      </c>
+      <c r="L86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>P1-09-04</t>
+          <t>P1-07-23</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-03</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>P1-09, D-67</t>
+          <t>P1-07, D-76 (WCAG 2.2 SC 2.5.8, erp-design 확정)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4803,55 +5027,43 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 일정 많은 날</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 프로젝트 '@신규' 입력</t>
+          <t>1) 날짜 숫자·더보기 주변 이웃 칩·빈 칸을 클릭 2) elementFromPoint로 투명 영역 범위 확인</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 @신규프로젝트' → '+ 새 프로젝트 "신규프로젝트" 만들기' 칩(button). 키보드 Enter로 눌러 생성 → 프로젝트 칩(색 P4)으로 바뀜, 설정 프로젝트 목록에 추가. '@Alpha' 만든 뒤 '@alpha'는 기존 Alpha로 인식(대소문자 무시)</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>날짜 숫자·더보기의 투명 영역이 이웃 칩·빈 칸의 클릭을 가로채지 않음(이웃을 누르면 이웃 동작)</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>업무 저장(Enter)은 API 연결 전이라 확인 안 함</t>
-        </is>
-      </c>
+      <c r="L87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>P1-09-13</t>
+          <t>P1-07-24</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-01</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>P1-09, TASK-04, D-67</t>
+          <t>P1-07, D-77 (모바일 주 보기는 훑어보기 전용)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4861,50 +5073,38 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 390px, 일정 있는 주</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1) '보고서 #긴급 #검토' 입력 2) 없는 태그 '#새태그' 입력 3) Enter 저장 후 업무 상세 확인</t>
+          <t>1) 390px에서 주 보기로 전환 2) 하루 칸을 누르기·Tab+Enter 3) 일정 블록을 끌고, 빈 칸을 누르기</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>태그 칩 2개(#긴급·#검토), 프로젝트 칩과 다른 색. 저장하면 업무에 태그 2개 연결(여러 개 허용 — 구현 범위 확인), 없는 태그 처리 방식은 구현 확인</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 #견적 #결제 #견적' → 태그 칩 2개(같은 이름 하나로), '#새태그'·'#1번' → 점선 '새' 칩. 규칙에 안 맞는 'C# 공부'·'메일 a@b.com 확인'·'보고서 @ #'은 칩 없이 제목에 남음. '@개발 @영업'은 처음 것(개발)만 프로젝트</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>하루 칸 전체가 버튼(접근 가능한 이름에 날짜), 누르면 그 날의 일 보기로 이동. 블록은 표시만 되고 끌어 옮기기·빈 칸 새 일정 만들기는 일어나지 않음</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>표시는 확인. 저장 시 태그 생성·연결은 Enter 저장 API 연결 전</t>
-        </is>
-      </c>
+      <c r="L88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>P1-09-05</t>
+          <t>P1-08-01</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>P1-09</t>
+          <t>P1-08, SCH-07</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4919,46 +5119,38 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 일정 없는 업무(마감 초과·날짜 없음 포함)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '@영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
+          <t>1) 캘린더 업무 패널 확인</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] Esc → 입력 비움, 빈 입력 Enter 무시, '@영업 #견적'처럼 제목이 비면 칩과 '할 일 이름을 적어 주세요'</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>기본 열림, 마감순, 마감 초과 강조, 프로젝트 칩·마감 표시, 날짜 없는 업무 접힘</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>P1-09-12</t>
+          <t>P1-08-02</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09, 01</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCR-COM-02 주요 동작</t>
+          <t>P1-08, SCH-04, SCH-07</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4978,45 +5170,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1) 해석 칩 클릭</t>
+          <t>1) 패널 카드를 그리드 10:15 칸으로 끌기</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>그 값만 바꾸는 드롭다운</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>10:15~11:15 일정 생성(15분 단위), 업무와 연결, 패널에서 빠짐</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>P1-09-06</t>
+          <t>P1-08-03</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-08</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5031,50 +5211,38 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 모든 업무가 배치됨</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
+          <t>1) 패널 확인</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>"배치할 업무가 없어요"</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
-        </is>
-      </c>
+      <c r="L91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>P1-09-07</t>
+          <t>P1-08-04</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>UX-09</t>
+          <t>P1-08, UX-09</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5094,41 +5262,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
+          <t>1) P 키로 패널 닫기·열기 2) 패널 안 빠른 입력으로 업무 추가</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>토글 동작, 추가한 업무가 패널에 나타남</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>P1-09-11</t>
+          <t>P1-08-05</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>P1-09, UX-09</t>
+          <t>P1-08, SCR-HOME-01 ④</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5138,7 +5298,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5148,45 +5308,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
+          <t>1) 홈 남은 업무를 일정 영역으로 끌기</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>P1 범위 확인: 오늘 일정 영역(③)은 P2라 이번에는 대상 없음 → N/A 예상</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
-        </is>
-      </c>
+      <c r="L93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>P1-09-08</t>
+          <t>P1-09-01</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SCR-ONB-02</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-67</t>
+          <t>P1-09, REC-04, D-62, D-67</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5206,17 +5354,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
+          <t>1) '14-16 견적서 작성 @영업 #긴급 !높음 ~금' 입력</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>문법 표(시간·@프로젝트·#태그·!우선순위·~마감·날짜(시간 없이 쓰면 마감일))와 예시 3개(새 기호), 예시 클릭 시 입력창에 채워짐, Esc로 닫으면 ? 버튼으로 포커스 복귀</t>
+          <t>칩: 시간(오늘 14:00–16:00) · 프로젝트 @영업 · 태그 #긴급 · 우선순위 높음 · 마감 이번 주 금요일 실제 날짜, 종류별 색 구분, 제목 '견적서 작성'</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] 문법 표: 시간 / @영업 프로젝트(없으면 새로 만들지 물어봐요) / #결제 #견적 태그(여러 개 가능, 없으면 저장할 때 만들어요) / !높음·!낮음 / ~금·~10/12 마감일 / 오늘·내일·다음주 수요일 날짜(시간 없이 쓰면 마감일). 예시 3개 @·# 기호로 갱신. Esc로 닫으면 ? 버튼으로 포커스</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] '14-16 견적서 작성 @영업 #긴급 !높음 ~금' → 칩 '오늘 14:00–16:00'(accent) · '영업'(프로젝트 색 P2 주황) · '#긴급 새'(점선 테두리, 없는 태그) · '우선순위 높음'(빨강 계열) · '마감 10/9(금)'(회색), 안내 '일정과 업무가 함께 만들어져요'. 있는 태그 '#견적'은 흰 바탕 실선 테두리로 프로젝트 칩과 구분</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -5227,24 +5375,24 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>[이전 FAIL 증거 evidence/P1/P1-09-08.png]</t>
+          <t>[이전: 2026-10-06 기호 변경 전 코드에서 FAIL→재검증 PASS, 증거 evidence/P1/P1-09-01.png]</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>P1-09-09</t>
+          <t>P1-09-02</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-06</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCH-02</t>
+          <t>P1-09, REC-04</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5259,17 +5407,17 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 @영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
+          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 토글 기본 켜짐(끄면 일정만), Esc는 임시 블록 제거</t>
+          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5285,14 +5433,14 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
+          <t>Enter 저장: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>P1-09-10</t>
+          <t>P1-09-03</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5302,7 +5450,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>P1-09, REC-04, D-62</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5317,50 +5465,50 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 포커스</t>
+          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 상위 3개 제안</t>
+          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
+          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>P1-10-01</t>
+          <t>P1-09-04</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-09, D-67</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5380,17 +5528,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
+          <t>1) 없는 프로젝트 '@신규' 입력</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
+          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 @신규프로젝트' → '+ 새 프로젝트 "신규프로젝트" 만들기' 칩(button). 키보드 Enter로 눌러 생성 → 프로젝트 칩(색 P4)으로 바뀜, 설정 프로젝트 목록에 추가. '@Alpha' 만든 뒤 '@alpha'는 기존 Alpha로 인식(대소문자 무시)</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -5401,24 +5549,24 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎) / [재검증 a5bb168] vite dev에서도 입력창 Ctrl+K → 팔레트 검색 입력에 포커스, Esc로 닫히고 빠른 입력창 값 유지(관찰 ① 해소)</t>
+          <t>업무 저장(Enter)은 API 연결 전이라 확인 안 함</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>P1-10-02</t>
+          <t>P1-09-13</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-09, TASK-04, D-67</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5438,45 +5586,45 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
+          <t>1) '보고서 #긴급 #검토' 입력 2) 없는 태그 '#새태그' 입력 3) Enter 저장 후 업무 상세 확인</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
+          <t>태그 칩 2개(#긴급·#검토), 프로젝트 칩과 다른 색. 저장하면 업무에 태그 2개 연결(여러 개 허용 — 구현 범위 확인), 없는 태그 처리 방식은 구현 확인</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 #견적 #결제 #견적' → 태그 칩 2개(같은 이름 하나로), '#새태그'·'#1번' → 점선 '새' 칩. 규칙에 안 맞는 'C# 공부'·'메일 a@b.com 확인'·'보고서 @ #'은 칩 없이 제목에 남음. '@개발 @영업'은 처음 것(개발)만 프로젝트</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
+          <t>표시는 확인. 저장 시 태그 생성·연결은 Enter 저장 API 연결 전</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>P1-10-08</t>
+          <t>P1-09-05</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01, SCR-COM-03 ②</t>
+          <t>P1-09</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5491,50 +5639,46 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 제목 일부·일지 내용 입력</t>
+          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '@영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>업무 검색·일지 검색 결과 그룹</t>
+          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] Esc → 입력 비움, 빈 입력 Enter 무시, '@영업 #견적'처럼 제목이 비면 칩과 '할 일 이름을 적어 주세요'</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>P1-10-03</t>
+          <t>P1-09-12</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-09, SCR-COM-02 주요 동작</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5554,45 +5698,45 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
+          <t>1) 해석 칩 클릭</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
+          <t>그 값만 바꾸는 드롭다운</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
+          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>P1-10-04</t>
+          <t>P1-09-06</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>P1-09, REC-04, D-62</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5612,45 +5756,45 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
+          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
+          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>P1-10-09</t>
+          <t>P1-09-07</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03, UX-09</t>
+          <t>UX-09</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5670,17 +5814,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
+          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
+          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -5694,42 +5838,42 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>P1-10-05</t>
+          <t>P1-09-11</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>P1-09, UX-09</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 업무 보관</t>
+          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>토스트가 하단 탭 위에 표시</t>
+          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5745,24 +5889,24 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
+          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>P1-10-06</t>
+          <t>P1-09-08</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-ONB-02</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-04</t>
+          <t>P1-09, REC-04, D-67</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5777,22 +5921,22 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 직후 첫 화면</t>
+          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
+          <t>문법 표(시간·@프로젝트·#태그·!우선순위·~마감·날짜(시간 없이 쓰면 마감일))와 예시 3개(새 기호), 예시 클릭 시 입력창에 채워짐, Esc로 닫으면 ? 버튼으로 포커스 복귀</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>[재검증 2026-10-06, 444466e 소스 확인] 홈 빈 상태 안내가 '시간·@프로젝트·#태그·!우선순위·~마감을 같이 적으면 알아서 나눠 저장해요.'로 바뀜(453401f)</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] 문법 표: 시간 / @영업 프로젝트(없으면 새로 만들지 물어봐요) / #결제 #견적 태그(여러 개 가능, 없으면 저장할 때 만들어요) / !높음·!낮음 / ~금·~10/12 마감일 / 오늘·내일·다음주 수요일 날짜(시간 없이 쓰면 마감일). 예시 3개 @·# 기호로 갱신. Esc로 닫으면 ? 버튼으로 포커스</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -5803,29 +5947,29 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>[최초 FAIL 증거 evidence/P1/P1-10-06.png] 이번엔 소스로만 확인. 화면은 다음 실행 때 함께 봄</t>
+          <t>[이전 FAIL 증거 evidence/P1/P1-09-08.png]</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>P1-10-07</t>
+          <t>P1-09-09</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-CAL-06</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>UX-09, 2.5</t>
+          <t>P1-09, SCH-02</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5835,50 +5979,50 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
+          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 @영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 시간 칩 누르면 '자세히'(CAL-07)로, Esc는 임시 블록 제거. '업무로도 만들기' 토글은 업무 API 연결(P1-03) 전이라 숨김</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
-        </is>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고) / [재검증 a5bb168] dev 모드에서도 같은 결과</t>
+          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>P1-11-01</t>
+          <t>P1-09-10</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5893,38 +6037,50 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
+          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 직후 홈 확인</t>
+          <t>1) 빠른 입력 포커스</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+          <t>자주 하는 업무 상위 3개 제안</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>P1-11-02</t>
+          <t>P1-10-01</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5944,33 +6100,45 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
+          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎) / [재검증 a5bb168] vite dev에서도 입력창 Ctrl+K → 팔레트 검색 입력에 포커스, Esc로 닫히고 빠른 입력창 값 유지(관찰 ① 해소)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>P1-11-03</t>
+          <t>P1-10-02</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5985,38 +6153,50 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
+          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
+          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>P1-11-04</t>
+          <t>P1-10-08</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05, D-25</t>
+          <t>P1-10, UX-01, SCR-COM-03 ②</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6031,38 +6211,50 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
+          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1) 다가오는 일정 영역</t>
+          <t>1) 업무 제목 일부·일지 내용 입력</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
+          <t>업무 검색·일지 검색 결과 그룹</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>P1-11-05</t>
+          <t>P1-10-03</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6082,38 +6274,50 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1) 홈 빠른 입력으로 업무 추가</t>
+          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>P1-11-06</t>
+          <t>P1-10-04</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, 2.4</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6123,43 +6327,55 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1) 폭별 카드 배치</t>
+          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
+          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>P1-11-07</t>
+          <t>P1-10-09</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>2.5 (로딩)</t>
+          <t>P1-10, UX-03, UX-09</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6174,38 +6390,46 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1) 느린 네트워크로 홈 진입</t>
+          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
+          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>P1-12-01</t>
+          <t>P1-10-05</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6215,38 +6439,50 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 미인증 계정</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
+          <t>1) 모바일에서 업무 보관</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
+          <t>토스트가 하단 탭 위에 표시</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02</t>
+          <t>P1-10-06</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-01</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08, D-41, D-53</t>
+          <t>P1-10, UX-04</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6256,89 +6492,113 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 qa- 주소(사용자 승인)</t>
+          <t>막 가입한 계정</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
+          <t>1) 가입 직후 첫 화면</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
+          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>[재검증 2026-10-06, 444466e 소스 확인] 홈 빈 상태 안내가 '시간·@프로젝트·#태그·!우선순위·~마감을 같이 적으면 알아서 나눠 저장해요.'로 바뀜(453401f)</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>[최초 FAIL 증거 evidence/P1/P1-10-06.png] 이번엔 소스로만 확인. 화면은 다음 실행 때 함께 봄</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>P1-12-03</t>
+          <t>P1-10-07</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>P1-12, D-57</t>
+          <t>UX-09, 2.5</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02 메일</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
+          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
+          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고) / [재검증 a5bb168] dev 모드에서도 같은 결과</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>P1-12-04</t>
+          <t>P1-11-01</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6348,22 +6608,22 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
+          <t>1) 로그인 직후 홈 확인</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
+          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6374,17 +6634,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>P1-12-05</t>
+          <t>P1-11-02</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -6394,22 +6654,22 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번 입력</t>
+          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
+          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6420,17 +6680,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>P1-12-06</t>
+          <t>P1-11-03</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6440,22 +6700,22 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
+          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 발급 후 10분 경과</t>
+          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
+          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -6466,17 +6726,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>P1-12-07</t>
+          <t>P1-11-04</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-11, SCH-05, D-25</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6486,22 +6746,22 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 다시 받기 직후 다시 누르기</t>
+          <t>1) 다가오는 일정 영역</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
+          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -6512,17 +6772,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>P1-12-08</t>
+          <t>P1-11-05</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08, D-64</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -6532,22 +6792,22 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>로컬(실제 메일 10통 발송 회피)</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 직후 자동 발송 1통 포함, 24시간 안에 11번째 발송 요청 2) 첫 발송 24시간 뒤 다시 요청</t>
+          <t>1) 홈 빠른 입력으로 업무 추가</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
+          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -6558,42 +6818,42 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>P1-12-09</t>
+          <t>P1-11-06</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>P1-12, D-64</t>
+          <t>NFR-06, 2.4</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>코드 2번 발급</t>
+          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1) 먼저 받은 코드로 인증</t>
+          <t>1) 폭별 카드 배치</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
+          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -6604,22 +6864,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>P1-12-10</t>
+          <t>P1-11-07</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>2.5 (로딩)</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6629,17 +6889,17 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
+          <t>1) 느린 네트워크로 홈 진입</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>거부(코드는 계정별), 비로그인 401</t>
+          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -6650,42 +6910,42 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>P1-12-12</t>
+          <t>P1-12-01</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>P1-12, P1-13, D-65</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>로컬(운영 IP 제한 회피), 계정 여러 개</t>
+          <t>막 가입한 미인증 계정</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 IP에서 인증 코드·재설정 코드 메일을 합쳐 1시간에 11번 요청 2) X-Client-Ip 헤더 없이 요청</t>
+          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
+          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6696,17 +6956,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>P1-12-11</t>
+          <t>P1-12-02</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>SCR-MAIL-01</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>P1-12</t>
+          <t>P1-12, AUTH-08, D-41, D-53</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6716,22 +6976,22 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>인증 완료 계정</t>
+          <t>수신 가능한 qa- 주소(사용자 승인)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입</t>
+          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>배너 표시 안 됨</t>
+          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -6742,42 +7002,42 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>P1-13-01</t>
+          <t>P1-12-03</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-MAIL-01</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>P1-13, SCR-AUTH-02 ④</t>
+          <t>P1-12, D-57</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>P1-12-02 메일</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
+          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>/password/forgot 이동</t>
+          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -6788,42 +7048,42 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>P1-13-02</t>
+          <t>P1-12-04</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-65</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
+          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
+          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -6834,17 +7094,17 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>P1-13-03</t>
+          <t>P1-12-05</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -6854,22 +7114,22 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1) 빈 값·형식 오류 이메일 제출</t>
+          <t>1) 틀린 코드 5번 입력</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
+          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -6880,17 +7140,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>P1-13-04</t>
+          <t>P1-12-06</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-02</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-41</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -6900,22 +7160,22 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 계정</t>
+          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1) 재설정 메일 확인</t>
+          <t>1) 코드 발급 후 10분 경과</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
+          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -6926,17 +7186,17 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>P1-13-05</t>
+          <t>P1-12-07</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -6951,17 +7211,17 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
+          <t>1) 코드 다시 받기 직후 다시 누르기</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
+          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6972,17 +7232,17 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>P1-13-06</t>
+          <t>P1-12-08</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-38</t>
+          <t>P1-12, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -6992,22 +7252,22 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>코드 확인됨</t>
+          <t>로컬(실제 메일 10통 발송 회피)</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
+          <t>1) 가입 직후 자동 발송 1통 포함, 24시간 안에 11번째 발송 요청 2) 첫 발송 24시간 뒤 다시 요청</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
+          <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -7018,17 +7278,17 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>P1-13-07</t>
+          <t>P1-12-09</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, AUTH-08, D-64</t>
+          <t>P1-12, D-64</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -7043,17 +7303,17 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
+          <t>코드 2번 발급</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
+          <t>1) 먼저 받은 코드로 인증</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
+          <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -7064,42 +7324,42 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>P1-13-12</t>
+          <t>P1-12-10</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02, 05</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>P1-13, P1-14, D-64</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>로컬, 10회 실패로 잠긴 계정</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1) 잠긴 상태에서 비밀번호 재설정 완료 2) 곧바로 새 비밀번호로 로그인</t>
+          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>잠금이 풀려 바로 로그인 성공</t>
+          <t>거부(코드는 계정별), 비로그인 401</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -7110,42 +7370,42 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>P1-13-08</t>
+          <t>P1-12-12</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12, P1-13, D-65</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>로컬(운영 IP 제한 회피), 계정 여러 개</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번</t>
+          <t>1) 같은 IP에서 인증 코드·재설정 코드 메일을 합쳐 1시간에 11번 요청 2) X-Client-Ip 헤더 없이 요청</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
+          <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -7156,17 +7416,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>P1-13-09</t>
+          <t>P1-12-11</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-12</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -7176,22 +7436,22 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>인증 완료 계정</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
+          <t>1) 앱 화면 진입</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
+          <t>배너 표시 안 됨</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -7202,17 +7462,17 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>P1-13-10</t>
+          <t>P1-13-01</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02, 04</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>P1-13, P1-14</t>
+          <t>P1-13, SCR-AUTH-02 ④</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -7227,12 +7487,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>잠긴 계정</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 안내의 재설정 링크</t>
+          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7248,22 +7508,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>P1-13-11</t>
+          <t>P1-13-02</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04, 05</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, NFR-13</t>
+          <t>P1-13, AUTH-03, D-65</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7273,17 +7533,17 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>비로그인, 390px, 오프라인 전환</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
+          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
+          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -7294,17 +7554,17 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>P1-14-01</t>
+          <t>P1-13-03</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7319,17 +7579,17 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>qa- 계정</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
+          <t>1) 빈 값·형식 오류 이메일 제출</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
+          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -7340,17 +7600,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>P1-14-02</t>
+          <t>P1-13-04</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-MAIL-02</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, AUTH-03, D-41</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -7360,22 +7620,22 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>qa- 계정</t>
+          <t>수신 가능한 계정</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
+          <t>1) 재설정 메일 확인</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
+          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -7386,17 +7646,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>P1-14-03</t>
+          <t>P1-13-05</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -7406,22 +7666,22 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 해제 시점 이후 로그인</t>
+          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
+          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -7432,42 +7692,42 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>P1-14-04</t>
+          <t>P1-13-06</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>P1-14, D-61</t>
+          <t>P1-13, AUTH-03, D-38</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>없는 이메일</t>
+          <t>코드 확인됨</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 이메일로 10회 이상 실패</t>
+          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
+          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -7478,42 +7738,42 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>P1-14-05</t>
+          <t>P1-13-07</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09, D-61</t>
+          <t>P1-13, AUTH-03, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>로컬(운영 IP 차단 위험 회피)</t>
+          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
+          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
+          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -7524,38 +7784,42 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>P1-14-06</t>
+          <t>P1-13-12</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-02, 05</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>P1-14, p1-14-springdoc-429</t>
+          <t>P1-13, P1-14, D-64</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr"/>
+          <t>로컬</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>로컬, 10회 실패로 잠긴 계정</t>
+        </is>
+      </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
+          <t>1) 잠긴 상태에서 비밀번호 재설정 완료 2) 곧바로 새 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
+          <t>잠금이 풀려 바로 로그인 성공</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -7566,17 +7830,17 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>P1-X-01</t>
+          <t>P1-13-08</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01 (P1 완성)</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -7586,22 +7850,22 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
+          <t>1) 틀린 코드 5번</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
+          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -7612,42 +7876,42 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>P1-X-02</t>
+          <t>P1-13-09</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1) 화면 전환 중 표시</t>
+          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
+          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -7658,17 +7922,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>P1-X-03</t>
+          <t>P1-13-10</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ④</t>
+          <t>SCR-AUTH-02, 04</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>NFR-13 (P0 TC-81 재확인)</t>
+          <t>P1-13, P1-14</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -7683,17 +7947,17 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>잠긴 계정</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
+          <t>1) 잠금 안내의 재설정 링크</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
+          <t>/password/forgot 이동</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -7704,22 +7968,22 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>P1-X-04</t>
+          <t>P1-13-11</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ③</t>
+          <t>SCR-AUTH-04, 05</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>NFR-13</t>
+          <t>NFR-06, NFR-13</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7729,17 +7993,17 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>비로그인, 390px, 오프라인 전환</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
+          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
+          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -7750,22 +8014,22 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>P1-X-05</t>
+          <t>P1-14-01</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>NFR-02, NFR-14</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7775,17 +8039,17 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>qa- 계정</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
+          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>모두 403 ORIGIN_REJECTED</t>
+          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
@@ -7796,22 +8060,22 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>P1-X-06</t>
+          <t>P1-14-02</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>D-30</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7821,17 +8085,17 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>qa- 계정</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
+          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
+          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
@@ -7842,42 +8106,42 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>P1-X-07</t>
+          <t>P1-14-03</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>—(배포)</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>D-56</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>배포 브랜치 main 전환 후</t>
+          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
+          <t>1) 잠금 해제 시점 이후 로그인</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
+          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
@@ -7888,22 +8152,22 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>P1-X-08</t>
+          <t>P1-14-04</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>—(배포)</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>P0-09</t>
+          <t>P1-14, D-61</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7913,17 +8177,17 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
+          <t>없는 이메일</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
+          <t>1) 없는 이메일로 10회 이상 실패</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
+          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -7934,42 +8198,42 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>P1-X-09</t>
+          <t>P1-14-05</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>2.6 문구 말투, D-36</t>
+          <t>P1-14, AUTH-09, D-61</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로컬(운영 IP 차단 위험 회피)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면 문구 말투 확인</t>
+          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
+          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr"/>
@@ -7980,22 +8244,22 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>P1-X-10</t>
+          <t>P1-14-06</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>화면정의서 2.5 (키보드·터치)</t>
+          <t>P1-14, p1-14-springdoc-429</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8003,19 +8267,15 @@
           <t>운영</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>로그인 상태(qa- 계정)</t>
-        </is>
-      </c>
+      <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
@@ -8023,10 +8283,470 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-01</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SCR-COM-01</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>SCR-COM-01 (P1 완성)</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정), 390px</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-02</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SCR-COM-01</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>SCR-COM-01</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>1) 화면 전환 중 표시</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-03</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SCR-SYS-02 ④</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>NFR-13 (P0 TC-81 재확인)</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-04</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SCR-SYS-02 ③</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>NFR-13</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-05</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>—(API)</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>NFR-02, NFR-14</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>모두 403 ORIGIN_REJECTED</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-06</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>—(API)</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>D-30</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-07</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>—(배포)</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>D-56</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>배포 브랜치 main 전환 후</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-08</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>—(배포)</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>P0-09</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>브라우저</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-09</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>2.6 문구 말투, D-36</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 새 화면 문구 말투 확인</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-10</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>화면정의서 2.5 (키보드·터치)</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L152"/>
+  <autoFilter ref="A1:L162"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8465,7 +9185,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1-09·10, P1-01, P1-02, 재검증)</t>
+          <t>2026-10-06 (P1-09·10, P1-01, P1-02, P1-07 일부, P1-03·04, 재검증)</t>
         </is>
       </c>
     </row>
@@ -8489,7 +9209,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -8501,7 +9221,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>기능 119, 사용성 19, 보안 9, 배포 4</t>
+          <t>기능 123, 사용성 25, 보안 9, 배포 4</t>
         </is>
       </c>
     </row>
@@ -8513,7 +9233,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>미실행 103, PASS 32, BLOCKED 13, FAIL 3</t>
+          <t>미실행 89, PASS 49, BLOCKED 17, FAIL 6</t>
         </is>
       </c>
     </row>
@@ -8525,7 +9245,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>P1-02-07 새로고침 시 태그 지연 삭제 취소(정책 확인), P1-02-09 프로젝트·태그 화면 터치 영역 44px 미만, P1-02-10 태그 편집 후 포커스 유실. 해결: P1-09-01·08, P1-01-11, P1-10-06(453401f, 소스 확인)</t>
+          <t>미해결(fix(P1-03) 묶음 재검증 대상): P1-03-01 패널 열림 제목 폭, P1-03-04·08·07·13·P1-04-04 포커스 유실, P1-03-05 빨강 미적용·날짜 입력 중간값 저장, P1-03-09 보관 업무 마감일 편집. 해결: P1-02-11, P1-09-01·08, P1-01-11, P1-10-06, P1-02-09·10</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'테스트 항목'!$A$1:$L$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8D3CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,6 +108,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2190,7 +2198,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 14784f0 스냅숏, 2026-10-06] [재검증 4b5f035] ✎ → 삭제를 Enter로: 가운데 태그(결제) → 다음 태그(리뷰) ✎로 포커스, 마지막 태그 → 이전 태그 ✎(4번 연속), 하나 남은 태그(견적) → '태그' 제목(H2)</t>
+          <t>[로컬 dev:mock, feature/P1 14784f0 스냅숏, 2026-10-06] [재검증 4b5f035] ✎ → 삭제를 Enter로: 가운데 태그(결제) → 다음 태그(리뷰) ✎로 포커스, 마지막 태그 → 이전 태그 ✎(4번 연속), 하나 남은 태그(견적) → '태그' 제목(H2) / [로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [회귀 4eda960] 가운데 → 다음 ✎, 되돌리기(키보드) → H1 '설정'</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2302,22 +2310,18 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 빠른 입력 'QA 테스트 업무 #리뷰 @개발' Enter → 행 추가(업무 6→7, 토스트 '업무 1개를 추가했어요'+되돌리기), 행 클릭으로 /tasks/:id 패널, 새로고침해도 같은 패널. 결함: 패널이 열리면 목록 제목 폭이 0(1024·1280px), 1440px 124px, 1600px 284px</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-03-01.png</t>
-        </is>
-      </c>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재검증 1042730·4f44b11·4eda960] 상세 패널을 연 상태에서 제목 폭 1024px 133~157(칸: 완료·제목·마감), 1280px 338~362(+프로젝트), 1440px 498~522px</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤 (1024·1280·1440px)</t>
+          <t>[최초 FAIL 2026-10-06 21c8f0e] 패널 열림 시 제목 폭 0</t>
         </is>
       </c>
     </row>
@@ -2476,18 +2480,18 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 목록 완료 원 클릭 → '업무 1개를 완료했어요'+되돌리기, 행이 '완료 n개(최근 7일)'로 이동, 결과 팝오버 없음(P2). 되돌리기·체크 해제로 다시 열림. 결함: 완료 뒤 포커스가 BODY로 감</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재검증 1042730·4f44b11·4eda960] 가운데 행 완료(Space) → 다음 행 완료 버튼으로 포커스, 되돌리기 동작</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+          <t>[최초 FAIL 2026-10-06 21c8f0e] 완료 후 포커스 BODY</t>
         </is>
       </c>
     </row>
@@ -2534,22 +2538,18 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 마감일 어제(10/5) → '마감 초과' 그룹·10/5(월), 오늘 → '오늘', 10/13 → '다음' 10/13(화). 우선순위 높음 표시. 결함: 마감 초과 날짜와 '높음'이 빨강이 아니라 회색(.danger가 .due·.priority보다 앞에 선언됨). 마감일을 키보드로 입력하면 중간값(1013-06-06 등)이 키마다 저장됨</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-03-05.png</t>
-        </is>
-      </c>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재검증 1042730·4f44b11·4eda960] '높음'·마감 초과 10/5(월) 빨강 rgb(160,38,19). 날짜 칸 키 입력(↑·숫자) 중에는 저장 안 됨, 칸을 벗어날 때·Enter 때만 저장</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤 (색, 날짜 입력 중간값 저장)</t>
+          <t>[최초 FAIL 2026-10-06 21c8f0e] 회색 표시, 키 입력 중간값 저장</t>
         </is>
       </c>
     </row>
@@ -2650,18 +2650,18 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 프로젝트 개발→영업, 태그 #견적·#보고 추가, #리뷰 빼기 → 목록 행 '영업 #견적 #보고', 사이드바 남은 수(개발 3→2, 영업 2→3) 반영. 결함: 태그 빼기(클릭·Enter) 뒤 포커스 BODY</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재검증 1042730·4f44b11·4eda960] 태그 빼기: 가운데 → 다음 태그 빼기, 마지막 → 이전, 하나 남은 것 → '태그 추가' 입력</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+          <t>[최초 FAIL 2026-10-06 21c8f0e] 태그 빼기 후 포커스 BODY</t>
         </is>
       </c>
     </row>
@@ -2708,18 +2708,18 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 제목 링크에 포커스 → Delete → '업무 1개를 보관했어요'+되돌리기, 되돌리기로 복원. 다시 Delete 후 6.5초 → 토스트 닫히고 목록에서 빠짐. 결함: 보관 뒤 포커스 BODY</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재검증 1042730·4f44b11·4eda960] Delete 보관 → 다음 행(마지막 행이면 이전 행), 패널 [보관] → 다음 행(4f44b11)</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+          <t>[최초 FAIL 2026-10-06 21c8f0e] 보관 후 포커스 BODY</t>
         </is>
       </c>
     </row>
@@ -2766,22 +2766,18 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] /tasks/&lt;보관 id&gt; → 상태·우선순위·프로젝트·태그·진행률·메모 disabled, 제목 readOnly, [복원] → '업무를 복원했어요', 목록에 다시 나타남. 결함: 마감일 칸만 편집 가능 → 바꾸면 '보관한 업무라 바꿀 수 없어요' 토스트, 서버 값은 그대로인데 칸에는 바꾼 값이 남음(복원 뒤에도 패널 10-20, 목록 10/5)</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-03-09.png</t>
-        </is>
-      </c>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재검증 1042730·4f44b11·4eda960] 보관 업무 마감일 disabled=true, 복원 후 풀림</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+          <t>[최초 FAIL 2026-10-06 21c8f0e] 마감일 칸만 편집 가능</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2990,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 390px: 패널이 0,0 390x844 전체 화면, 문서 폭 390(가로 스크롤 없음), 닫기로 /tasks</t>
+          <t>[로컬 dev:mock, feature/P1 21c8f0e 스냅숏, 2026-10-06] 390px: 패널이 0,0 390x844 전체 화면, 문서 폭 390(가로 스크롤 없음), 닫기로 /tasks / [로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재검증] × → 연 행 링크, Esc(select에서) → 연 행</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3005,7 +3001,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>패널 닫은 뒤(Esc·×, 1600px도) 포커스가 연 행으로 돌아가지 않고 BODY — 재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+          <t>[최초 비고 21c8f0e] 닫은 뒤 포커스 BODY → 해결. 남은 비고: 슬라이더에 포커스가 있으면 Esc로 안 닫힘 — pm 결정으로 수정 배정, 재검증 대상: 다음 fix 묶음 뒤</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3225,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>필터 지우기 뒤 포커스 BODY — 재검증 대상: fix(P1-03) 묶음 커밋 뒤</t>
+          <t>[21c8f0e 비고] 필터 지우기 뒤 포커스 BODY → [재검증 aa4d756] H1 '업무'로 해결</t>
         </is>
       </c>
     </row>
@@ -3790,18 +3786,18 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] '이 일정만' 이동은 그 회차만 바뀜(드래그 경로로 확인). 상세 모달 수정 경로는 미실행</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 회차 제목 수정 저장 → alertdialog '반복 일정을 수정할까요?' 선택지 '이 일정만/모든 일정' 2개. 이 일정만 → 그 회차만 '팀 스탠드업(수)'. 모든 일정 → 시리즈 '데일리 스탠드업', 수요일 회차는 자기 제목 유지</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>실행 중단(사용자 지시)</t>
+          <t>D-71: 제목만 바꾸면 회차 변경 유지. 저장 뒤 포커스는 H1(같은 블록 아님)</t>
         </is>
       </c>
     </row>
@@ -3894,18 +3890,18 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] 실제 마우스 드래그: 반복 '팀 스탠드업' 회차를 끌면 '반복 일정을 옮길까요?' 대화상자(이 일정만/모든 일정, 취소/확인, role=alertdialog). 취소 → 원위치, 포커스는 캘린더 제목(H1). '이 일정만' → 그 회차만 11:00으로. '모든 일정' → 4회차 모두 11:00 + '모든 일정을 옮겼어요 [되돌리기]'</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 수 스탠드업을 목 +30분으로 끌기 → alertdialog '반복 일정을 옮길까요?' → 취소 시 원위치. 모든 일정 → 시작 10/7 10:00, 요일 MO~FR → TU~SA, 토스트 '모든 일정을 옮겼어요' → Ctrl+Z로 원래 시각·요일, 회차 변경 0</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>후반부 결과가 불안정: '모든 일정' 뒤 Ctrl+Z로 원래 시각 복원이 안 됐고, 이후 같은 드래그가 대화상자를 열지 않음. 화면 상태가 꼬였을 가능성이 있어 결함으로 보내지 않고 새 브라우저로 재실행 필요. 실행 중단(사용자 지시). 월요일(10/5 대체공휴일)에는 스탠드업 회차가 없음 — 반복 규칙 확인 필요</t>
+          <t>[이전 실행 f32d598 결과 불안정 — alertdialog 놓침]</t>
         </is>
       </c>
     </row>
@@ -4100,10 +4096,22 @@
           <t>보기 전환·오늘·이전/다음·만들기 동작, 한글 상태에서도 동작(event.code). P(업무 패널)는 P1-08 범위 — 완료 보고에 없어 동작 여부만 기록</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] D/W/M/Y/A/T/C 동작, 한글 상태(key 'ㅡ', code KeyM) → 월 보기, P → 할 일 상자 토글. J=이전, K=다음</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>pm 결정 2026-10-06: J=다음·K=이전으로 바꿈(frontend2) — 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4146,10 +4154,22 @@
           <t>입력창·모달에서는 글자만 입력되고 보기 안 바뀜, 끄면 단일 문자 단축키 모두 무시. 설정은 다른 브라우저에서 로그인해도 유지(identity 저장, D-60)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 입력칸에서 dw → 글자만 입력, 설정에서 단축키 끔 → d·m·c·p 모두 무시, 다시 켬</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>다른 브라우저 유지(D-60)는 dev:mock에서 확인 불가</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4238,10 +4258,22 @@
           <t>끈 프로젝트의 일정이 숨겨지고 다시 켜면 표시, 숨김 상태는 새로고침 뒤에도 유지(브라우저 저장), 프로젝트 없는 일정은 늘 보임</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>dev:mock 회차에 projectId가 없어 업무를 연결해도 기본 보라색 — 프로젝트 색·필터 확인 불가</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>pm: frontend2가 mock 회차에 projectId를 채움 → 재검증 대상: 다음 fix 묶음 뒤. 실서버 확인은 병합 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4386,18 +4418,18 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] 실제 마우스 드래그: 블록을 하루 오른쪽·24px 아래로 → 금 12:30–14:15로 이동(30분, 15분 단위) + '일정을 옮겼어요 [되돌리기]'. 아래 끝 손잡이(높이 8px)를 40px 끌기 → 15:00으로 길이 조절, 입력창 밖 Ctrl+Z → 14:15로 복원, 위로 크게 끌면 최소 15분(12:30–12:45). 종일 막대 '부산 출장'을 하루 왼쪽으로 끌면 이동은 되나 되돌리기 토스트가 보이지 않았음</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] [재실행] 종일 막대 '부산 출장'을 이틀 옮기기 → '일정을 옮겼어요'+되돌리기로 복원, 다시 끌고 Ctrl+Z로 복원</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>종일 막대 이동의 되돌리기 토스트 유무는 같은 실행 후반에 결과가 불안정해(아래 P1-06-05 비고) 재확인 필요. 실행 중단(사용자 지시)</t>
+          <t>[이전 실행 결과 불안정 — 남은 대화상자가 끌기를 삼킴]</t>
         </is>
       </c>
     </row>
@@ -4488,10 +4520,26 @@
           <t>6주×7일, 칩 최대 3개 + '+n개' 팝오버, 날짜 숫자 → 일 보기, 빈 칸 → 종일 빠른 생성, 칩을 끌어 다른 날로 이동(실제 브라우저 드래그). 일지 상태 점은 P3라 없음</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 할 일 상자를 닫은 상태: 날짜 숫자 → 일 보기, 빈 칸 → '새 일정 … 종일', 칩 10/17→10/24 끌기(시각 유지, 되돌리기 토스트), +n개 팝오버. 결함: 할 일 상자가 열려 있으면 그리드가 1280px에서 252px, 1440px에서 92px 가려져 주말이 안 보이고 스크롤바도 없음</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-07-11.png</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: 다음 fix 묶음 뒤. 관찰: 390px 월 보기는 그리드 안에서 가로 스크롤(358/724px)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4534,10 +4582,26 @@
           <t>12개월(데스크톱 4×3, 모바일 1열), 일정 밀도 점 3단계(없음/1~2/3+), 날짜 → 일 보기, 월 이름 → 월 보기. 일지 상태 표시는 P3라 없음</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 열 수가 2~6열(패널 닫힘 1280 3열·1600 5열·1920 6열, 패널 열림 1280 2열, 390px 2열). 밀도 점 3단계, 날짜 → 일 보기, 월 이름 → 월 보기는 동작</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-07-12.png</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>화면정의서 4×3·모바일 1열과 다름 — pm 판단 대기</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4580,8 +4644,16 @@
           <t>오늘부터 날짜별 그룹, 반복 아이콘, 스크롤하면 30일씩 더 불러옴(400일 상한), 지난 일정 표시</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 오늘부터 날짜별 그룹, '반복' 표기, 처음 60일(~12/4), 스크롤 끝·더 불러오기마다 30일씩, 11번 뒤 버튼 사라짐(마지막 2027-10-29, 30일×13창 = 390일 ≤ 400일), 지난 일정 보기 → 9/28부터</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
     </row>
@@ -4764,10 +4836,22 @@
           <t>미니 달력 → 이전/다음·보기 전환, 연 보기 날짜 → 월 이름 버튼·월 보기, 월 칩 → 목록·일 보기, 종일 막대·짧은 블록 → Tab+Enter/Space로 상세 모달·목록 보기. 나머지 버튼은 44px 이상. 예외 5가지는 24x24px 이상이거나, 작으면 지름 24px 원이 이웃과 겹치지 않는 간격(WCAG 2.5.8, erp-design 확정 2026-10-06) — 15분 블록·월 칸 칩 크기·간격 측정값 기록</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 1280px 주 보기에서 44px 미만은 예외 5종뿐: 미니 달력 날짜 26x26, 종일 막대 113x24, 블록 높이 22~24px(나란히 놓이면 폭 23px), 월 칩 높이 24px. 블록·막대·칩·날짜 모두 button이라 Tab+Enter로 상세 모달·일 보기</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>예외 밖 미달: 빠른 입력 '문법 도움말' 32x32 — frontend 배정, 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4802,18 +4886,30 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 생성 팝오버·상세 모달·'+n개' 팝오버를 열고 닫기 2) 상세 모달에서 일정 삭제</t>
+          <t>1) 빠른 생성 팝오버·상세 모달·'+n개' 팝오버를 열고 닫기 2) 상세 모달에서 일정 삭제 3) 상세 모달에서 시간 변경 후 저장</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>닫으면 연 요소로 포커스 복귀, 연 요소가 사라졌으면(삭제) 캘린더 제목으로</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
+          <t>닫으면 연 요소로 포커스 복귀, 연 요소가 사라졌으면(삭제) 캘린더 제목으로, 시간 저장 후에는 옮겨진 같은 블록으로(pm 전달 2026-10-06)</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 상세 모달 Esc → 연 블록, 시간 저장 → 옮겨진 같은 블록, 삭제 → 캘린더 제목, '+4개 더보기' 팝오버 Esc → 그 버튼, 일정 만들기·C 팝오버 Esc → '일정 만들기'</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>반복 회차를 범위 대화상자로 저장하면 H1로 감(같은 블록 아님)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4856,8 +4952,16 @@
           <t>15분 블록이 30분 블록과 같은 높이(22px, 위아래 1px 틈)로 그려지고 이어진 짧은 블록은 나란히 배치됨. 시간 글자·aria-label은 실제 시각(10:00~10:15)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 15분 블록 A·B와 30분 블록 C 모두 높이 22px, 2열로 나란히, aria-label은 실제 시각(10:00–10:15). 짧은 블록에는 제목만 보임</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
     </row>
@@ -4902,8 +5006,16 @@
           <t>빈 칸 동작(빠른 생성 팝오버, 드래그로 새 일정 만들기 등)이 일어나지 않음</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 이어진 블록 사이 틈(y396~397)은 column 요소, 클릭·드래그 모두 대화상자 없음·일정 수 그대로. 대조: 빈 칸 클릭 → '새 일정'</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
     </row>
@@ -4948,8 +5060,16 @@
           <t>23:45 시작 15분 블록이 23:30 위치에 그려져 그리드 밖으로 넘치지 않음. 23:30에 다른 일정이 있으면 나란히 배치됨. 시간 글자·aria-label은 23:45</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 목 23:45 블록이 23:30 줄(y1022)에 51px 폭으로, 금 23:45·23:30 블록은 나란히, 라벨 23:45–00:00</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
     </row>
@@ -4994,8 +5114,16 @@
           <t>칩·더보기 최소 24px. 3개인 날은 칩 3개, 4개 이상인 날은 칩 2개+더보기가 칸 안에 들어감(넘치거나 잘리지 않음)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 1280·390px: 칩·더보기 높이 24, 토 10/17 3개 → 칩 3개, 6개인 날 → 칩 2 + '+4개 더보기', 칸 높이 132px 안</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
     </row>
@@ -5040,8 +5168,16 @@
           <t>날짜 숫자·더보기의 투명 영역이 이웃 칩·빈 칸의 클릭을 가로채지 않음(이웃을 누르면 이웃 동작)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 할 일 상자 닫고 1280px 월 그리드 버튼 78개를 702점 표본: 다른 버튼이 가로챈 곳 0. 날짜 숫자 28x28 바깥은 셀·칩, 더보기 위아래 2px부터 이웃</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
     </row>
@@ -5086,8 +5222,16 @@
           <t>하루 칸 전체가 버튼(접근 가능한 이름에 날짜), 누르면 그 날의 일 보기로 이동. 블록은 표시만 되고 끌어 옮기기·빈 칸 새 일정 만들기는 일어나지 않음</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 390px 주 보기: 하루 칸이 버튼 '10월 8일 목요일, 일정 6개'(39x1152, 안에 포커스 요소 0, 블록 aria-hidden), Enter → /calendar/day/2026-10-08. 블록 끌기 → 일정 그대로, 놓으면 그날 일 보기(누름으로 처리)</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
     </row>
@@ -5132,8 +5276,16 @@
           <t>기본 열림, 마감순, 마감 초과 강조, 프로젝트 칩·마감 표시, 날짜 없는 업무 접힘</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 기본 열림('할 일 상자'), 마감순(어제→오늘→내일), '어제 마감' 빨강, 프로젝트 칩·마감 표시, '날짜 없는 업무 1개 더 보기' 접힘</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
     </row>
@@ -5178,8 +5330,16 @@
           <t>10:15~11:15 일정 생성(15분 단위), 업무와 연결, 패널에서 빠짐</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 카드를 목 10:15 칸으로 끌기 → 10:15~11:15 일정(taskId 연결), 패널에서 빠짐, '업무를 일정에 넣었어요'+되돌리기</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
     </row>
@@ -5224,8 +5384,16 @@
           <t>"배치할 업무가 없어요"</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 업무 0개 → '배치할 업무가 없어요'</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
     </row>
@@ -5270,8 +5438,16 @@
           <t>토글 동작, 추가한 업무가 패널에 나타남</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] P로 닫기·열기, 패널 빠른 입력 'QA 패널 업무 ~금' → 카드 추가, '업무를 만들었어요'</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
     </row>
@@ -5316,30 +5492,38 @@
           <t>P1 범위 확인: 오늘 일정 영역(③)은 P2라 이번에는 대상 없음 → N/A 예상</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>홈 오늘 일정 영역(③)은 P2라 대상 없음</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>P1-09-01</t>
+          <t>P1-08-06</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-09</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62, D-67</t>
+          <t>P1-08, 화면정의서 2.5(키보드), pm 전달 2026-10-06</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5349,22 +5533,22 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 패널에 업무 3개</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1) '14-16 견적서 작성 @영업 #긴급 !높음 ~금' 입력</t>
+          <t>1) 가운데 카드의 "일정 잡기"를 키보드로 실행해 배치 2) 포커스 위치 확인</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>칩: 시간(오늘 14:00–16:00) · 프로젝트 @영업 · 태그 #긴급 · 우선순위 높음 · 마감 이번 주 금요일 실제 날짜, 종류별 색 구분, 제목 '견적서 작성'</t>
+          <t>배치된 카드가 패널에서 빠진 뒤 이웃 카드(다음, 없으면 이전)로 포커스, 카드가 없으면 패널 제목. BODY로 사라지지 않음</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] '14-16 견적서 작성 @영업 #긴급 !높음 ~금' → 칩 '오늘 14:00–16:00'(accent) · '영업'(프로젝트 색 P2 주황) · '#긴급 새'(점선 테두리, 없는 태그) · '우선순위 높음'(빨강 계열) · '마감 10/9(금)'(회색), 안내 '일정과 업무가 함께 만들어져요'. 있는 태그 '#견적'은 흰 바탕 실선 테두리로 프로젝트 칩과 구분</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 가운데 카드 '일정 잡기' Enter → 새 일정 모달(제목, 오늘 15:00~16:00) → 저장 → 다음 카드 '결제 API 문서화 일정 잡기'로 포커스, 패널에서 빠짐</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -5373,16 +5557,12 @@
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>[이전: 2026-10-06 기호 변경 전 코드에서 FAIL→재검증 PASS, 증거 evidence/P1/P1-09-01.png]</t>
-        </is>
-      </c>
+      <c r="L94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>P1-09-02</t>
+          <t>P1-09-01</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5392,7 +5572,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04</t>
+          <t>P1-09, REC-04, D-62, D-67</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5412,35 +5592,35 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
+          <t>1) '14-16 견적서 작성 @영업 #긴급 !높음 ~금' 입력</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
+          <t>칩: 시간(오늘 14:00–16:00) · 프로젝트 @영업 · 태그 #긴급 · 우선순위 높음 · 마감 이번 주 금요일 실제 날짜, 종류별 색 구분, 제목 '견적서 작성'</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] '14-16 견적서 작성 @영업 #긴급 !높음 ~금' → 칩 '오늘 14:00–16:00'(accent) · '영업'(프로젝트 색 P2 주황) · '#긴급 새'(점선 테두리, 없는 태그) · '우선순위 높음'(빨강 계열) · '마감 10/9(금)'(회색), 안내 '일정과 업무가 함께 만들어져요'. 있는 태그 '#견적'은 흰 바탕 실선 테두리로 프로젝트 칩과 구분</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Enter 저장: API 연결 전(pm 지시)</t>
+          <t>[이전: 2026-10-06 기호 변경 전 코드에서 FAIL→재검증 PASS, 증거 evidence/P1/P1-09-01.png]</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>P1-09-03</t>
+          <t>P1-09-02</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5450,7 +5630,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-09, REC-04</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5470,35 +5650,35 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
+          <t>1) Enter로 저장(시간 있음) 2) 시간 없는 입력 저장</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
+          <t>시간 있음 → 업무+일정, 없음 → 업무만, 각각 되돌리기 토스트</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
+          <t>Enter 저장: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>P1-09-04</t>
+          <t>P1-09-03</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5508,7 +5688,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>P1-09, D-67</t>
+          <t>P1-09, REC-04, D-62</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5528,17 +5708,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 프로젝트 '@신규' 입력</t>
+          <t>1) '내일 보고서', '모레 보고서', '다음주 수요일 보고서', '10/12 보고서', '~금 보고서', '다음주 금 보고서', '금 보고서' 각각 입력</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
+          <t>시간 없이 날짜만 쓰면 마감 칩(A안)으로 실제 날짜 표시(사용자 시간대 기준). 한 글자 요일은 ~ 뒤·주 앞말(다음주 등) 뒤에서만 해석, '금 보고서'의 '금'은 제목에 남음</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 @신규프로젝트' → '+ 새 프로젝트 "신규프로젝트" 만들기' 칩(button). 키보드 Enter로 눌러 생성 → 프로젝트 칩(색 P4)으로 바뀜, 설정 프로젝트 목록에 추가. '@Alpha' 만든 뒤 '@alpha'는 기존 Alpha로 인식(대소문자 무시)</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 내일→마감 10/7(수), 모레→10/8(목), 다음주 수요일→10/14(수), 10/12·10월 12일→10/12(월), ~금→10/9(금), 다음주 금→10/16(금), '금 보고서'는 칩 없이 제목에 남음, '~10/12 내일 보고서'는 마감 10/12이고 '내일'은 제목에 남음. 시간 없이 날짜만이면 '업무가 만들어져요'(일정 안 만듦)</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -5549,14 +5729,14 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>업무 저장(Enter)은 API 연결 전이라 확인 안 함</t>
+          <t>기대 결과를 D-62(날짜만 → 마감, ~와 맨 날짜가 함께면 ~가 마감)와 frontend 확정 문법(한 글자 요일은 ~·주 앞말 뒤에서만)으로 고침</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>P1-09-13</t>
+          <t>P1-09-04</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5566,7 +5746,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>P1-09, TASK-04, D-67</t>
+          <t>P1-09, D-67</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5586,35 +5766,35 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1) '보고서 #긴급 #검토' 입력 2) 없는 태그 '#새태그' 입력 3) Enter 저장 후 업무 상세 확인</t>
+          <t>1) 없는 프로젝트 '@신규' 입력</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>태그 칩 2개(#긴급·#검토), 프로젝트 칩과 다른 색. 저장하면 업무에 태그 2개 연결(여러 개 허용 — 구현 범위 확인), 없는 태그 처리 방식은 구현 확인</t>
+          <t>"새 프로젝트 만들기" 칩, 확인해야 생성(확인 전 저장하면 프로젝트 없이 저장 또는 확인 요구)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 #견적 #결제 #견적' → 태그 칩 2개(같은 이름 하나로), '#새태그'·'#1번' → 점선 '새' 칩. 규칙에 안 맞는 'C# 공부'·'메일 a@b.com 확인'·'보고서 @ #'은 칩 없이 제목에 남음. '@개발 @영업'은 처음 것(개발)만 프로젝트</t>
-        </is>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 @신규프로젝트' → '+ 새 프로젝트 "신규프로젝트" 만들기' 칩(button). 키보드 Enter로 눌러 생성 → 프로젝트 칩(색 P4)으로 바뀜, 설정 프로젝트 목록에 추가. '@Alpha' 만든 뒤 '@alpha'는 기존 Alpha로 인식(대소문자 무시)</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>표시는 확인. 저장 시 태그 생성·연결은 Enter 저장 API 연결 전</t>
+          <t>업무 저장(Enter)은 API 연결 전이라 확인 안 함</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>P1-09-05</t>
+          <t>P1-09-13</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5624,7 +5804,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>P1-09</t>
+          <t>P1-09, TASK-04, D-67</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5644,31 +5824,35 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '@영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
+          <t>1) '보고서 #긴급 #검토' 입력 2) 없는 태그 '#새태그' 입력 3) Enter 저장 후 업무 상세 확인</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
+          <t>태그 칩 2개(#긴급·#검토), 프로젝트 칩과 다른 색. 저장하면 업무에 태그 2개 연결(여러 개 허용 — 구현 범위 확인), 없는 태그 처리 방식은 구현 확인</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] Esc → 입력 비움, 빈 입력 Enter 무시, '@영업 #견적'처럼 제목이 비면 칩과 '할 일 이름을 적어 주세요'</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 #견적 #결제 #견적' → 태그 칩 2개(같은 이름 하나로), '#새태그'·'#1번' → 점선 '새' 칩. 규칙에 안 맞는 'C# 공부'·'메일 a@b.com 확인'·'보고서 @ #'은 칩 없이 제목에 남음. '@개발 @영업'은 처음 것(개발)만 프로젝트</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>표시는 확인. 저장 시 태그 생성·연결은 Enter 저장 API 연결 전</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>P1-09-12</t>
+          <t>P1-09-05</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5678,7 +5862,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCR-COM-02 주요 동작</t>
+          <t>P1-09</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5698,35 +5882,31 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1) 해석 칩 클릭</t>
+          <t>1) 입력 후 Esc 2) 완전히 빈 입력(공백만 포함)에서 Enter 3) '@영업 !높음'처럼 낱말만 있고 제목이 없는 입력</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>그 값만 바꾸는 드롭다운</t>
+          <t>Esc는 입력 비움, 완전히 빈 입력 Enter는 조용히 무시, 제목이 비면 "할 일 이름을 적어 주세요" 안내(저장 안 함)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] Esc → 입력 비움, 빈 입력 Enter 무시, '@영업 #견적'처럼 제목이 비면 칩과 '할 일 이름을 적어 주세요'</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>P1-09-06</t>
+          <t>P1-09-12</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5736,7 +5916,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-62</t>
+          <t>P1-09, SCR-COM-02 주요 동작</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5756,35 +5936,35 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
+          <t>1) 해석 칩 클릭</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
+          <t>그 값만 바꾸는 드롭다운</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
+          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>P1-09-07</t>
+          <t>P1-09-06</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5794,7 +5974,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>UX-09</t>
+          <t>P1-09, REC-04, D-62</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5814,17 +5994,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
+          <t>1) '25-26 테스트', '14-13 테스트', '!아주높음 테스트' 2) '9-3 회의', '9:30-10 회의', '23-24 작업'</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
+          <t>해석 안 되는 부분은 칩 없이 제목으로 남음. 끝 시각이 시작보다 앞서면 오후로 봄(9-3 → 09:00~15:00), 24:00까지 허용</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '25-26 테스트'·'14-13 테스트'·'!아주높음 테스트' → 칩 없이 제목으로 남음(오류 없음). '9-3 회의' → 09:00–15:00, '9:30-10 회의' → 09:30–10:00, '23-24 작업' → 23:00–24:00</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -5833,12 +6013,16 @@
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>시간 규칙(끝이 시작보다 앞서면 오후, 24:00까지)은 docs/개정대기_화면정의서.md P1-09 항목 기준</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>P1-09-11</t>
+          <t>P1-09-07</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5848,7 +6032,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>P1-09, UX-09</t>
+          <t>UX-09</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -5858,7 +6042,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5868,45 +6052,41 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
+          <t>1) 입력창 밖에서 N 키(한글 상태 포함)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
+          <t>입력창 밖에서 N → 빠른 입력창으로 포커스. 입력창·모달 안에서는 n이 그대로 입력됨</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖 N → 빠른 입력창 포커스(홈). 다른 화면(/tasks·/calendar)에서 N → 홈으로 이동해 입력창 포커스. 한글 상태(code=KeyN, key=ㅜ)도 동작. 입력창 안에서는 n이 그대로 입력됨. Shift+N은 무시</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
-        </is>
-      </c>
+      <c r="L103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>P1-09-08</t>
+          <t>P1-09-11</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SCR-ONB-02</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>P1-09, REC-04, D-67</t>
+          <t>P1-09, UX-09</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5916,7 +6096,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5926,45 +6106,45 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
+          <t>1) 한글 입력 중(조합 중) Enter 2) 조합을 끝낸 뒤 Enter</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>문법 표(시간·@프로젝트·#태그·!우선순위·~마감·날짜(시간 없이 쓰면 마감일))와 예시 3개(새 기호), 예시 클릭 시 입력창에 채워짐, Esc로 닫으면 ? 버튼으로 포커스 복귀</t>
+          <t>조합 중 Enter는 무시(저장·제출 안 됨), 조합이 끝난 뒤 Enter만 동작</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] 문법 표: 시간 / @영업 프로젝트(없으면 새로 만들지 물어봐요) / #결제 #견적 태그(여러 개 가능, 없으면 저장할 때 만들어요) / !높음·!낮음 / ~금·~10/12 마감일 / 오늘·내일·다음주 수요일 날짜(시간 없이 쓰면 마감일). 예시 3개 @·# 기호로 갱신. Esc로 닫으면 ? 버튼으로 포커스</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>[이전 FAIL 증거 evidence/P1/P1-09-08.png]</t>
+          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>P1-09-09</t>
+          <t>P1-09-08</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SCR-CAL-06</t>
+          <t>SCR-ONB-02</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>P1-09, SCH-02</t>
+          <t>P1-09, REC-04, D-67</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5979,50 +6159,50 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 @영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
+          <t>1) 빠른 입력 ? 아이콘 2) 예시 클릭</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 시간 칩 누르면 '자세히'(CAL-07)로, Esc는 임시 블록 제거. '업무로도 만들기' 토글은 업무 API 연결(P1-03) 전이라 숨김</t>
+          <t>문법 표(시간·@프로젝트·#태그·!우선순위·~마감·날짜(시간 없이 쓰면 마감일))와 예시 3개(새 기호), 예시 클릭 시 입력창에 채워짐, Esc로 닫으면 ? 버튼으로 포커스 복귀</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] [D-67 재실행] 문법 표: 시간 / @영업 프로젝트(없으면 새로 만들지 물어봐요) / #결제 #견적 태그(여러 개 가능, 없으면 저장할 때 만들어요) / !높음·!낮음 / ~금·~10/12 마감일 / 오늘·내일·다음주 수요일 날짜(시간 없이 쓰면 마감일). 예시 3개 @·# 기호로 갱신. Esc로 닫으면 ? 버튼으로 포커스</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
+          <t>[이전 FAIL 증거 evidence/P1/P1-09-08.png]</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>P1-09-10</t>
+          <t>P1-09-09</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-02</t>
+          <t>SCR-CAL-06</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>P1-09, SCH-02</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6037,17 +6217,17 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
+          <t>로그인 상태(qa- 계정), 캘린더(P1-07) 구현 후</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력 포커스</t>
+          <t>1) 캘린더 빈 칸 클릭 → 팝오버에 '회의 @영업' 입력 2) 입력에 '15-16' 포함해 다시 3) 업무로도 만들기 끄고 저장 4) Esc</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 상위 3개 제안</t>
+          <t>선택 시간이 기본, 입력 시간이 있으면 덮어씀, 시간 칩 누르면 '자세히'(CAL-07)로, Esc는 임시 블록 제거. '업무로도 만들기' 토글은 업무 API 연결(P1-03) 전이라 숨김</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -6063,24 +6243,24 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
+          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>P1-10-01</t>
+          <t>P1-09-10</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-COM-02</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6095,40 +6275,40 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 같은 요일·시간대 기록 이력(P2 기록 기능 전이면 N/A)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
+          <t>1) 빠른 입력 포커스</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
+          <t>자주 하는 업무 상위 3개 제안</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
-        </is>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎) / [재검증 a5bb168] vite dev에서도 입력창 Ctrl+K → 팔레트 검색 입력에 포커스, Esc로 닫히고 빠른 입력창 값 유지(관찰 ① 해소)</t>
+          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>P1-10-02</t>
+          <t>P1-10-01</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6158,17 +6338,17 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
+          <t>1) 입력창 밖·빠른 입력창 안에서 각각 Ctrl+K(맥 ⌘K, 한글 상태 포함) 2) ↑↓ 이동 3) Enter 4) Esc</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
+          <t>어느 화면·입력창 안에서도 열림, 입력 전 최근 사용 항목, 항목 오른쪽 단축키, Enter 실행, Esc 닫기</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 입력창 밖·빠른 입력창 안·한글 상태(code=KeyK) 모두 Ctrl+K로 열림, 검색 입력에 포커스. 처음엔 최근 항목 없음, 한 번 쓰면 '최근 사용' 그룹. '업무 추가' 오른쪽에 N 표시. ↑↓ 이동(끝에서 순환), Enter 실행, Esc 닫기, Ctrl+K 다시 누르면 닫힘</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -6179,14 +6359,14 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
+          <t>mock 프로덕션 빌드(vite build --mode mock + preview)에서 확인. vite dev(StrictMode)에서는 입력창에서 Ctrl+K로 열면 포커스가 입력창에 남아 Esc가 입력을 지우고 팔레트가 안 닫힘 — 개발 모드에서만 생기는 현상이라 결함으로 보지 않음(effect 두 번 실행으로 포커스 복원 cleanup이 먼저 돎) / [재검증 a5bb168] vite dev에서도 입력창 Ctrl+K → 팔레트 검색 입력에 포커스, Esc로 닫히고 빠른 입력창 값 유지(관찰 ① 해소)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>P1-10-08</t>
+          <t>P1-10-02</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6196,7 +6376,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01, SCR-COM-03 ②</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6211,40 +6391,40 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 제목 일부·일지 내용 입력</t>
+          <t>1) '업무목록'·'캘린더' 입력해 이동 2) '10/12', '다음주 수요일' 입력</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>업무 검색·일지 검색 결과 그룹</t>
+          <t>화면 이동, 날짜는 'm/d(요일) 캘린더 보기' 항목으로 그날 캘린더 이동</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '업무목록' → /tasks, '캘린더' → /calendar. '10/12' → '10/12(월) 캘린더 보기' → /calendar?date=2026-10-12, '다음주 수요일' → '10/14(수) 캘린더 보기'</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
+          <t>업무·일지 검색은 P1-10-08로 분리. 캘린더 화면(P1-07)은 아직 자리 화면이라 date 파라미터 반영은 P1-07에서 확인</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>P1-10-03</t>
+          <t>P1-10-08</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6254,7 +6434,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-01</t>
+          <t>P1-10, UX-01, SCR-COM-03 ②</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6269,50 +6449,50 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무·일지 있음</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
+          <t>1) 업무 제목 일부·일지 내용 입력</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
+          <t>업무 검색·일지 검색 결과 그룹</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
-        </is>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
+          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>P1-10-04</t>
+          <t>P1-10-03</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-04</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>P1-10, UX-01</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6332,35 +6512,35 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
+          <t>1) 어떤 명령과도 맞지 않는 문구 입력 후 Enter</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
+          <t>첫 항목 "…을(를) 업무로 추가", 실행하면 업무 생성</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] '주간 보고서 정리' → 유일 항목 "‘주간 보고서 정리’를 업무로 추가", Enter → 홈 이동·빠른 입력창에 그 문구 채움·포커스. 조사: '보고서 작성'→을, '3번'→을, '견적서'·'회의'→를, 'API'→을(를)</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+          <t>업무 생성 자체는 Enter 저장(API) 이후</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>P1-10-09</t>
+          <t>P1-10-04</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6370,7 +6550,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03, UX-09</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6390,31 +6570,35 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
+          <t>1) 업무 3개 연속 보관 2) 토스트 확인 3) 마우스 올린 채 6초 4) 입력창 밖에서 Ctrl+Z</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
+          <t>토스트 하나에 '3개' 누적, 마우스 올리면 유지, 입력창 밖 Ctrl+Z로 복원, 데스크톱 좌하단</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
-        </is>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>P1-10-05</t>
+          <t>P1-10-09</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6424,12 +6608,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-03</t>
+          <t>P1-10, UX-03, UX-09</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6439,55 +6623,51 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일에서 업무 보관</t>
+          <t>1) 빠른 입력창에 글자 입력 후 Ctrl+Z</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>토스트가 하단 탭 위에 표시</t>
+          <t>입력창 안 Ctrl+Z는 글자 되돌리기(업무 되돌리기로 가로채지 않음)</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 빠른 입력창에서 '보고서 작성' 입력 후 Ctrl+Z → '보고서 작', 다시 → '보고서 '(브라우저 글자 되돌리기). 입력창 밖 Ctrl+Z(되돌릴 항목 없음)는 아무 일 없음</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
-        </is>
-      </c>
+      <c r="L113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>P1-10-06</t>
+          <t>P1-10-05</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-04</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>P1-10, UX-04</t>
+          <t>P1-10, UX-03</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6497,55 +6677,55 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 계정</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 직후 첫 화면</t>
+          <t>1) 모바일에서 업무 보관</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
+          <t>토스트가 하단 탭 위에 표시</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>[재검증 2026-10-06, 444466e 소스 확인] 홈 빈 상태 안내가 '시간·@프로젝트·#태그·!우선순위·~마감을 같이 적으면 알아서 나눠 저장해요.'로 바뀜(453401f)</t>
-        </is>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>[최초 FAIL 증거 evidence/P1/P1-10-06.png] 이번엔 소스로만 확인. 화면은 다음 실행 때 함께 봄</t>
+          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>P1-10-07</t>
+          <t>P1-10-06</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-03</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>UX-09, 2.5</t>
+          <t>P1-10, UX-04</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6555,22 +6735,22 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>막 가입한 계정</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
+          <t>1) 가입 직후 첫 화면</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+          <t>설정 요구 없이 "오늘 할 일을 한 줄로 적어 보세요" 안내와 문법 예시, 빠른 입력 바로 사용 가능</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
+          <t>[재검증 2026-10-06, 444466e 소스 확인] 홈 빈 상태 안내가 '시간·@프로젝트·#태그·!우선순위·~마감을 같이 적으면 알아서 나눠 저장해요.'로 바뀜(453401f)</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
@@ -6581,29 +6761,29 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고) / [재검증 a5bb168] dev 모드에서도 같은 결과</t>
+          <t>[최초 FAIL 증거 evidence/P1/P1-10-06.png] 이번엔 소스로만 확인. 화면은 다음 실행 때 함께 봄</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>P1-11-01</t>
+          <t>P1-10-07</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>SCR-HOME-01</t>
+          <t>SCR-COM-03</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05</t>
+          <t>UX-09, 2.5</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6613,28 +6793,40 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 직후 홈 확인</t>
+          <t>1) 팔레트·모달이 열린 상태에서 Tab 순서·포커스 표시 2) 닫은 뒤 포커스 위치</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
+          <t>포커스가 팔레트 안에 갇힘, 닫으면 원래 위치로 복귀</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06] 팔레트 열린 동안 Tab은 검색 입력에 머묾(포커스 가둠), Esc로 닫으면 연 곳(빠른 입력창)으로 포커스 복귀·입력값 유지</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>mock 프로덕션 빌드 기준(P1-10-01 비고 참고) / [재검증 a5bb168] dev 모드에서도 같은 결과</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>P1-11-02</t>
+          <t>P1-11-01</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6659,28 +6851,40 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 업무·일정 있음</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
+          <t>1) 로그인 직후 홈 확인</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
+          <t>P1 영역 ①헤더(날짜·인사·빠른 입력) ②요약 카드 4개 ④남은 업무 ⑥다가오는 일정 7일. ③⑤⑦은 P2·P3라 없음</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 헤더(10월 6일 화요일·인사·빠른 기록), 요약 카드(남은 업무·오늘 일정·이번 주 완료), 남은 업무, 다가오는 일정</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>요약 카드 3개 — 화면정의서의 4개 중 '확인 대기'는 REC-03 P2</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>P1-11-03</t>
+          <t>P1-11-02</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6705,28 +6909,44 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
+          <t>1) 요약 카드 숫자를 업무·일정 데이터와 대조 2) 카드 클릭</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
+          <t>남은 업무(마감 초과 수)·오늘 일정(남은 수)·이번 주 완료 숫자 일치, 클릭 시 해당 목록으로 이동</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 남은 업무 7(초과 1) → /tasks, 오늘 일정 3(2개 남음) → /calendar/day/2026-10-06, 숫자는 mock 데이터와 일치. 결함: 이번 주 완료 → /tasks?status=DONE에서 '상태를 하나 이상 골라 주세요', 완료 업무는 접힌 영역에만</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-11-02.png</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>P1-11-04</t>
+          <t>P1-11-03</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6736,7 +6956,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>P1-11, SCH-05, D-25</t>
+          <t>P1-11, SCH-05</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6751,28 +6971,36 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
+          <t>로그인 상태(qa- 계정), 마감 초과·오늘·이번 주·날짜 없음 업무</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>1) 다가오는 일정 영역</t>
+          <t>1) 남은 업무 영역 2) 마감순/프로젝트 전환</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
+          <t>마감 초과 → 오늘 → 이번 주 → 날짜 없음 순 그룹, 전환 동작</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 마감 초과 1 / 오늘 2 / 이번 주 3 + 날짜 없는 업무 1개 접힘, 프로젝트 전환 → 개발 2 / 영업 2 / 공통 1 / 프로젝트 없음 2</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>P1-11-05</t>
+          <t>P1-11-04</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6782,7 +7010,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>P1-11, SCH-05, D-25</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -6797,28 +7025,36 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 7일 안 일정·반복 일정</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1) 홈 빠른 입력으로 업무 추가</t>
+          <t>1) 다가오는 일정 영역</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
+          <t>7일 범위만, 반복 회차 전개, 공휴일 포함</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 오늘부터 7일(오늘 지난 일정은 제외), 반복 회차 펼침, 10/9(금) 한글날 '공휴일' 항목, 최대 8개 + 'n개 더 · 캘린더에서 보기'</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>P1-11-06</t>
+          <t>P1-11-05</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6828,12 +7064,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, 2.4</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6843,28 +7079,36 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1) 폭별 카드 배치</t>
+          <t>1) 홈 빠른 입력으로 업무 추가</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
+          <t>남은 업무·요약 카드가 새로고침 없이 갱신</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 홈 빠른 입력 'QA 홈 업무 ~오늘' → 남은 업무 7→8, 오늘 2→3이 새로고침 없이 갱신</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>P1-11-07</t>
+          <t>P1-11-06</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6874,7 +7118,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>2.5 (로딩)</t>
+          <t>NFR-06, 2.4</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -6889,43 +7133,55 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 390px·800px·1280px</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1) 느린 네트워크로 홈 진입</t>
+          <t>1) 폭별 카드 배치</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
+          <t>모바일 1열, 태블릿 2열, 데스크톱 3열, 가로 스크롤 없음</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 390px 섹션 1열, 800·1024·1280px 2열, 가로 스크롤 없음</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>요약 카드 3개는 모든 폭에서 한 줄. P1 섹션이 2개라 데스크톱도 2열</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>P1-12-01</t>
+          <t>P1-11-07</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>SCR-HOME-01</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>2.5 (로딩)</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6935,38 +7191,50 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>막 가입한 미인증 계정</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
+          <t>1) 느린 네트워크로 홈 진입</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
+          <t>0.3초 넘으면 콘텐츠 영역 스켈레톤, 셸은 유지</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>코드 근거(화면 확인 불가): HomeDashboard.tsx 199·341행이 스켈레톤 대신 '불러오는 중…'을 지연 없이 표시. 화면정의서 2장은 스켈레톤 + 0.3초 안에 끝나면 표시 안 함</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>dev:mock 응답 지연이 300ms 고정이라 느린 응답을 재현할 수 없음</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02</t>
+          <t>P1-12-01</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-01</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08, D-41, D-53</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6976,22 +7244,22 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 qa- 주소(사용자 승인)</t>
+          <t>막 가입한 미인증 계정</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
+          <t>1) 앱 화면 진입 2) 닫기 3) 새로고침 4) 로그아웃 후 재로그인</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
+          <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -7002,7 +7270,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>P1-12-03</t>
+          <t>P1-12-02</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -7012,12 +7280,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>P1-12, D-57</t>
+          <t>P1-12, AUTH-08, D-41, D-53</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7027,17 +7295,17 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>P1-12-02 메일</t>
+          <t>수신 가능한 qa- 주소(사용자 승인)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
+          <t>1) 가입 2) 받은 메일 확인(제목·본문·텍스트 버전·발신자)</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
+          <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -7048,22 +7316,22 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>P1-12-04</t>
+          <t>P1-12-03</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-08</t>
+          <t>SCR-MAIL-01</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-12, D-57</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7073,17 +7341,17 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>P1-12-02 메일</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
+          <t>1) 메일 원본에서 발신 주소·보내는 사람 이름 확인 2) 스팸함 여부</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
+          <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -7094,7 +7362,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>P1-12-05</t>
+          <t>P1-12-04</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -7124,12 +7392,12 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번 입력</t>
+          <t>1) 배너 인증하기 2) 6자리 붙여넣기</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
+          <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -7140,7 +7408,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>P1-12-06</t>
+          <t>P1-12-05</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -7160,22 +7428,22 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 발급 후 10분 경과</t>
+          <t>1) 틀린 코드 5번 입력</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
+          <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -7186,7 +7454,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>P1-12-07</t>
+          <t>P1-12-06</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -7206,22 +7474,22 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정</t>
+          <t>로컬(시간 조작 또는 짧은 TTL 설정)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 다시 받기 직후 다시 누르기</t>
+          <t>1) 코드 발급 후 10분 경과</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
+          <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -7232,7 +7500,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>P1-12-08</t>
+          <t>P1-12-07</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -7242,7 +7510,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08, D-64</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -7252,22 +7520,22 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>로컬(실제 메일 10통 발송 회피)</t>
+          <t>미인증 계정</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1) 가입 직후 자동 발송 1통 포함, 24시간 안에 11번째 발송 요청 2) 첫 발송 24시간 뒤 다시 요청</t>
+          <t>1) 코드 다시 받기 직후 다시 누르기</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
+          <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -7278,7 +7546,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>P1-12-09</t>
+          <t>P1-12-08</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -7288,7 +7556,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>P1-12, D-64</t>
+          <t>P1-12, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -7298,22 +7566,22 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>코드 2번 발급</t>
+          <t>로컬(실제 메일 10통 발송 회피)</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>1) 먼저 받은 코드로 인증</t>
+          <t>1) 가입 직후 자동 발송 1통 포함, 24시간 안에 11번째 발송 요청 2) 첫 발송 24시간 뒤 다시 요청</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
+          <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -7324,42 +7592,42 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>P1-12-10</t>
+          <t>P1-12-09</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-08</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>P1-12, AUTH-08</t>
+          <t>P1-12, D-64</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>계정 A·B</t>
+          <t>코드 2번 발급</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
+          <t>1) 먼저 받은 코드로 인증</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>거부(코드는 계정별), 비로그인 401</t>
+          <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -7370,7 +7638,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>P1-12-12</t>
+          <t>P1-12-10</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -7380,7 +7648,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>P1-12, P1-13, D-65</t>
+          <t>P1-12, AUTH-08</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -7390,22 +7658,22 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>로컬(운영 IP 제한 회피), 계정 여러 개</t>
+          <t>계정 A·B</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 IP에서 인증 코드·재설정 코드 메일을 합쳐 1시간에 11번 요청 2) X-Client-Ip 헤더 없이 요청</t>
+          <t>1) A의 코드로 B 세션에서 인증 요청 2) 비로그인으로 인증 확인 API 호출</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
+          <t>거부(코드는 계정별), 비로그인 401</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -7416,42 +7684,42 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>P1-12-11</t>
+          <t>P1-12-12</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-07</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>P1-12</t>
+          <t>P1-12, P1-13, D-65</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>인증 완료 계정</t>
+          <t>로컬(운영 IP 제한 회피), 계정 여러 개</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>1) 앱 화면 진입</t>
+          <t>1) 같은 IP에서 인증 코드·재설정 코드 메일을 합쳐 1시간에 11번 요청 2) X-Client-Ip 헤더 없이 요청</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>배너 표시 안 됨</t>
+          <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -7462,17 +7730,17 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>P1-13-01</t>
+          <t>P1-12-11</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-COM-07</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>P1-13, SCR-AUTH-02 ④</t>
+          <t>P1-12</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -7487,17 +7755,17 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>비로그인</t>
+          <t>인증 완료 계정</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
+          <t>1) 앱 화면 진입</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>/password/forgot 이동</t>
+          <t>배너 표시 안 됨</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
@@ -7508,22 +7776,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>P1-13-02</t>
+          <t>P1-13-01</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-65</t>
+          <t>P1-13, SCR-AUTH-02 ④</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7538,12 +7806,12 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
+          <t>1) 로그인 화면의 비밀번호 찾기 링크</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
+          <t>/password/forgot 이동</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -7554,7 +7822,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>P1-13-03</t>
+          <t>P1-13-02</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -7564,12 +7832,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-13, AUTH-03, D-65</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7584,12 +7852,12 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1) 빈 값·형식 오류 이메일 제출</t>
+          <t>1) 가입된 이메일로 요청 2) 가입되지 않은 이메일로 요청</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
+          <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -7600,17 +7868,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>P1-13-04</t>
+          <t>P1-13-03</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>SCR-MAIL-02</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-41</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -7620,22 +7888,22 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>수신 가능한 계정</t>
+          <t>비로그인</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>1) 재설정 메일 확인</t>
+          <t>1) 빈 값·형식 오류 이메일 제출</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
+          <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -7646,17 +7914,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>P1-13-05</t>
+          <t>P1-13-04</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-MAIL-02</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-13, AUTH-03, D-41</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -7671,17 +7939,17 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>수신 가능한 계정</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
+          <t>1) 재설정 메일 확인</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
+          <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -7692,7 +7960,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>P1-13-06</t>
+          <t>P1-13-05</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7702,7 +7970,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, D-38</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -7717,17 +7985,17 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>코드 확인됨</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
+          <t>1) 코드 입력 전 새 비밀번호 칸 상태 2) 맞는 코드 입력</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
+          <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -7738,7 +8006,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>P1-13-07</t>
+          <t>P1-13-06</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7748,7 +8016,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03, AUTH-08, D-64</t>
+          <t>P1-13, AUTH-03, D-38</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -7763,17 +8031,17 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
+          <t>코드 확인됨</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
+          <t>1) 규칙 위반 비밀번호 2) 한글 25자 3) 확인 불일치</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
+          <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -7784,17 +8052,17 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>P1-13-12</t>
+          <t>P1-13-07</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02, 05</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>P1-13, P1-14, D-64</t>
+          <t>P1-13, AUTH-03, AUTH-08, D-64</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -7804,22 +8072,22 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>로컬, 10회 실패로 잠긴 계정</t>
+          <t>미인증 계정, 다른 브라우저에도 로그인해 둠</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1) 잠긴 상태에서 비밀번호 재설정 완료 2) 곧바로 새 비밀번호로 로그인</t>
+          <t>1) 새 비밀번호 저장 2) 다른 브라우저에서 API 호출·새로고침 3) 옛 비밀번호 로그인 4) 새 비밀번호 로그인</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>잠금이 풀려 바로 로그인 성공</t>
+          <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -7830,17 +8098,17 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>P1-13-08</t>
+          <t>P1-13-12</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-05</t>
+          <t>SCR-AUTH-02, 05</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>P1-13, AUTH-03</t>
+          <t>P1-13, P1-14, D-64</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -7850,22 +8118,22 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>운영(메일 수신)</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>재설정 코드 받음</t>
+          <t>로컬, 10회 실패로 잠긴 계정</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 코드 5번</t>
+          <t>1) 잠긴 상태에서 비밀번호 재설정 완료 2) 곧바로 새 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
+          <t>잠금이 풀려 바로 로그인 성공</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -7876,12 +8144,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>P1-13-09</t>
+          <t>P1-13-08</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04</t>
+          <t>SCR-AUTH-05</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7896,22 +8164,22 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영(메일 수신)</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>재설정 코드 받음</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
+          <t>1) 틀린 코드 5번</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
+          <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -7922,17 +8190,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>P1-13-10</t>
+          <t>P1-13-09</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02, 04</t>
+          <t>SCR-AUTH-04</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>P1-13, P1-14</t>
+          <t>P1-13, AUTH-03</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -7942,22 +8210,22 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>잠긴 계정</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 안내의 재설정 링크</t>
+          <t>1) 60초 안 재요청 2) 하루 11번째 요청</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>/password/forgot 이동</t>
+          <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -7968,22 +8236,22 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>P1-13-11</t>
+          <t>P1-13-10</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-04, 05</t>
+          <t>SCR-AUTH-02, 04</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>NFR-06, NFR-13</t>
+          <t>P1-13, P1-14</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7993,17 +8261,17 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>비로그인, 390px, 오프라인 전환</t>
+          <t>잠긴 계정</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
+          <t>1) 잠금 안내의 재설정 링크</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
+          <t>/password/forgot 이동</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -8014,22 +8282,22 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>P1-14-01</t>
+          <t>P1-13-11</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>SCR-AUTH-02</t>
+          <t>SCR-AUTH-04, 05</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09</t>
+          <t>NFR-06, NFR-13</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8039,17 +8307,17 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>qa- 계정</t>
+          <t>비로그인, 390px, 오프라인 전환</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
+          <t>1) 모바일 폭 확인 2) 오프라인 전환</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
+          <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
@@ -8060,7 +8328,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>P1-14-02</t>
+          <t>P1-14-01</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -8090,23 +8358,35 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
+          <t>1) 틀린 비밀번호로 연속 로그인하며 응답 시간 측정</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
+          <t>실패할수록 응답이 늦어지고 "잠시 후 다시 시도해 주세요" + 버튼 카운트다운(429 TOO_MANY_REQUESTS)</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 틀린 비밀번호 3회 → '이메일 또는 비밀번호가 맞지 않아요'만 표시. mock은 응답 지연이 없어 '잠시 후 다시 시도해 주세요' 줄(900ms 이상 늦은 응답일 때)이 안 뜨는 게 맞음</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>점진 지연·429 TOO_MANY_REQUESTS 카운트다운은 실서버에서 확인</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>P1-14-03</t>
+          <t>P1-14-02</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -8126,33 +8406,45 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
+          <t>qa- 계정</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>1) 잠금 해제 시점 이후 로그인</t>
+          <t>1) 10회 실패 2) 맞는 비밀번호로 로그인</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
+          <t>"15분 동안 로그인할 수 없어요…" + 재설정 링크 + '로그인 · m:ss 후 가능', 잠금 중에는 맞는 비밀번호도 거부</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] (UI만) locked@example.com → '15분 동안 로그인할 수 없어요. 비밀번호를 10번 잘못 입력했어요… 재설정하세요'(링크), 버튼 '로그인 · 14:51 후 가능' disabled, 초 단위로 줄어듦</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K149" s="2" t="inlineStr"/>
-      <c r="L149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>10회 실패로 잠기는지, 잠금 중 맞는 비밀번호 거부는 실서버에서 확인</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>P1-14-04</t>
+          <t>P1-14-03</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -8162,53 +8454,61 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>P1-14, D-61</t>
+          <t>P1-14, AUTH-09</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>로컬</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>없는 이메일</t>
+          <t>로컬(잠금 시간 단축 또는 시각 조작)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>1) 없는 이메일로 10회 이상 실패</t>
+          <t>1) 잠금 해제 시점 이후 로그인</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
+          <t>잠금 풀림(영구 잠금 없음), 성공 시 실패 횟수 초기화</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>dev:mock에서는 확인할 수 없음(실서버 필요)</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>P1-14-05</t>
+          <t>P1-14-04</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-AUTH-02</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>P1-14, AUTH-09, D-61</t>
+          <t>P1-14, D-61</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -8218,33 +8518,41 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>로컬</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>로컬(운영 IP 차단 위험 회피)</t>
+          <t>없는 이메일</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
+          <t>1) 없는 이메일로 10회 이상 실패</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
+          <t>계정 잠금 응답으로 계정 존재가 드러날 수 있음(D-61에서 허용). 없는 이메일도 IP 단위 제한(429)에 걸림을 확인</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>dev:mock에서는 확인할 수 없음(실서버 필요)</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>P1-14-06</t>
+          <t>P1-14-05</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -8254,54 +8562,66 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>P1-14, p1-14-springdoc-429</t>
+          <t>P1-14, AUTH-09, D-61</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
+          <t>로컬</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>로컬(운영 IP 차단 위험 회피)</t>
+        </is>
+      </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
+          <t>1) 같은 IP에서 여러 계정으로 빠르게 실패</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
+          <t>IP 단위 제한으로 429. X-Client-Ip 위조 헤더를 직접 보내도 무시됨(Gateway가 지움, D-61)</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>dev:mock에서는 확인할 수 없음(실서버 필요)</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>P1-X-01</t>
+          <t>P1-14-06</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01 (P1 완성)</t>
+          <t>P1-14, p1-14-springdoc-429</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8309,30 +8629,34 @@
           <t>운영</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>로그인 상태(qa- 계정), 390px</t>
-        </is>
-      </c>
+      <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
+          <t>1) contracts/generated/identity.json에서 /api/auth/login 응답 확인</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
+          <t>429와 RateLimitedProblem(retryAfterSeconds)이 명세 스냅샷에 들어 있음</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>[aa4d756] contracts/generated/identity.json /api/auth/login 응답 200·400·401·429, 429 → RateLimitedProblem + Retry-After 헤더</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>P1-X-02</t>
+          <t>P1-X-01</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -8342,12 +8666,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>SCR-COM-01</t>
+          <t>SCR-COM-01 (P1 완성)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8357,17 +8681,17 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>로그인 상태(qa- 계정), 390px</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>1) 화면 전환 중 표시</t>
+          <t>1) 하단 탭 더보기 2) 빠른 기록 버튼</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
+          <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
@@ -8378,22 +8702,22 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>P1-X-03</t>
+          <t>P1-X-02</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ④</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>NFR-13 (P0 TC-81 재확인)</t>
+          <t>SCR-COM-01</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8408,12 +8732,12 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
+          <t>1) 화면 전환 중 표시</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
+          <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
@@ -8424,17 +8748,17 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>P1-X-04</t>
+          <t>P1-X-03</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>SCR-SYS-02 ③</t>
+          <t>SCR-SYS-02 ④</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>NFR-13</t>
+          <t>NFR-13 (P0 TC-81 재확인)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -8454,12 +8778,12 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
+          <t>1) 화면을 연 채로 쿠키 삭제 2) 업무 목록 새로 불러오기 등 API를 부르는 동작</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
+          <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
@@ -8470,22 +8794,22 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>P1-X-05</t>
+          <t>P1-X-04</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>—(API)</t>
+          <t>SCR-SYS-02 ③</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>NFR-02, NFR-14</t>
+          <t>NFR-13</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8495,17 +8819,17 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>로그인 상태(qa- 계정)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
+          <t>1) 업무 상세·설정·캘린더에서 오프라인 전환</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>모두 403 ORIGIN_REJECTED</t>
+          <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
@@ -8516,7 +8840,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>P1-X-06</t>
+          <t>P1-X-05</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -8526,12 +8850,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>D-30</t>
+          <t>NFR-02, NFR-14</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>배포</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8546,12 +8870,12 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
+          <t>1) 새 쓰기 API(worklog 업무·일정·설정, identity 인증 코드·재설정)에 다른 Origin으로 POST·PATCH·DELETE</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
+          <t>모두 403 ORIGIN_REJECTED</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
@@ -8562,17 +8886,17 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>P1-X-07</t>
+          <t>P1-X-06</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>—(배포)</t>
+          <t>—(API)</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>D-56</t>
+          <t>D-30</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -8587,17 +8911,17 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>배포 브랜치 main 전환 후</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
+          <t>1) 목록 API cursor 페이지네이션 2) 오류 응답 형식</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
+          <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
@@ -8608,7 +8932,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>P1-X-08</t>
+          <t>P1-X-07</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -8618,7 +8942,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>P0-09</t>
+          <t>D-56</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -8633,17 +8957,17 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
+          <t>배포 브랜치 main 전환 후</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
+          <t>1) 운영(wy-worklog.com)에서 P0 완료 기준(가입·로그인·me·새로고침 유지)·Origin 403·x-vercel-cache 재확인</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
+          <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
@@ -8654,22 +8978,22 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>P1-X-09</t>
+          <t>P1-X-08</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>—(배포)</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>2.6 문구 말투, D-36</t>
+          <t>P0-09</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8679,17 +9003,17 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>로그인 상태(qa- 계정)</t>
+          <t>브라우저</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면 문구 말투 확인</t>
+          <t>1) P1 화면 전체 순회 중 콘솔 오류·실패한 리소스 확인</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
+          <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
@@ -8700,7 +9024,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>P1-X-10</t>
+          <t>P1-X-09</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8710,7 +9034,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>화면정의서 2.5 (키보드·터치)</t>
+          <t>2.6 문구 말투, D-36</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -8730,12 +9054,12 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+          <t>1) P1 새 화면 문구 말투 확인</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+          <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
@@ -8743,10 +9067,56 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr"/>
     </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>P1-X-10</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>화면정의서 2.5 (키보드·터치)</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>사용성</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>로그인 상태(qa- 계정)</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>1) P1 새 화면을 키보드만으로 조작 2) 390px 터치 영역 측정</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L162"/>
+  <autoFilter ref="A1:L163"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9185,7 +9555,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1-09·10, P1-01, P1-02, P1-07 일부, P1-03·04, 재검증)</t>
+          <t>2026-10-06 (P1-09·10, P1-01, P1-02, P1-03·04, P1-06·07·08, P1-11, P1-14, 재검증)</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9579,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9591,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>기능 123, 사용성 25, 보안 9, 배포 4</t>
+          <t>기능 123, 사용성 26, 보안 9, 배포 4</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9603,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>미실행 89, PASS 49, BLOCKED 17, FAIL 6</t>
+          <t>미실행 57, PASS 80, BLOCKED 20, FAIL 4, N/A 1</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9615,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>미해결(fix(P1-03) 묶음 재검증 대상): P1-03-01 패널 열림 제목 폭, P1-03-04·08·07·13·P1-04-04 포커스 유실, P1-03-05 빨강 미적용·날짜 입력 중간값 저장, P1-03-09 보관 업무 마감일 편집. 해결: P1-02-11, P1-09-01·08, P1-01-11, P1-10-06, P1-02-09·10</t>
+          <t>미해결: P1-07-11 할 일 상자 열림 시 월 그리드 가려짐, P1-07-12 연 보기 열 수(문서와 다름, pm 판단 대기), P1-11-02 이번 주 완료 링크, P1-11-07 로딩 스켈레톤 없음, 빠른 입력 ? 버튼 32px(P1-07-17 비고), 패널 슬라이더 Esc(P1-03-13 비고), J/K 방향(P1-07-03 비고). 해결: P1-03-01·04·05·07·08·09·13, P1-04-04, P1-02-11, P1-09-01·08, P1-01-11, P1-10-06, P1-02-09·10</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -601,7 +601,11 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -647,7 +651,11 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -693,7 +701,11 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -739,7 +751,11 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1981,7 +1997,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>새로고침·탭 닫기 확정은 실서버(운영 배포 뒤 또는 로컬 백엔드)에서 재확인 필요. 최초 FAIL 2026-10-06</t>
+          <t>[병합 직후 운영 확인] 새로고침·탭 닫기 확정은 실서버(운영 배포 뒤 또는 로컬 백엔드)에서 재확인 필요. 최초 FAIL 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2905,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>pm: 병합 후 운영 확인 때</t>
+          <t>[병합 직후 운영 확인] pm: 병합 후 운영 확인 때</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3017,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>[최초 비고 21c8f0e] 닫은 뒤 포커스 BODY → 해결. 남은 비고: 슬라이더에 포커스가 있으면 Esc로 안 닫힘 — pm 결정으로 수정 배정, 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[최초 비고 21c8f0e] 닫은 뒤 포커스 BODY → 해결. [재검증 15ae612] 슬라이더에서 Esc → 닫힘·연 행 포커스, 메모·제목 칸은 Esc로 안 닫힘 → 해결</t>
         </is>
       </c>
     </row>
@@ -3324,10 +3340,22 @@
           <t>생성·수정 반영. 삭제는 확인창 없이 바로 빠지고 되돌리기 토스트, 토스트가 닫힐 때·새로고침·탭 닫기·탭 전환 때 확정(D-72)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 일정 만들기(전체 폼) 제목·10/7·13:00~14:30·메모 → '일정을 만들었어요', 다시 열면 값 그대로, 제목·종료 수정 → '일정을 저장했어요', 삭제는 확인창 없음 + 탭 전환(visibilitychange) 때 바로 확정</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>새로고침·탭 닫기 때 확정(keepalive)은 dev:mock 불가 — 병합 직후 운영 목록</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3370,8 +3398,16 @@
           <t>주·일 보기 종일 행, 월 보기 칩으로 표시</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 종일 체크 → 시간 칸 숨김(날짜 2칸), 저장 allDay 10/8, 주 보기 종일 행(높이 24), 월 칩 높이 24</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
     </row>
@@ -3416,10 +3452,22 @@
           <t>해당 칸 아래 오류(서버 errors[] 포함), 저장 안 됨</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 종료&lt;시작 저장 → 종료 아래 '끝나는 시각을 시작보다 뒤로 골라 주세요', 저장 안 됨. 결함: 종료 input에 aria-invalid·aria-describedby 없고 포커스가 × 버튼으로 감</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>서버 errors[]는 클라이언트가 먼저 막아 확인 불가. 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3462,10 +3510,22 @@
           <t>겹침 경고 없이 생성, 주 보기에서 나란히 배치</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 같은 시간 1시간 일정 2개 경고 없이 생성, 나란히 배치. 블록 폭 1280px(패널 열림) 23.4px·중심 간격 27.4px(간격 예외 충족), 1440px 34.9px, 1024px(패널 닫힘) 24.9px</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>1024px 패널 열림에서 18px·겹침 → P1-07-15 결함</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3508,10 +3568,22 @@
           <t>B 모달 상단 충돌 띠 + [새로 불러오기]</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 두 탭: A 제목 저장 → B 메모 저장 → 모달 위 충돌 띠 '다른 곳에서 먼저 수정됐어요…'+[새로 불러오기](정상). 결함: 새로 불러오기 뒤 모달 제목이 옛 값(그리드는 최신)</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>바뀐 칸만 보내서 A 값이 덮어써지지는 않음. 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3554,10 +3626,22 @@
           <t>연결·해제 반영, 일정 프로젝트는 업무를 따름, 업무 상세 연결 일정 목록에도 반영</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 일정 모달에 '연결 업무'(검색·새 업무·해제) 칸 없음, 업무 상세 '연결된 일정'은 목록 없이 '캘린더에 배치된 일정이 있어요' 문구만</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>pm 결정: P1 범위, 구현(모달 frontend2, 업무 상세 frontend) — 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3603,7 +3687,11 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3649,7 +3737,11 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3692,8 +3784,16 @@
           <t>지정 범위 회차만 표시, 종료 없음은 먼 미래 달에도 표시</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 매일·날짜까지 10/15 → 10/12~15 4회, 매월·종료 없음 → 2027-06-20·2028-03-20에도 표시</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
     </row>
@@ -3738,10 +3838,22 @@
           <t>선택한 요일에만 회차 표시</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 주 보기 10/12 주에서 일정 만들기(기본 10/12 월) → 날짜 10/13(화) → 매주 → 요일 기본값이 월·화 둘 다 → 목 추가해 저장하면 MONDAY·TUESDAY·THURSDAY, 10/19·26(월) 회차 생김</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>고르지 않은 처음 날짜의 요일이 남음 — 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3842,10 +3954,22 @@
           <t>해당 회차만 사라짐 / 반복 전체 사라짐, 되돌리기 토스트</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 회차 삭제 → alertdialog '반복 일정을 삭제할까요?' → 이 일정만: 그 회차만 빠짐+되돌리기 / 모든 일정: 그리드·목록 0, 토스트 닫힌 뒤 시리즈 삭제</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>범위 대화상자 확인 뒤 포커스 BODY(범위 대화상자 뒤 포커스 비고 — frontend2 작업 중, 판정 보류)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3946,8 +4070,16 @@
           <t>Esc로 닫힘(변경 없음), 키보드만으로 선택·확인 가능</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 삭제 범위 alertdialog: 열면 '이 일정만' 라디오에 포커스, ↓↑로 선택, Tab → 취소 → 확인, Enter로 실행. Esc → 변경 없음(편집 모달도 함께 닫힘)</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
     </row>
@@ -4050,8 +4182,16 @@
           <t>각 보기가 정의된 경로로 열리고 새로고침·뒤로 가기에도 같은 상태(URL이 상태 기준)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] day/week/month/year/list 주소를 새로고침해도 같은 보기·제목, 단축키 M→D로 이동한 뒤 뒤로 가기 두 번에 차례대로 복귀</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
     </row>
@@ -4109,7 +4249,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>pm 결정 2026-10-06: J=다음·K=이전으로 바꿈(frontend2) — 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[재검증 e7f4a7e] J=다음(10/13), K=이전 — pm 결정대로 바뀜</t>
         </is>
       </c>
     </row>
@@ -4212,10 +4352,22 @@
           <t>요일 머리·날짜가 빨강 + 공휴일 명칭, 주말·공휴일 음영</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 주 보기 10/9 '한글날' 빨강+분홍 배경, 월 보기 12/25 '기독탄신일' 빨강 숫자·칸 음영, 연 보기 숫자 빨강, aria-label에 명칭</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>주말 머리는 회색(빨강 아님)이고 음영만 — 기대 결과와 같음</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4260,18 +4412,18 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>dev:mock 회차에 projectId가 없어 업무를 연결해도 기본 보라색 — 프로젝트 색·필터 확인 불가</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] [재검증] 업무 연결 일정 '코드 리뷰 — PR #42'가 개발 파랑 rgb(45,91,216), 프로젝트 없는 일정은 기본 보라. 개발 끄기 → 숨김, 새로고침 뒤 유지, 프로젝트 없는 일정은 늘 보임, 다시 켜면 표시</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>pm: frontend2가 mock 회차에 projectId를 채움 → 재검증 대상: 다음 fix 묶음 뒤. 실서버 확인은 병합 뒤</t>
+          <t>[최초 BLOCKED] mock 회차 projectId 없음 → 해결. 실서버 확인은 병합 직후 운영 목록</t>
         </is>
       </c>
     </row>
@@ -4316,8 +4468,16 @@
           <t>해당 주로 이동, 미니 달력에 이번 주 강조</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 미니 달력 10/22 → /calendar/week/2026-10-22(19~25일), 미니 달력에 보이는 주 강조, 오늘(6) 표시</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
     </row>
@@ -4474,8 +4634,16 @@
           <t>하루 시간 그리드(주 보기와 같은 조작). '이날의 기록' 패널은 P2라 없음</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 일 보기 머리 1칸, 블록 표시, 18:00부터 끌기 → '새 일정 10월 8일 (목) 18:00–19:45', '이날의 기록' 없음(P2)</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
     </row>
@@ -4522,22 +4690,18 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 할 일 상자를 닫은 상태: 날짜 숫자 → 일 보기, 빈 칸 → '새 일정 … 종일', 칩 10/17→10/24 끌기(시각 유지, 되돌리기 토스트), +n개 팝오버. 결함: 할 일 상자가 열려 있으면 그리드가 1280px에서 252px, 1440px에서 92px 가려져 주말이 안 보이고 스크롤바도 없음</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-07-11.png</t>
-        </is>
-      </c>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] [재검증 e7f4a7e·15ae612·edca07e] 할 일 상자 열림 1280px 그리드 472/472, 1440px 632/632 — 7일 모두 보임(칩 제목 말줄임). 390px: 날짜 칸이 44x64 버튼('10월 15일 목요일, 일정 6개'), 점 3개 + '+3', Enter → 일 보기, 가로 스크롤 없음</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: 다음 fix 묶음 뒤. 관찰: 390px 월 보기는 그리드 안에서 가로 스크롤(358/724px)</t>
+          <t>[최초 FAIL aa4d756] 패널 열림 시 주말 가려짐</t>
         </is>
       </c>
     </row>
@@ -4584,22 +4748,18 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 열 수가 2~6열(패널 닫힘 1280 3열·1600 5열·1920 6열, 패널 열림 1280 2열, 390px 2열). 밀도 점 3단계, 날짜 → 일 보기, 월 이름 → 월 보기는 동작</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-07-12.png</t>
-        </is>
-      </c>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] [재검증 e7f4a7e·15ae612·edca07e] 패널 닫힘 1920·1440px 4열, 1280px 3열, 1024px 2열 / 패널 열림 1920px 4열, 1440·1280px 2열, 1024px 1열 / 390px 1열, 날짜 버튼 42x30</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>화면정의서 4×3·모바일 1열과 다름 — pm 판단 대기</t>
+          <t>[최초 FAIL aa4d756] 열 수 2~6열</t>
         </is>
       </c>
     </row>
@@ -4698,8 +4858,16 @@
           <t>"다가오는 일정이 없어요"</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 일정 0개 → '다가오는 일정이 없어요'</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
     </row>
@@ -4744,10 +4912,26 @@
           <t>모바일 기본 보기는 일 보기, 가로 스크롤 없음. 태블릿은 업무 패널 접힘</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 390px → /calendar/day(일 보기), 800px → 할 일 상자 접힘·아이콘 사이드바 76px·가로 스크롤 없음. 결함: 1024px(데스크톱 최소)에서 할 일 상자가 기본으로 열려 그리드 196px, 요일 머리 겹침, 같은 시간 블록 18px로 겹침, 보기 전환 '목록' 잘림</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-07-15.png</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4790,8 +4974,16 @@
           <t>연도가 바뀌는 주가 끊기지 않고 표시, 1/1 공휴일 표시</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 2026-12-28 – 2027-01-03이 한 주로, 2027-01-01 '신정', J → 2027년 1월 4일 – 10일</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
     </row>
@@ -4849,7 +5041,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>예외 밖 미달: 빠른 입력 '문법 도움말' 32x32 — frontend 배정, 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[재검증 edca07e] '문법 도움말' 보이는 32x32, ::after 44x44, 중심 ±21px 모두 버튼, 옆 N(kbd)은 가로채지 않음 → 해결</t>
         </is>
       </c>
     </row>
@@ -6924,22 +7116,18 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 남은 업무 7(초과 1) → /tasks, 오늘 일정 3(2개 남음) → /calendar/day/2026-10-06, 숫자는 mock 데이터와 일치. 결함: 이번 주 완료 → /tasks?status=DONE에서 '상태를 하나 이상 골라 주세요', 완료 업무는 접힌 영역에만</t>
-        </is>
-      </c>
-      <c r="J118" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>evidence/P1/P1-11-02.png</t>
-        </is>
-      </c>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] [재검증 e7f4a7e·15ae612·edca07e] '이번 주 완료 1' → /tasks?status=DONE&amp;completed=week, 목록 1개('스프린트 계획 공유')</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[최초 FAIL aa4d756] 상태를 하나 이상 골라 주세요</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7394,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>코드 근거(화면 확인 불가): HomeDashboard.tsx 199·341행이 스켈레톤 대신 '불러오는 중…'을 지연 없이 표시. 화면정의서 2장은 스켈레톤 + 0.3초 안에 끝나면 표시 안 함</t>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] [재검증 15ae612] ?mockDelay=2000으로 설정 → 홈 이동: 264ms 0개 → 361ms 스켈레톤 5개(셸 유지) → 2.6초에 사라짐. 200ms 지연에서는 한 번도 안 보임. 결함: 불러오는 동안 카드 보조 문구 '마감 초과 없음'·'일정 없음'이 먼저 보임</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
@@ -7214,10 +7402,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>evidence/P1/P1-11-07.png</t>
+        </is>
+      </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>dev:mock 응답 지연이 300ms 고정이라 느린 응답을 재현할 수 없음</t>
+          <t>[최초 FAIL aa4d756] 스켈레톤 없음 → 해결. 남은 결함: 로딩 중 보조 문구 — 재검증 대상: 다음 fix 묶음 뒤</t>
         </is>
       </c>
     </row>
@@ -7262,10 +7454,22 @@
           <t>배너 "이메일 인증을 마치면 일지를 내보낼 수 있어요" + 인증하기 + 닫기. 닫으면 이번 로그인 동안 숨김, 다시 로그인하면 표시</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 배너 'demo@example.com 인증을 마치면 일지를 내보낼 수 있어요'+인증하기+×, × → 새로고침·다른 화면에서도 숨김, 다시 로그인 → 다시 보임</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>로그아웃 버튼은 SCR-SET-06(P4)이라 mock 세션을 비우고 다시 로그인해서 확인</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7311,7 +7515,11 @@
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7357,7 +7565,11 @@
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7400,10 +7612,22 @@
           <t>모달(모바일 전체 화면), 붙여넣기로 6칸 채움, 다 차면 자동 제출, 성공 시 모달 닫힘 + "이메일 인증을 마쳤어요" 토스트 + 배너 제거</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 인증하기 → 모달, 코드가 없으면 '코드를 새로 받아 주세요'+새 코드 받기 → 09:59 카운트다운·'다시 받기 · 59초', 6자리 한 번에 입력 → 자동 제출 → '이메일 인증을 마쳤어요', 모달 닫힘, 포커스 H1</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>실제 클립보드 붙여넣기·모바일 전체 화면은 계정 인증 뒤 다시 열 수 없어 미확인. 모달 열릴 때·새 코드 받기 뒤 포커스 BODY(포커스 메모)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7446,8 +7670,16 @@
           <t>"코드가 맞지 않아요(남은 시도 n회)" n 감소, 5회째 입력 잠금 + "새 코드 받기"</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] '코드가 맞지 않아요 (남은 시도 4~1회)', aria-invalid=true, 5회째 '이 코드는 더 쓸 수 없어요. 새 코드를 받아 주세요' + 입력 잠금, '새 코드 받기 · n초' 쿨다운</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
     </row>
@@ -7495,7 +7727,11 @@
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7541,7 +7777,11 @@
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7587,7 +7827,11 @@
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06 (있는 테스트: 하루 10통)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7633,7 +7877,11 @@
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7679,7 +7927,11 @@
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7725,7 +7977,11 @@
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06 (있는 테스트: IP당 1시간 10회)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7768,8 +8024,16 @@
           <t>배너 표시 안 됨</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 인증 후 새로고침 → 배너 없음</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
     </row>
@@ -7814,8 +8078,16 @@
           <t>/password/forgot 이동</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 로그인 '비밀번호 찾기' → /password/forgot</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
     </row>
@@ -7860,8 +8132,16 @@
           <t>두 경우 모두 같은 화면·같은 문구("메일을 보냈어요")로 코드 입력 단계 이동. 단 발송 제한 응답 등으로 계정 존재가 드러날 수 있는 점은 D-65에서 허용</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 가입한 이메일(demo)과 없는 이메일(nobody-xyz) 모두 같은 /password/reset 단계와 같은 안내('…으로 보낸 6자리 숫자를 입력하세요')</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
     </row>
@@ -7906,10 +8186,22 @@
           <t>칸 아래 "입력해 주세요" / "이메일 형식이 맞지 않아요"</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 빈 값 → '이메일을 입력해 주세요'(aria-invalid) 정상. 결함: 형식 오류 문구가 '이메일 형식이 올바르지 않아요' — 화면정의서는 '이메일 형식이 맞지 않아요'</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7955,7 +8247,11 @@
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7998,10 +8294,22 @@
           <t>안내에 보낸 주소 표시, 코드가 맞기 전에는 ③~⑥ 비활성, 맞으면 활성</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 코드 확인 전 새 비밀번호·확인·저장이 fieldset으로 비활성, 맞는 코드 → '✓ 확인됐어요' 후 활성, 코드 칸 잠금</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>확인 뒤 포커스 BODY(포커스 메모)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8044,8 +8352,16 @@
           <t>규칙 실시간 표시, '비밀번호 규칙을 확인해 주세요.', '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'(친근한 말투)</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 규칙 실시간 ○/✓, 'abc' 저장 → '비밀번호 규칙을 확인해 주세요', 확인 불일치 → '비밀번호가 일치하지 않아요', 한글 25자+a1(77바이트) → '비밀번호가 너무 길어요. 한글은 한 글자가 더 많은 자리를 차지해요'</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr"/>
     </row>
@@ -8093,7 +8409,11 @@
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8139,7 +8459,11 @@
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8182,8 +8506,16 @@
           <t>남은 시도 n회 감소, 5회 뒤 입력 잠금 + 새 코드 받기</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 남은 시도 4~1회, 5회째 '이 코드는 더 쓸 수 없어요. 새 코드를 받아 주세요'+잠금, 새 코드 받기 쿨다운</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
     </row>
@@ -8231,7 +8563,11 @@
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8274,10 +8610,22 @@
           <t>/password/forgot 이동</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 잠금 안내의 '재설정하세요' → /password/forgot</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>이메일 미리 채움은 없음</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8320,8 +8668,16 @@
           <t>가로 스크롤 없음, 오프라인 띠 + 입력 비활성</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 390px 가로 스크롤 없음, 오프라인 → '연결이 끊겼어요. 다시 연결되면 입력할 수 있어요 / 재시도 중…' + 입력·버튼 비활성, 온라인 복귀 → 띠 사라지고 활성</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
     </row>
@@ -8379,7 +8735,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>점진 지연·429 TOO_MANY_REQUESTS 카운트다운은 실서버에서 확인</t>
+          <t>[병합 직후 운영 확인] 점진 지연·429 TOO_MANY_REQUESTS 카운트다운은 실서버에서 확인</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8793,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>10회 실패로 잠기는지, 잠금 중 맞는 비밀번호 거부는 실서버에서 확인</t>
+          <t>[병합 직후 운영 확인] 10회 실패로 잠기는지, 잠금 중 맞는 비밀번호 거부는 실서버에서 확인</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8849,11 @@
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[병합 직후 운영 확인] </t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8547,7 +8907,11 @@
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
-      <c r="L151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[병합 직후 운영 확인] </t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8601,7 +8965,11 @@
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[병합 직후 운영 확인] </t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8694,10 +9062,22 @@
           <t>더보기에서 업무·통계·설정으로 이동 가능(P0 관찰 사항). 빠른 기록 바텀시트는 P4라 동작 범위 확인</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 390px 하단 탭 홈·캘린더·일지·더보기 78x72, 가운데 +는 52x52. 결함: '더보기'를 눌러도 메뉴가 없음 — 모바일에서 업무·통계·설정으로 갈 길이 없음</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>'+'(빠른 기록)도 캘린더에서 동작 없음 — 바텀시트는 P4라 기록만. 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8740,10 +9120,22 @@
           <t>콘텐츠 영역만 스켈레톤, 사이드바 유지</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] ?mockDelay=2000: 업무 목록·상세·프로젝트·태그 설정으로 이동하면 약 0.4초 뒤 스켈레톤, 사이드바 유지. 홈은 P1-11-07</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>캘린더 4곳은 frontend2 작업 중이라 판정 보류</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8789,7 +9181,11 @@
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8832,10 +9228,22 @@
           <t>띠 표시, 편집·드래그 비활성, 복귀 후 입력 가능</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 업무 상세·설정 일반: 오프라인 → 띠 + 입력·선택·스위치 비활성, 온라인 복귀 → 활성. 결함: 캘린더는 오프라인에서도 일정 끌기가 동작(dev:mock에서는 저장까지 됨)</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K157" s="2" t="inlineStr"/>
-      <c r="L157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8881,7 +9289,11 @@
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -8927,7 +9339,11 @@
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8973,7 +9389,11 @@
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>[병합 직후 운영 확인] 실서버</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9016,10 +9436,22 @@
           <t>콘솔 오류 없음(의도된 401 제외), 정적 리소스 404 없음</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 홈·업무 목록·상세·캘린더 5보기·설정 3개·비밀번호 찾기를 돌며 페이지 오류 0, console error·warn 0, 응답 200/304</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K161" s="2" t="inlineStr"/>
-      <c r="L161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>403 131건은 스냅숏 junction 경로의 Pretendard 글꼴(vite @fs 허용 밖) — 테스트 환경 탓. 정적 리소스 404는 운영에서 다시 확인</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9062,10 +9494,22 @@
           <t>친근한 말투(~해요), 사무적 말투 화면 없음</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] P1 새 화면(홈·업무·캘린더·설정)에 '습니다·십시오' 없음</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>가입·로그인(P0)의 '습니다'체는 화면정의서 문구 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9108,10 +9552,22 @@
           <t>모든 동작 키보드 가능, 포커스 표시 키 컬러, 터치 영역 44px 이상</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 키보드만으로 조작 가능(이번 실행 전체). 결함(390px 44px 미달): 묶음 전환 높이 36, 업무 완료 원 ::after 42, 행 제목 높이 41, 상세 select·날짜 40, '태그 추가' 32, 슬라이더 32, '캘린더에 배치' 83x20, '‹ 설정' 40x44</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>포커스 유실은 메모로 따로 보냄. 재검증 대상: 다음 fix 묶음 뒤</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L163"/>
@@ -9555,7 +10011,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1-09·10, P1-01, P1-02, P1-03·04, P1-06·07·08, P1-11, P1-14, 재검증)</t>
+          <t>2026-10-06 (P1 전 영역 dev:mock, 재검증 3차)</t>
         </is>
       </c>
     </row>
@@ -9603,7 +10059,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>미실행 57, PASS 80, BLOCKED 20, FAIL 4, N/A 1</t>
+          <t>미실행 22, PASS 110, BLOCKED 19, FAIL 10, N/A 1</t>
         </is>
       </c>
     </row>
@@ -9615,7 +10071,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>미해결: P1-07-11 할 일 상자 열림 시 월 그리드 가려짐, P1-07-12 연 보기 열 수(문서와 다름, pm 판단 대기), P1-11-02 이번 주 완료 링크, P1-11-07 로딩 스켈레톤 없음, 빠른 입력 ? 버튼 32px(P1-07-17 비고), 패널 슬라이더 Esc(P1-03-13 비고), J/K 방향(P1-07-03 비고). 해결: P1-03-01·04·05·07·08·09·13, P1-04-04, P1-02-11, P1-09-01·08, P1-01-11, P1-10-06, P1-02-09·10</t>
+          <t>미해결: P1-05-03 시간 오류 aria, P1-05-05 새로 불러오기 뒤 모달 옛 값, P1-05-06 연결 업무 칸·연결 일정 목록, P1-06-02 매주 요일 남음, P1-07-15 1024px 그리드 196px, P1-11-07 로딩 중 보조 문구, P1-13-03 문구, P1-X-01 더보기, P1-X-04 캘린더 오프라인 끌기, P1-X-10 390px 44px 미달. 해결: P1-07-06·11·12, P1-11-02, P1-07-03(J/K), P1-07-17 ? 버튼, P1-03-13 슬라이더 Esc, P1-03-01·04·05·07·08·09, P1-04-04, P1-02-11 외</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -3454,18 +3454,18 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 종료&lt;시작 저장 → 종료 아래 '끝나는 시각을 시작보다 뒤로 골라 주세요', 저장 안 됨. 결함: 종료 input에 aria-invalid·aria-describedby 없고 포커스가 × 버튼으로 감</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 종료&lt;시작 → 종료 칸 aria-invalid=true, aria-describedby → '끝나는 시각을 시작보다 뒤로 골라 주세요', 포커스 종료 칸, 저장 안 됨</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>서버 errors[]는 클라이언트가 먼저 막아 확인 불가. 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e] 서버 errors[]는 클라이언트가 먼저 막아 확인 불가</t>
         </is>
       </c>
     </row>
@@ -3570,18 +3570,18 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 두 탭: A 제목 저장 → B 메모 저장 → 모달 위 충돌 띠 '다른 곳에서 먼저 수정됐어요…'+[새로 불러오기](정상). 결함: 새로 불러오기 뒤 모달 제목이 옛 값(그리드는 최신)</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 두 탭 충돌 → [새로 불러오기] → 모달 제목이 A의 '고객사 미팅 A수정'(최신), 띠 사라짐</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>바뀐 칸만 보내서 A 값이 덮어써지지는 않음. 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e] 바뀐 칸만 보내서 A 값이 덮어써지지는 않음</t>
         </is>
       </c>
     </row>
@@ -3628,18 +3628,18 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 일정 모달에 '연결 업무'(검색·새 업무·해제) 칸 없음, 업무 상세 '연결된 일정'은 목록 없이 '캘린더에 배치된 일정이 있어요' 문구만</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 일정 모달 '연결 업무' 콤보박스: '결제' 검색 → ↓·Enter로 연결, 저장하면 taskId·개발 파랑, 해제 → 연결 없음, 새 업무 'QA 새 연결 업무' 만들고 연결. 반복 일정은 '반복 일정은 모든 회차에 연결돼요' 안내 + 시리즈 전체. 업무 상세 '연결된 일정': 다가오는 5개(10/7~10/13, '반복'), '일정 58개 더 · 캘린더에서 보기' → /calendar/list, [캘린더에 배치] → 업무 제목·연결 업무가 채워진 새 일정 창</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>pm 결정: P1 범위, 구현(모달 frontend2, 업무 상세 frontend) — 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e] pm 결정: P1 범위, 구현(모달 frontend2, 업무 상세 frontend) / 관찰: 해제 뒤 포커스가 닫기 버튼으로 감</t>
         </is>
       </c>
     </row>
@@ -3840,18 +3840,18 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 주 보기 10/12 주에서 일정 만들기(기본 10/12 월) → 날짜 10/13(화) → 매주 → 요일 기본값이 월·화 둘 다 → 목 추가해 저장하면 MONDAY·TUESDAY·THURSDAY, 10/19·26(월) 회차 생김</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 매주 → 기본 요일이 시작일(화)만, 날짜를 10/15로 바꾸면 목만</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>고르지 않은 처음 날짜의 요일이 남음 — 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e] 고르지 않은 처음 날짜의 요일이 남음</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>D-71: 제목만 바꾸면 회차 변경 유지. 저장 뒤 포커스는 H1(같은 블록 아님)</t>
+          <t>D-71: 제목만 바꾸면 회차 변경 유지. [재검증 15ec39b] 저장 뒤 포커스가 수정한 블록으로 감(해결)</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>범위 대화상자 확인 뒤 포커스 BODY(범위 대화상자 뒤 포커스 비고 — frontend2 작업 중, 판정 보류)</t>
+          <t>범위 대화상자 확인 뒤 포커스 BODY — P1-07-18 결함으로 기록</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 390px → /calendar/day(일 보기), 800px → 할 일 상자 접힘·아이콘 사이드바 76px·가로 스크롤 없음. 결함: 1024px(데스크톱 최소)에서 할 일 상자가 기본으로 열려 그리드 196px, 요일 머리 겹침, 같은 시간 블록 18px로 겹침, 보기 전환 '목록' 잘림</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 1024px: 할 일 상자 기본 접힘(그리드 472px, 보기 전환 5개 보임), P → 패널이 그리드 위에 떠서 그리드 폭 유지. 1280px은 기본 열림. 390px → 일 보기, 800px → 접힘</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e]  / 관찰: 떠 있는 패널은 Esc로 안 닫힘(P로 닫힘)</t>
         </is>
       </c>
     </row>
@@ -5088,18 +5088,18 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 상세 모달 Esc → 연 블록, 시간 저장 → 옮겨진 같은 블록, 삭제 → 캘린더 제목, '+4개 더보기' 팝오버 Esc → 그 버튼, 일정 만들기·C 팝오버 Esc → '일정 만들기'</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 상세 모달 Esc → 연 블록, 시간 저장 → 옮겨진 같은 블록, 삭제 → 캘린더 제목, '+4개 더보기' 팝오버 Esc → 그 버튼, 일정 만들기·C 팝오버 Esc → '일정 만들기' / [로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 반복 회차 제목을 범위 대화상자 '이 일정만'으로 저장 → 수정한 블록으로 포커스(해결). 결함: 반복 일정을 범위 대화상자로 삭제(이 일정만·모든 일정) → 포커스 BODY</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>반복 회차를 범위 대화상자로 저장하면 H1로 감(같은 블록 아님)</t>
+          <t>재검증 대상: 다음 fix 묶음 뒤</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] [재검증 15ae612] ?mockDelay=2000으로 설정 → 홈 이동: 264ms 0개 → 361ms 스켈레톤 5개(셸 유지) → 2.6초에 사라짐. 200ms 지연에서는 한 번도 안 보임. 결함: 불러오는 동안 카드 보조 문구 '마감 초과 없음'·'일정 없음'이 먼저 보임</t>
-        </is>
-      </c>
-      <c r="J123" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] ?mockDelay=2000: 홈 카드 숫자·보조 문구 모두 스켈레톤(불러오는 중) → 2.8초 뒤 값. 200ms면 안 보임(이전 실행)</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>[최초 FAIL aa4d756] 스켈레톤 없음 → 해결. 남은 결함: 로딩 중 보조 문구 — 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e] [최초 FAIL aa4d756] 스켈레톤 없음 → 해결. 남은 결함: 로딩 중 보조 문구</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7724,20 @@
           <t>남은 시간 카운트다운 0 → 입력 잠금 + 새 코드 받기, 만료 코드 제출 시 거부</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] identity-service VerificationFlowTest.인증_코드는_10분이_지나면_만료된다 — GitHub Actions PR #2 CI run 37428788043(HEAD 15ec39b) backend success, 이전 run 37427409574(35ebff6)도 success</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06</t>
+          <t>pm 결정 2026-10-06: 시간·발송 한도 항목은 통합 테스트 결과로 갈음. CI 결과는 pm이 gh로 확인, qa도 gh run view로 재확인</t>
         </is>
       </c>
     </row>
@@ -7824,12 +7832,20 @@
           <t>"내일 다시 시도" 안내·서버 거부. 한도는 보낸 시각부터 24시간(rolling, 자정에 한꺼번에 풀리지 않음), 가입 자동 발송도 한도에 포함</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] identity-service VerificationFlowTest.하루_10통을_넘으면_DAILY_SEND_LIMIT — GitHub Actions PR #2 CI run 37428788043(HEAD 15ec39b) backend success, 이전 run 37427409574(35ebff6)도 success</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06 (있는 테스트: 하루 10통)</t>
+          <t>pm 결정 2026-10-06: 시간·발송 한도 항목은 통합 테스트 결과로 갈음. CI 결과는 pm이 gh로 확인, qa도 gh run view로 재확인</t>
         </is>
       </c>
     </row>
@@ -7974,12 +7990,20 @@
           <t>11번째 거부(두 종류 합산, IP당 1시간 10통). 헤더가 없으면 IP 제한은 건너뜀(D-65)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] identity-service VerificationFlowTest.한_IP에서_코드_메일_요청은_1시간에_10회까지 — GitHub Actions PR #2 CI run 37428788043(HEAD 15ec39b) backend success, 이전 run 37427409574(35ebff6)도 success</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06 (있는 테스트: IP당 1시간 10회)</t>
+          <t>pm 결정 2026-10-06: 시간·발송 한도 항목은 통합 테스트 결과로 갈음. CI 결과는 pm이 gh로 확인, qa도 gh run view로 재확인</t>
         </is>
       </c>
     </row>
@@ -8188,18 +8212,18 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 빈 값 → '이메일을 입력해 주세요'(aria-invalid) 정상. 결함: 형식 오류 문구가 '이메일 형식이 올바르지 않아요' — 화면정의서는 '이메일 형식이 맞지 않아요'</t>
-        </is>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 형식 오류 '이메일 형식이 맞지 않아요', 빈 값 '이메일을 입력해 주세요'</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+          <t xml:space="preserve">[이전 FAIL e7f4a7e] </t>
         </is>
       </c>
     </row>
@@ -8456,12 +8480,20 @@
           <t>잠금이 풀려 바로 로그인 성공</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] identity-service VerificationFlowTest.로그인이_잠긴_동안_비밀번호를_재설정하면_잠금이_풀린다 — GitHub Actions PR #2 CI run 37428788043(HEAD 15ec39b) backend success, 이전 run 37427409574(35ebff6)도 success</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06</t>
+          <t>pm 결정 2026-10-06: 시간·발송 한도 항목은 통합 테스트 결과로 갈음. CI 결과는 pm이 gh로 확인, qa도 gh run view로 재확인</t>
         </is>
       </c>
     </row>
@@ -8560,12 +8592,20 @@
           <t>재발송 60초 제한, 초과 시 "내일 다시 시도해 주세요"</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>[통합 테스트로 확인] identity-service VerificationFlowTest.재설정_코드_재요청은_60초_안이면_거부하고_하루_10통까지 — GitHub Actions PR #2 CI run 37428788043(HEAD 15ec39b) backend success, 이전 run 37427409574(35ebff6)도 success</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>[통합 테스트로 확인] 테스트 이름은 backend1 추가 후 기록 — pm 결정 2026-10-06</t>
+          <t>pm 결정 2026-10-06: 시간·발송 한도 항목은 통합 테스트 결과로 갈음. CI 결과는 pm이 gh로 확인, qa도 gh run view로 재확인</t>
         </is>
       </c>
     </row>
@@ -9064,18 +9104,18 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 390px 하단 탭 홈·캘린더·일지·더보기 78x72, 가운데 +는 52x52. 결함: '더보기'를 눌러도 메뉴가 없음 — 모바일에서 업무·통계·설정으로 갈 길이 없음</t>
-        </is>
-      </c>
-      <c r="J154" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 더보기(aria-expanded·controls) → 메뉴 업무→/tasks·설정→/settings(44px), Enter로 열면 첫 항목 포커스, Esc → 더보기로 포커스. '+' → 홈 빠른 입력칸 포커스</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>'+'(빠른 기록)도 캘린더에서 동작 없음 — 바텀시트는 P4라 기록만. 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e] '+'(빠른 기록)도 캘린더에서 동작 없음 — 바텀시트는 P4라 기록만</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9173,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>캘린더 4곳은 frontend2 작업 중이라 판정 보류</t>
+          <t>[재검증 15ec39b] 캘린더 스켈레톤도 PASS: 처음 열면 월·연·목록·일 보기 셸 뒤 스켈레톤, 주 보기 전환 0.4초 뒤. 보기 전환 때는 이전 내용 유지(공용 규칙)</t>
         </is>
       </c>
     </row>
@@ -9230,18 +9270,18 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 업무 상세·설정 일반: 오프라인 → 띠 + 입력·선택·스위치 비활성, 온라인 복귀 → 활성. 결함: 캘린더는 오프라인에서도 일정 끌기가 동작(dev:mock에서는 저장까지 됨)</t>
-        </is>
-      </c>
-      <c r="J157" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 오프라인: 업무 상세·설정 입력 비활성(이전 실행), 캘린더 블록 끌기·빈 칸 끌기·'일정 만들기'(disabled)·C 키 모두 막힘, 블록·칸 touch-action none→auto로 스크롤 가능</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+          <t xml:space="preserve">[이전 FAIL e7f4a7e] </t>
         </is>
       </c>
     </row>
@@ -9554,7 +9594,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] 키보드만으로 조작 가능(이번 실행 전체). 결함(390px 44px 미달): 묶음 전환 높이 36, 업무 완료 원 ::after 42, 행 제목 높이 41, 상세 select·날짜 40, '태그 추가' 32, 슬라이더 32, '캘린더에 배치' 83x20, '‹ 설정' 40x44</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 이전 목록(묶음 전환·완료 원·행 제목·상세 select·날짜·태그 추가·슬라이더·'캘린더에 배치'·'‹ 설정') 모두 44px 이상. 남은 결함: 미인증 배너 '인증하기' 92x40</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
@@ -9565,7 +9605,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>포커스 유실은 메모로 따로 보냄. 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL e7f4a7e] 8개 미달. 재검증 대상: 다음 fix 묶음 뒤</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10051,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1 전 영역 dev:mock, 재검증 3차)</t>
+          <t>2026-10-06 (P1 최종 재검증, 15ec39b)</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10099,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>미실행 22, PASS 110, BLOCKED 19, FAIL 10, N/A 1</t>
+          <t>미실행 17, PASS 123, BLOCKED 19, FAIL 2, N/A 1</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10111,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>미해결: P1-05-03 시간 오류 aria, P1-05-05 새로 불러오기 뒤 모달 옛 값, P1-05-06 연결 업무 칸·연결 일정 목록, P1-06-02 매주 요일 남음, P1-07-15 1024px 그리드 196px, P1-11-07 로딩 중 보조 문구, P1-13-03 문구, P1-X-01 더보기, P1-X-04 캘린더 오프라인 끌기, P1-X-10 390px 44px 미달. 해결: P1-07-06·11·12, P1-11-02, P1-07-03(J/K), P1-07-17 ? 버튼, P1-03-13 슬라이더 Esc, P1-03-01·04·05·07·08·09, P1-04-04, P1-02-11 외</t>
+          <t>미해결: P1-07-18 반복 일정 범위 대화상자 삭제 뒤 포커스 BODY, P1-X-10 미인증 배너 '인증하기' 40px. 해결(15ec39b): P1-05-03·05·06, P1-06-02, P1-07-15, P1-11-07, P1-13-03, P1-X-01·04, 인증·재설정 포커스, 캘린더 스켈레톤, 390px 할 일 상자</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -58,12 +58,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D3CE"/>
+        <fgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00F8D3CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -598,12 +598,20 @@
           <t>업무 생성(되돌리기 토스트), 패널에서 1시간 일정(14:00~15:00) 생성·업무 연결, 패널 목록에서 빠짐</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 빠른 입력 '견적서 작성 @영업 !높음 ~내일' → 없는 프로젝트 안내와 '새 프로젝트 만들기' 칩 → 만든 뒤 Enter로 업무 생성(되돌리기 토스트). 캘린더 할 일 상자에서 오늘 14:00 칸으로 끌기 → 14:00–15:00 일정, 업무 연결, 패널에서 빠짐</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인]</t>
         </is>
       </c>
     </row>
@@ -648,12 +656,20 @@
           <t>다섯 보기 모두 같은 회차(날짜·시간)가 표시되고 7번째 회차는 없음</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 매주 월·수, 종료 횟수 6회(10/12~10/28) → 목록·월·주·일·연 보기 모두 같은 6회, 7번째(11/2) 없음</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인]</t>
         </is>
       </c>
     </row>
@@ -698,12 +714,20 @@
           <t>메일 수신, 인증 완료, 미인증 배너 사라짐</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 가입 인증 메일 → 다시 받기로 받은 새 코드 입력 → '이메일 인증을 마쳤어요', 미인증 배너 사라짐(새로고침 뒤에도), emailVerified=true</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인] 실제 메일(사용자 승인)</t>
         </is>
       </c>
     </row>
@@ -748,12 +772,20 @@
           <t>메일 수신, 재설정 후 로그인 화면 이동, 새 비밀번호로 로그인 성공</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 비밀번호 찾기 → 재설정 메일 코드 → '✓ 확인됐어요' → 새 비밀번호 저장 → 로그인 화면 + '비밀번호를 바꿨어요. 새 비밀번호로 로그인해 주세요', 옛 비밀번호 실패, 새 비밀번호 로그인 성공</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인] 실제 메일(사용자 승인)</t>
         </is>
       </c>
     </row>
@@ -1986,18 +2018,18 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 f32d598 스냅숏, 2026-10-06] [재검증 29a1e96] 다른 브라우저 탭으로 전환 → 토스트가 떠 있는 동안에도 삭제 확정(PASS). 새로고침·탭 닫기는 dev:mock에서 확인 불가: mock 응답이 300ms 지연 뒤 localStorage에 쓰므로 페이지가 먼저 사라져 기록되지 않음(코드는 DELETE를 keepalive로 보냄)</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 태그 삭제 직후(서버에는 아직 남아 있음, 지연 삭제) 새로고침 → 확정, 앱 안 다른 화면 이동 → 확정, 브라우저 닫기 → 확정</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 새로고침·탭 닫기 확정은 실서버(운영 배포 뒤 또는 로컬 백엔드)에서 재확인 필요. 최초 FAIL 2026-10-06</t>
+          <t>[병합 직후 운영 확인]  / 이전: 새로고침·탭 닫기 확정은 실서버(운영 배포 뒤 또는 로컬 백엔드)에서 재확인 필요. 최초 FAIL 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2539,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>[최초 FAIL 2026-10-06 21c8f0e] 완료 후 포커스 BODY</t>
+          <t>[최초 FAIL 2026-10-06 21c8f0e] 완료 후 포커스 BODY / [c6215b3] 프로젝트 없는 업무 완료 원도 키 컬러로 채우고 흰 ✓</t>
         </is>
       </c>
     </row>
@@ -2894,18 +2926,18 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>dev:mock에서는 확인할 수 없음(실서버 계정 A·B로 API를 직접 호출해야 함)</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 계정 B가 A의 업무 id로 GET·PATCH·DELETE → 모두 404, A의 업무는 그대로</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] pm: 병합 후 운영 확인 때</t>
+          <t>[병합 직후 운영 확인]  / 이전: pm: 병합 후 운영 확인 때</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3671,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>[이전 FAIL e7f4a7e] pm 결정: P1 범위, 구현(모달 frontend2, 업무 상세 frontend) / 관찰: 해제 뒤 포커스가 닫기 버튼으로 감</t>
+          <t>[이전 FAIL e7f4a7e] pm 결정: P1 범위, 구현(모달 frontend2, 업무 상세 frontend) / [1b78018] 해제 뒤 포커스가 연결 업무 콤보박스로 감(해결)</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3716,20 @@
           <t>404(또는 403)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 계정 B가 A의 일정 id로 GET·PATCH·DELETE → 모두 404, B로 A 업무의 회차 조회(taskId 조건) → 빈 목록</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인]</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3774,20 @@
           <t>일정은 만든 시간대 기준으로 고정되어 표시 시각만 바뀜, 서머타임 전환 주에도 시각이 어긋나지 않음</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 매주 월 09:00(Asia/Seoul) 3회를 만든 뒤 시간대를 America/New_York으로 → 10/26 회차는 10/25 20:00(EDT), 11/2 회차는 11/1 19:00(EST, 서머타임 종료 반영). 저장 시각은 그대로, 표시만 바뀜, 시간대 변경 안내 문구 표시</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인]</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4460,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 e7f4a7e 스냅숏, 2026-10-06] [재검증] 업무 연결 일정 '코드 리뷰 — PR #42'가 개발 파랑 rgb(45,91,216), 프로젝트 없는 일정은 기본 보라. 개발 끄기 → 숨김, 새로고침 뒤 유지, 프로젝트 없는 일정은 늘 보임, 다시 켜면 표시</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 회차 응답에 projectId·taskId가 들어 있고, 업무를 연결한 일정 블록이 프로젝트 색(P1)으로 표시</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -4423,7 +4471,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>[최초 BLOCKED] mock 회차 projectId 없음 → 해결. 실서버 확인은 병합 직후 운영 목록</t>
+          <t>[병합 직후 운영 확인] dev:mock 확인(15ec39b)에 이어 운영 확인 / [최초 BLOCKED] mock 회차 projectId 없음 → 해결. 실서버 확인은 병합 직후 운영 목록</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4749,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>[최초 FAIL aa4d756] 패널 열림 시 주말 가려짐</t>
+          <t>[최초 FAIL aa4d756] 패널 열림 시 주말 가려짐 / [c6215b3] 칸 안쪽 폭 120px 미만이면 칩은 제목만(1440px 패널 열림: 칸 83px), 이상이면 시각+제목(1920px)</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4977,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>[이전 FAIL e7f4a7e]  / 관찰: 떠 있는 패널은 Esc로 안 닫힘(P로 닫힘)</t>
+          <t>[이전 FAIL e7f4a7e]  / [1b78018] 떠 있는 패널 Esc로 닫힘·포커스 캘린더 제목(해결) / [c6215b3] 390px 상단 바 ‹·›가 한 묶음으로 한 줄</t>
         </is>
       </c>
     </row>
@@ -5088,18 +5136,18 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 상세 모달 Esc → 연 블록, 시간 저장 → 옮겨진 같은 블록, 삭제 → 캘린더 제목, '+4개 더보기' 팝오버 Esc → 그 버튼, 일정 만들기·C 팝오버 Esc → '일정 만들기' / [로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 반복 회차 제목을 범위 대화상자 '이 일정만'으로 저장 → 수정한 블록으로 포커스(해결). 결함: 반복 일정을 범위 대화상자로 삭제(이 일정만·모든 일정) → 포커스 BODY</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 상세 모달 Esc → 연 블록, 시간 저장 → 옮겨진 같은 블록, 삭제 → 캘린더 제목, '+4개 더보기' 팝오버 Esc → 그 버튼, 일정 만들기·C 팝오버 Esc → '일정 만들기' / [로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 반복 회차 제목을 범위 대화상자 '이 일정만'으로 저장 → 수정한 블록으로 포커스(해결). 결함: 반복 일정을 범위 대화상자로 삭제(이 일정만·모든 일정) → 포커스 BODY / [로컬 dev:mock, feature/P1 1b78018 스냅숏, 2026-10-06] [재검증] 반복 일정 범위 대화상자 삭제(이 일정만·모든 일정) → 캘린더 제목(H1)으로 포커스, 되돌리기 복원 정상</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL 15ec39b] 반복 일정 삭제 뒤 포커스 BODY → 해결(68193be)</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5689,11 @@
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>[c6215b3] 할 일 상자 빠른 입력 안내 '+ 업무 추가'</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5689,7 +5741,7 @@
           <t>홈 오늘 일정 영역(③)은 P2라 대상 없음</t>
         </is>
       </c>
-      <c r="J93" s="6" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7512,12 +7564,20 @@
           <t>제목 '[worklog] 이메일 인증번호 안내'에 코드 없음, 본문 6자리 큰 글씨·10분·무시 안내·바닥글, 텍스트 버전 있음</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 가입 인증 메일: 제목 '[worklog] 이메일 인증번호 안내'(코드 없음), 본문 큰 6자리·10분 안내·무시 안내·바닥글, text/plain·text/html 둘 다</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인] 메일 내용은 사용자가 확인</t>
         </is>
       </c>
     </row>
@@ -7562,12 +7622,20 @@
           <t>Gmail SMTP 발신(보내는 주소는 Gmail 계정 주소, @wy-worklog.com 아님, D-57), 받은편지함 도착</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 보낸 주소는 Gmail 계정 주소(@wy-worklog.com 아님, D-57), 4통 모두 받은편지함 도착</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인] 메일 내용은 사용자가 확인</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7749,11 @@
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>[c6215b3·efcb8c9] 발송 한도 문구 '코드는 24시간에 10통까지 받을 수 있어요. HH:MM 이후에 다시 받을 수 있어요' — mock에 한도 응답이 없어 화면 미확인, vitest verification.test.tsx 15/15 PASS</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7782,12 +7854,20 @@
           <t>60초 쿨다운 표시, 60초 전 재요청 불가(서버도 거부)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 다시 받기 직후 버튼 비활성, 바로 다시 요청하면 서버도 429 RESEND_TOO_SOON으로 거부(메일 안 나감). 결함: 카운트다운이 '다시 받기 · 69초', '남은 시간 10:09'처럼 한도(60초·10:00)를 넘게 표시됨 — PC 시계가 서버보다 약 10초 늦어 서버 시각 기준 계산이 늘어남(재설정 화면도 같음)</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인] pm 판단: 결함(작음), 표시를 한도로 잘라야 함 — frontend 배정</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7970,20 @@
           <t>새 코드를 발급하면 이전 코드는 무효(이전 코드 제출 시 틀린 코드로 처리)</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 새 코드를 받은 뒤 먼저 받은 코드를 넣으면 '코드가 맞지 않아요(남은 시도 4회)'</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인]</t>
         </is>
       </c>
     </row>
@@ -7940,12 +8028,20 @@
           <t>거부(코드는 계정별), 비로그인 401</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 계정 A의 코드를 B 세션에서 제출 → 400 거부(B는 미인증 유지), 비로그인으로 인증 확인 API → 401 UNAUTHENTICATED</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인] B의 거부 사유는 B 자기 코드 만료(CODE_EXPIRED). 코드는 계정별로 확인됨</t>
         </is>
       </c>
     </row>
@@ -8268,12 +8364,20 @@
           <t>제목 '[worklog] 비밀번호 재설정 안내'(코드 없음, 인증 메일과 제목으로 구분), 6자리, 10분, '비밀번호는 바뀌지 않아요' 안내</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 재설정 메일: 제목 '[worklog] 비밀번호 재설정 안내'(코드 없음), 6자리·10분 안내, '비밀번호는 바뀌지 않아요' 안내</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인] 메일 내용은 사용자가 확인</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8534,20 @@
           <t>로그인 화면 이동 + 토스트, 다른 기기 세션 폐기(refresh 401 → 로그인 화면), 옛 비밀번호 실패, 새 비밀번호 성공, 이메일 인증 완료 상태(배너 없음), 로그인 실패 횟수·잠금도 해제(D-64)</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 미인증 계정을 두 브라우저에서 로그인해 두고 한쪽에서 재설정 저장 → 로그인 화면 + 토스트, 옛 비밀번호 401·새 비밀번호 200, 이메일 인증 완료(false → true). 다른 브라우저는 access 만료 뒤 me 401 → refresh 401 → 로그인 화면(세션 폐기)</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버 (실제 메일 발송은 사용자 승인 뒤)</t>
+          <t>[병합 직후 운영 확인] access는 만료(10분)까지 유효한 설계라 폐기 확인은 만료 뒤</t>
         </is>
       </c>
     </row>
@@ -8764,18 +8876,18 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] 틀린 비밀번호 3회 → '이메일 또는 비밀번호가 맞지 않아요'만 표시. mock은 응답 지연이 없어 '잠시 후 다시 시도해 주세요' 줄(900ms 이상 늦은 응답일 때)이 안 뜨는 게 맞음</t>
-        </is>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 틀린 비밀번호 연속: 0.34·0.36초 → 3회째부터 1.3·2.4·4.3초…(상한 약 8.5초), UI '이메일 또는 비밀번호가 맞지 않아요 / 잠시 후 다시 시도해 주세요'. IP 분당 10회 초과 → 429 TOO_MANY_REQUESTS + Retry-After, UI '잠시 후 다시 시도해 주세요' + '로그인 · 0:01 후 가능'(aria-disabled) → 풀리면 다시 활성</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 점진 지연·429 TOO_MANY_REQUESTS 카운트다운은 실서버에서 확인</t>
+          <t>[병합 직후 운영 확인]  / 이전: 점진 지연·429 TOO_MANY_REQUESTS 카운트다운은 실서버에서 확인</t>
         </is>
       </c>
     </row>
@@ -8822,18 +8934,18 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 aa4d756 스냅숏, 2026-10-06] (UI만) locked@example.com → '15분 동안 로그인할 수 없어요. 비밀번호를 10번 잘못 입력했어요… 재설정하세요'(링크), 버튼 '로그인 · 14:51 후 가능' disabled, 초 단위로 줄어듦</t>
-        </is>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 10회째 429 AUTH_LOCKED(900초), 잠금 중 맞는 비밀번호도 거부, UI '15분 동안 로그인할 수 없어요. / 비밀번호를 10번 잘못 입력했어요. 비밀번호가 기억나지 않으면 재설정하세요'(링크 /password/forgot), 버튼 '로그인 · 14:46 후 가능'(aria-disabled, 눌러도 요청 안 나감)</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 10회 실패로 잠기는지, 잠금 중 맞는 비밀번호 거부는 실서버에서 확인</t>
+          <t>[병합 직후 운영 확인]  / 이전: 10회 실패로 잠기는지, 잠금 중 맞는 비밀번호 거부는 실서버에서 확인</t>
         </is>
       </c>
     </row>
@@ -8880,18 +8992,18 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>dev:mock에서는 확인할 수 없음(실서버 필요)</t>
-        </is>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 잠금 15분 뒤 맞는 비밀번호로 로그인 200, 이후 틀린 비밀번호는 1·2회 지연 없이, 3회째부터 다시 지연(실패 횟수 초기화)</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[병합 직후 운영 확인] </t>
+          <t>[병합 직후 운영 확인] 시트 환경은 로컬이었으나 운영에서 15분 기다려 확인</t>
         </is>
       </c>
     </row>
@@ -8938,18 +9050,18 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>dev:mock에서는 확인할 수 없음(실서버 필요)</t>
-        </is>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 없는 이메일로 연속 실패 → 11회째 IP 429 TOO_MANY_REQUESTS(Retry-After)</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[병합 직후 운영 확인] </t>
+          <t>[병합 직후 운영 확인] 관찰: 없는 이메일은 점진 지연이 없어 응답 시간으로 계정 존재를 짐작할 수 있음 — D-61(계정 존재 노출 허용) 범위로 기록</t>
         </is>
       </c>
     </row>
@@ -8996,18 +9108,18 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>dev:mock에서는 확인할 수 없음(실서버 필요)</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] IP 제한에 걸린 상태에서 X-Client-Ip·X-Forwarded-For를 위조해도 429(위조 헤더 무시)</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[병합 직후 운영 확인] </t>
+          <t>[병합 직후 운영 확인] pm 결정: IP 제한 동작은 통합 테스트 LoginProtectionTest.한_IP에서_분당_10번_실패하면_없는_이메일이어도_429로 갈음</t>
         </is>
       </c>
     </row>
@@ -9218,12 +9330,20 @@
           <t>로그인 화면으로 이동 + "다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.", 로그인 후 원래 화면 복귀</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 로그인 중 쿠키 삭제 → 사이드바 이동 → 로그인 화면으로 이동하고 다시 로그인하면 원래 화면(/calendar/week)으로 복귀(정상). 결함: '다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.' 안내가 뜨지 않음(로그인 화면 state에 reason 없음)</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인] 추정: 동시 401에서 handleSessionExpired 두 번째 호출이 세션 종료 이유를 지움 — frontend</t>
         </is>
       </c>
     </row>
@@ -9326,12 +9446,20 @@
           <t>모두 403 ORIGIN_REJECTED</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 다른 Origin으로 POST tasks·schedules·tags·projects, PATCH users/me·worklog/me/settings, POST email-verification/confirm·password-reset/verify, DELETE task → 모두 403 ORIGIN_REJECTED, 데이터 그대로</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인]</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9504,20 @@
           <t>cursor 기반 다음 페이지, 오류는 Problem Details + traceId</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 업무 목록 limit=2 → nextCursor로 다음 쪽(마지막 쪽 null), 오류 응답은 application/problem+json·code·errors[field]·traceId·X-Trace-Id</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인]</t>
         </is>
       </c>
     </row>
@@ -9426,12 +9562,20 @@
           <t>P0 시트 '도메인 전환 재검증'과 같은 결과</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 배포: Vercel Production·Railway 모두 3d1159e success, gateway·identity·worklog 응답, 새 빌드 기능(회차 taskId 조건) 동작. www·http → apex 308(경로·쿼리 유지), www에서 시작한 가입 201 → 홈, 로그인 200, me 200, 쿠키 HttpOnly·Secure·SameSite=Strict(access Path=/api 600초, refresh Path=/api/auth 14일), 다른 Origin(evil·www·http·없음) 403, API x-vercel-cache MISS·X-Trace-Id, 새로고침·새 탭 유지, 390px 가로 스크롤 없음, 토큰 자동 갱신(me 401 → refresh 204 → me 200)</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 실서버</t>
+          <t>[병합 직후 운영 확인] 참고: 옛 project-7qtt1.vercel.app Origin은 아직 허용(전환 기간 설정)</t>
         </is>
       </c>
     </row>
@@ -9594,18 +9738,18 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 이전 목록(묶음 전환·완료 원·행 제목·상세 select·날짜·태그 추가·슬라이더·'캘린더에 배치'·'‹ 설정') 모두 44px 이상. 남은 결함: 미인증 배너 '인증하기' 92x40</t>
-        </is>
-      </c>
-      <c r="J163" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[로컬 dev:mock, feature/P1 15ec39b 스냅숏, 2026-10-06] [재검증] 이전 목록(묶음 전환·완료 원·행 제목·상세 select·날짜·태그 추가·슬라이더·'캘린더에 배치'·'‹ 설정') 모두 44px 이상. 남은 결함: 미인증 배너 '인증하기' 92x40 / [로컬 dev:mock, feature/P1 1b78018 스냅숏, 2026-10-06] [재검증] 미인증 배너 [인증하기] 홈·업무·설정 92x44, 중심 ±21px 모두 버튼</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>[이전 FAIL e7f4a7e] 8개 미달. 재검증 대상: 다음 fix 묶음 뒤</t>
+          <t>[이전 FAIL 15ec39b] 배너 [인증하기] 92x40 → 해결(e0a1c25) / [c6215b3] 업무 목록 완료 원 1440·390px 모두 버튼 44x44(보이는 원 22px), 390px 주 보기 ‹·› ::after 44x44</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10195,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1 최종 재검증, 15ec39b)</t>
+          <t>2026-10-06 (P1 dev:mock 전체 + 병합 직후 운영 확인, main 3d1159e)</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10243,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>미실행 17, PASS 123, BLOCKED 19, FAIL 2, N/A 1</t>
+          <t>PASS 147, BLOCKED 12, N/A 1, FAIL 2</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10255,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>미해결: P1-07-18 반복 일정 범위 대화상자 삭제 뒤 포커스 BODY, P1-X-10 미인증 배너 '인증하기' 40px. 해결(15ec39b): P1-05-03·05·06, P1-06-02, P1-07-15, P1-11-07, P1-13-03, P1-X-01·04, 인증·재설정 포커스, 캘린더 스켈레톤, 390px 할 일 상자</t>
+          <t>운영 확인 결함: P1-X-03 세션 만료 시 '다시 로그인해 주세요' 안내 없음, P1-12-07 카운트다운이 시계 차이로 한도를 넘게 표시. dev:mock 범위 미해결 없음. 실제 메일 7통(사용자 승인, 사용자 Gmail 별칭)</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,17 +53,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE9B8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D3CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,12 +95,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -998,18 +982,18 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 주 시작 요일 일요일로 바꾸면 즉시 저장(version 증가). 캘린더 반영은 확인 불가</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 주 시작 일요일 → 캘린더 주 보기 10/4~10/10, 미니 달력 일월화… / 월요일로 되돌리면 10/5~10/11</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>캘린더(P1-07) 구현 전</t>
+          <t>[이전] BLOCKED [로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 주 시작 요일 일요일로 바꾸면 즉시 저장(version</t>
         </is>
       </c>
     </row>
@@ -1056,18 +1040,18 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 시간대 도쿄로 바꾸면 즉시 저장. 안내 '시간대를 바꿔도 기존 기록의 날짜는 그대로예요. 시각 표시만 새 시간대로 바뀌어요.'는 화면에 늘 표시. 일정 시각 표시는 확인 불가</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 시간대 변경 → 안내 '시간대를 바꿔도 기존 기록의 날짜는 그대로예요…', 일정은 만든 시간대 기준 그대로 표시만 바뀜(America/New_York, 서머타임 반영) — 운영 P1-05-08과 같은 확인</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>일정 화면(P1-05·07) 구현 전. 안내를 변경 시에만이 아니라 늘 보여 줌 — 화면정의서 '시간대 변경 시 안내'와 표현 차이, 판단은 erp-design</t>
+          <t>[이전] BLOCKED [로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06] 시간대 도쿄로 바꾸면 즉시 저장. 안내 '시간대를 바꿔</t>
         </is>
       </c>
     </row>
@@ -1280,18 +1264,18 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 이름을 'QA 테스터'로 변경 → identity와 worklog/me 모두 3초 안에 반영, 사이드바·홈 인사('좋은 저녁이에요, QA 테스터님')에 표시</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>worklog 화면에서 이름을 보여 주는 곳이 아직 없고, dev:mock은 worklog 재조회를 흉내만 냄. 운영 배포 후 확인</t>
+          <t>늦게 온 옛 값이 덮어쓰지 않는지(version)는 외부에서 재현할 수 없어 확인 범위 밖 / [이전] BLOCKED [로컬 dev:mock, feature/P1 a5bb168 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5725,7 @@
           <t>홈 오늘 일정 영역(③)은 P2라 대상 없음</t>
         </is>
       </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5904,18 +5888,18 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] Enter 저장: 'QA 회의 준비 15-16' → 업무+일정(오늘 15:00–16:00, 업무 연결), 'QA 보고서 정리' → 업무만, 각각 되돌리기 토스트(연속이면 누적 표시)</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Enter 저장: API 연결 전(pm 지시)</t>
+          <t>[이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -6078,18 +6062,18 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 #견적 #결제 #견적' → 태그 칩 2개(같은 이름 하나로), '#새태그'·'#1번' → 점선 '새' 칩. 규칙에 안 맞는 'C# 공부'·'메일 a@b.com 확인'·'보고서 @ #'은 칩 없이 제목에 남음. '@개발 @영업'은 처음 것(개발)만 프로젝트</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 'QA 보고서 #긴급 #검토' 저장 → 없는 태그 2개를 저장할 때 만들고 업무에 2개 연결</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>표시는 확인. 저장 시 태그 생성·연결은 Enter 저장 API 연결 전</t>
+          <t>새 태그 칩 모양(점선·새 표시)은 dev:mock에서 확인 / [이전] BLOCKED [로컬 dev:mock, feature/P1 421c64f 스냅숏, 2026-10-06] '보고서 #견적 #결제 #견적' → 태그 칩 2개(같은</t>
         </is>
       </c>
     </row>
@@ -6190,18 +6174,18 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 해석 칩이 &lt;li&gt;(tabIndex -1)로 눌러서 고칠 수 없음 — 칩 수정 드롭다운 미구현</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>칩 수정 드롭다운: API 연결 전(pm 지시)</t>
+          <t>P2로 이관, 2026-10-06 사용자 결정 / [이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -6360,18 +6344,18 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 한글 조합 중 Enter(isComposing) → 저장되지 않고 입력 유지, 조합이 끝난 뒤 Enter → 저장</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>한글 조합 중 Enter 무시: Enter 저장(API 연결 전(pm 지시))이 없어 화면으로 확인 불가. 코드에는 isComposing 검사가 있음(QuickInput.tsx)</t>
+          <t>[이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -6476,18 +6460,18 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 팝오버 ①시간 칩(→ 자세히, 제목 이어짐)·②입력 시간 덮어쓰기('입력한 시간으로 만들어요')·Enter 저장·Esc 취소는 동작. ③해석 칩·④'업무로도 만들기' 토글 없음 → 'QA 팝오버 저장 @영업'은 일정만 생기고 @영업 정보가 사라짐</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>캘린더 빠른 생성 팝오버: 캘린더(P1-07) 구현 전</t>
+          <t>P2로 이관, 2026-10-06 사용자 결정. 정보 손실 방지 수정(@프로젝트·#태그를 제목에 남김)은 PR #4 — 배포 뒤 재확인 필요 / [이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -6534,18 +6518,18 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 빠른 입력에 포커스해도 자주 하는 업무 제안 목록 없음 — 미구현</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>자주 하는 업무 제안: API 연결 전(pm 지시)</t>
+          <t>P2로 이관, 2026-10-06 사용자 결정 / [이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -6708,18 +6692,18 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 명령 팔레트에 '보고서' 입력 → 업무 검색 결과 그룹 없이 '‘보고서’를 업무로 추가'만 표시 — 업무 검색 미구현(일지 검색은 P3)</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>업무·일지 검색: API 연결 전(pm 지시)</t>
+          <t>P2로 이관, 2026-10-06 사용자 결정(pm 판단, P1 운영 뒤 발견된 미구현 기능) / [이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -6824,18 +6808,18 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 업무 3개 연속 보관 → 토스트 하나에 '업무 3개를 보관했어요'(좌하단), 마우스를 올리면 7초 동안 유지, 입력창 밖 Ctrl+Z로 3개 모두 복원</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>되돌리기 토스트(보관·누적·유지·Ctrl+Z 복원): 되돌릴 동작을 만드는 API 연결 전(pm 지시)</t>
+          <t>[이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -6936,18 +6920,18 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>[로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
-        </is>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] 390px에서 보관 토스트가 하단 탭 위(토스트 아래끝 756px, 탭 위끝 772px), 되돌리기 정상</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>모바일 되돌리기 토스트 위치: API 연결 전(pm 지시)</t>
+          <t>[이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
@@ -7856,18 +7840,18 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 다시 받기 직후 버튼 비활성, 바로 다시 요청하면 서버도 429 RESEND_TOO_SOON으로 거부(메일 안 나감). 결함: 카운트다운이 '다시 받기 · 69초', '남은 시간 10:09'처럼 한도(60초·10:00)를 넘게 표시됨 — PC 시계가 서버보다 약 10초 늦어 서버 시각 기준 계산이 늘어남(재설정 화면도 같음)</t>
-        </is>
-      </c>
-      <c r="J130" s="6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] [재측정] 새 코드 받기(메일 1통, 사용자 승인) → PC 시계가 서버보다 약 11초 늦은 상태에서도 '남은 시간 10:00 | 다시 받기 · 60초'로 한도에서 멈춘 뒤 09:45·45초로 감소. 직후 재요청은 서버도 429 RESEND_TOO_SOON(이전 실행)</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] pm 판단: 결함(작음), 표시를 한도로 잘라야 함 — frontend 배정</t>
+          <t>[이전 FAIL 3d1159e] 카운트다운이 한도를 넘음 → 해결(daf818c) / [이전] FAIL [운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 다시 받기</t>
         </is>
       </c>
     </row>
@@ -9332,18 +9316,18 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>[운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 로그인 중 쿠키 삭제 → 사이드바 이동 → 로그인 화면으로 이동하고 다시 로그인하면 원래 화면(/calendar/week)으로 복귀(정상). 결함: '다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.' 안내가 뜨지 않음(로그인 화면 state에 reason 없음)</t>
-        </is>
-      </c>
-      <c r="J156" s="6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[운영 wy-worklog.com, main 0e41caa(PR #3), 2026-10-06, 계정은 사용자 Gmail 별칭] [재측정] 로그인 중 쿠키 삭제 → 사이드바 이동 → /login(state.reason='expired'), '다시 로그인해 주세요. 로그인 후 보던 화면으로 돌아가요.' 표시 → 다시 로그인하면 원래 화면(/calendar/week)</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>[병합 직후 운영 확인] 추정: 동시 401에서 handleSessionExpired 두 번째 호출이 세션 종료 이유를 지움 — frontend</t>
+          <t>[이전 FAIL 3d1159e] 안내 없음 → 해결(daf818c) / [이전] FAIL [운영 wy-worklog.com, main 3d1159e(PR #2 병합), 2026-10-06, 계정은 사용자 Gmail 별칭] 로그인 중</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10179,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 (P1 dev:mock 전체 + 병합 직후 운영 확인, main 3d1159e)</t>
+          <t>2026-10-06 (P1 dev:mock 전체 + 운영 확인 main 3d1159e·0e41caa)</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10227,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PASS 147, BLOCKED 12, N/A 1, FAIL 2</t>
+          <t>PASS 157, N/A 5</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10239,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>운영 확인 결함: P1-X-03 세션 만료 시 '다시 로그인해 주세요' 안내 없음, P1-12-07 카운트다운이 시계 차이로 한도를 넘게 표시. dev:mock 범위 미해결 없음. 실제 메일 7통(사용자 승인, 사용자 Gmail 별칭)</t>
+          <t>미해결 없음. P2 이관 4건(P1-09-09 팝오버 해석 칩·토글, P1-09-10 자주 하는 업무, P1-09-12 칩 수정, P1-10-08 팔레트 업무 검색). P1-09-09 정보 손실 방지는 PR #4 배포 뒤 재확인. 실제 메일 8통(사용자 승인, 사용자 Gmail 별칭)</t>
         </is>
       </c>
     </row>

--- a/docs/qa/P1-화면테스트_v1.0.xlsx
+++ b/docs/qa/P1-화면테스트_v1.0.xlsx
@@ -6471,7 +6471,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>P2로 이관, 2026-10-06 사용자 결정. 정보 손실 방지 수정(@프로젝트·#태그를 제목에 남김)은 PR #4 — 배포 뒤 재확인 필요 / [이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
+          <t>P2로 이관, 2026-10-06 사용자 결정. 정보 손실 방지(PR #4) 운영 재확인 PASS(main 9d94d71, 2026-10-06): 팝오버 'QA 팝오버 @영업 #태그 !높음 ~내일 15-16' 저장 → 제목 'QA 팝오버 @영업 #태그 !높음 ~내일'(토큰 그대로), 시간 15-16은 해석돼 15:00–16:00 일정으로, 제목에서 빠짐 / [이전] BLOCKED [로컬 dev:mock·mock 빌드, feature/P1 786eaf7 스냅숏, 2026-10-06]</t>
         </is>
       </c>
     </row>
